--- a/artfynd/A 8219-2025 artfynd.xlsx
+++ b/artfynd/A 8219-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY48"/>
+  <dimension ref="A1:AY49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>66544349</v>
+        <v>125605476</v>
       </c>
       <c r="B2" t="n">
-        <v>89388</v>
+        <v>91180</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>1204</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Djupfors V, Ly lm</t>
+          <t>Järnforsen, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>560829.2017359853</v>
+        <v>559981</v>
       </c>
       <c r="R2" t="n">
-        <v>7309021.683959483</v>
+        <v>7309888</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2014-09-05</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2014-09-05</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,31 +761,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>25090</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Malin Sahlin</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>66544354</v>
+        <v>66544349</v>
       </c>
       <c r="B3" t="n">
-        <v>89410</v>
+        <v>89388</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>560817.2887951054</v>
+        <v>560829.2017359853</v>
       </c>
       <c r="R3" t="n">
-        <v>7309023.475668295</v>
+        <v>7309021.683959483</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -891,7 +876,7 @@
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>25094</t>
+          <t>25090</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -909,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119301540</v>
+        <v>66544354</v>
       </c>
       <c r="B4" t="n">
-        <v>57257</v>
+        <v>89410</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,41 +906,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102620</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hökuggla</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Surnia ulula</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Järnforsen, Ly lm</t>
+          <t>Djupfors V, Ly lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>559939</v>
+        <v>560817.2887951054</v>
       </c>
       <c r="R4" t="n">
-        <v>7309726</v>
+        <v>7309023.475668295</v>
       </c>
       <c r="S4" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,22 +964,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2014-09-05</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2014-09-05</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,26 +990,31 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>25094</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Sonata Isaksson</t>
+          <t>Malin Sahlin</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sonata Isaksson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>66544347</v>
+        <v>119301540</v>
       </c>
       <c r="B5" t="n">
-        <v>89392</v>
+        <v>57257</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,41 +1023,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>102620</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Hökuggla</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Surnia ulula</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Djupfors V, Ly lm</t>
+          <t>Järnforsen, Ly lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>560878.5341145619</v>
+        <v>559939</v>
       </c>
       <c r="R5" t="n">
-        <v>7308993.284323963</v>
+        <v>7309726</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1091,22 +1081,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2014-09-05</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2014-09-05</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1117,28 +1107,23 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>25088</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Malin Sahlin</t>
+          <t>Sonata Isaksson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Sonata Isaksson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>66544345</v>
+        <v>66544347</v>
       </c>
       <c r="B6" t="n">
         <v>89392</v>
@@ -1178,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>560921.9021753618</v>
+        <v>560878.5341145619</v>
       </c>
       <c r="R6" t="n">
-        <v>7308956.577612261</v>
+        <v>7308993.284323963</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1237,7 +1222,7 @@
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>25086</t>
+          <t>25088</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1255,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>66544351</v>
+        <v>66544345</v>
       </c>
       <c r="B7" t="n">
-        <v>89673</v>
+        <v>89392</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,21 +1256,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1295,10 +1280,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>560857.1901938798</v>
+        <v>560921.9021753618</v>
       </c>
       <c r="R7" t="n">
-        <v>7309014.91711883</v>
+        <v>7308956.577612261</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1354,7 +1339,7 @@
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>25092</t>
+          <t>25086</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1372,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>66544353</v>
+        <v>66544351</v>
       </c>
       <c r="B8" t="n">
-        <v>89356</v>
+        <v>89673</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1384,25 +1369,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1471,7 +1456,7 @@
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>25093</t>
+          <t>25092</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1489,10 +1474,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>66544343</v>
+        <v>66544353</v>
       </c>
       <c r="B9" t="n">
-        <v>89392</v>
+        <v>89356</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1501,25 +1486,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1529,10 +1514,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>560933.9809844483</v>
+        <v>560857.1901938798</v>
       </c>
       <c r="R9" t="n">
-        <v>7308947.018279012</v>
+        <v>7309014.91711883</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1588,7 +1573,7 @@
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>25084</t>
+          <t>25093</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1606,10 +1591,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>66544348</v>
+        <v>66544343</v>
       </c>
       <c r="B10" t="n">
-        <v>89388</v>
+        <v>89392</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1622,21 +1607,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1646,10 +1631,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>560863.3901593408</v>
+        <v>560933.9809844483</v>
       </c>
       <c r="R10" t="n">
-        <v>7308992.96197705</v>
+        <v>7308947.018279012</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1705,7 +1690,7 @@
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>25089</t>
+          <t>25084</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1723,10 +1708,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>66544344</v>
+        <v>66544348</v>
       </c>
       <c r="B11" t="n">
-        <v>89780</v>
+        <v>89388</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1735,25 +1720,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4217</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1763,10 +1748,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>560933.9809844483</v>
+        <v>560863.3901593408</v>
       </c>
       <c r="R11" t="n">
-        <v>7308947.018279012</v>
+        <v>7308992.96197705</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1822,7 +1807,7 @@
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>25085</t>
+          <t>25089</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1840,10 +1825,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>66544346</v>
+        <v>66544344</v>
       </c>
       <c r="B12" t="n">
-        <v>77506</v>
+        <v>89780</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1852,25 +1837,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>4217</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1880,10 +1865,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>560921.9021753618</v>
+        <v>560933.9809844483</v>
       </c>
       <c r="R12" t="n">
-        <v>7308956.577612261</v>
+        <v>7308947.018279012</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1939,7 +1924,7 @@
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>25087</t>
+          <t>25085</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1957,10 +1942,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>66544350</v>
+        <v>66544346</v>
       </c>
       <c r="B13" t="n">
-        <v>89392</v>
+        <v>77506</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1973,21 +1958,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1997,10 +1982,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>560857.1901938798</v>
+        <v>560921.9021753618</v>
       </c>
       <c r="R13" t="n">
-        <v>7309014.91711883</v>
+        <v>7308956.577612261</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -2056,7 +2041,7 @@
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>25091</t>
+          <t>25087</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2074,10 +2059,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>66544342</v>
+        <v>66544350</v>
       </c>
       <c r="B14" t="n">
-        <v>90074</v>
+        <v>89392</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2086,25 +2071,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2114,10 +2099,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>560960.3945341655</v>
+        <v>560857.1901938798</v>
       </c>
       <c r="R14" t="n">
-        <v>7308918.130968786</v>
+        <v>7309014.91711883</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2173,7 +2158,7 @@
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>25083</t>
+          <t>25091</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2191,10 +2176,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>66544630</v>
+        <v>66544342</v>
       </c>
       <c r="B15" t="n">
-        <v>89388</v>
+        <v>90074</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2203,25 +2188,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2231,10 +2216,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>561061.5146522231</v>
+        <v>560960.3945341655</v>
       </c>
       <c r="R15" t="n">
-        <v>7308842.570840668</v>
+        <v>7308918.130968786</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2290,7 +2275,7 @@
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>25353</t>
+          <t>25083</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2301,17 +2286,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Via Malin Sahlin</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>66544637</v>
+        <v>66544630</v>
       </c>
       <c r="B16" t="n">
-        <v>89410</v>
+        <v>89388</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2324,21 +2309,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2348,10 +2333,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>561099.626093693</v>
+        <v>561061.5146522231</v>
       </c>
       <c r="R16" t="n">
-        <v>7308822.114403572</v>
+        <v>7308842.570840668</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2407,7 +2392,7 @@
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>25360</t>
+          <t>25353</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2425,10 +2410,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>66544633</v>
+        <v>66544637</v>
       </c>
       <c r="B17" t="n">
-        <v>90160</v>
+        <v>89410</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2437,25 +2422,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>918</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2465,10 +2450,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>561072.4974219487</v>
+        <v>561099.626093693</v>
       </c>
       <c r="R17" t="n">
-        <v>7308826.852570722</v>
+        <v>7308822.114403572</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2524,7 +2509,7 @@
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>25356</t>
+          <t>25360</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2542,10 +2527,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>66544627</v>
+        <v>66544633</v>
       </c>
       <c r="B18" t="n">
-        <v>89392</v>
+        <v>90160</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2554,25 +2539,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>918</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2582,10 +2567,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>561044.5755368763</v>
+        <v>561072.4974219487</v>
       </c>
       <c r="R18" t="n">
-        <v>7308849.572017924</v>
+        <v>7308826.852570722</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2641,7 +2626,7 @@
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>25350</t>
+          <t>25356</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2659,10 +2644,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>66544641</v>
+        <v>66544627</v>
       </c>
       <c r="B19" t="n">
-        <v>89832</v>
+        <v>89392</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2671,25 +2656,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2699,10 +2684,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>561099.626093693</v>
+        <v>561044.5755368763</v>
       </c>
       <c r="R19" t="n">
-        <v>7308822.114403572</v>
+        <v>7308849.572017924</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2758,7 +2743,7 @@
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>25364</t>
+          <t>25350</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2776,10 +2761,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>66544639</v>
+        <v>66544641</v>
       </c>
       <c r="B20" t="n">
-        <v>77506</v>
+        <v>89832</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2788,32 +2773,28 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Djupfors V, Ly lm</t>
@@ -2879,7 +2860,7 @@
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>25362</t>
+          <t>25364</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2897,10 +2878,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>66544619</v>
+        <v>66544639</v>
       </c>
       <c r="B21" t="n">
-        <v>81236</v>
+        <v>77506</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2913,34 +2894,38 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Djupfors V, Ly lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>561027.2184662716</v>
+        <v>561099.626093693</v>
       </c>
       <c r="R21" t="n">
-        <v>7308856.973397947</v>
+        <v>7308822.114403572</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2996,7 +2981,7 @@
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>25343</t>
+          <t>25362</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3014,10 +2999,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>66544626</v>
+        <v>66544619</v>
       </c>
       <c r="B22" t="n">
-        <v>77506</v>
+        <v>81236</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3030,38 +3015,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Djupfors V, Ly lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>561044.5755368763</v>
+        <v>561027.2184662716</v>
       </c>
       <c r="R22" t="n">
-        <v>7308849.572017924</v>
+        <v>7308856.973397947</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -3117,7 +3098,7 @@
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>25349</t>
+          <t>25343</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3135,10 +3116,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>66544638</v>
+        <v>66544626</v>
       </c>
       <c r="B23" t="n">
-        <v>89673</v>
+        <v>77506</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3151,34 +3132,38 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Djupfors V, Ly lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>561099.626093693</v>
+        <v>561044.5755368763</v>
       </c>
       <c r="R23" t="n">
-        <v>7308822.114403572</v>
+        <v>7308849.572017924</v>
       </c>
       <c r="S23" t="n">
         <v>50</v>
@@ -3234,7 +3219,7 @@
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>25361</t>
+          <t>25349</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3252,10 +3237,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>66544620</v>
+        <v>66544638</v>
       </c>
       <c r="B24" t="n">
-        <v>89410</v>
+        <v>89673</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3268,21 +3253,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3292,10 +3277,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>561027.2184662716</v>
+        <v>561099.626093693</v>
       </c>
       <c r="R24" t="n">
-        <v>7308856.973397947</v>
+        <v>7308822.114403572</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3351,7 +3336,7 @@
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>25344</t>
+          <t>25361</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3369,10 +3354,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>66544640</v>
+        <v>66544620</v>
       </c>
       <c r="B25" t="n">
-        <v>89392</v>
+        <v>89410</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3385,21 +3370,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3409,10 +3394,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>561099.626093693</v>
+        <v>561027.2184662716</v>
       </c>
       <c r="R25" t="n">
-        <v>7308822.114403572</v>
+        <v>7308856.973397947</v>
       </c>
       <c r="S25" t="n">
         <v>50</v>
@@ -3468,7 +3453,7 @@
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>25363</t>
+          <t>25344</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3486,10 +3471,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>66544649</v>
+        <v>66544640</v>
       </c>
       <c r="B26" t="n">
-        <v>81236</v>
+        <v>89392</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3502,21 +3487,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3526,10 +3511,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>561139.9464785276</v>
+        <v>561099.626093693</v>
       </c>
       <c r="R26" t="n">
-        <v>7308736.66569937</v>
+        <v>7308822.114403572</v>
       </c>
       <c r="S26" t="n">
         <v>50</v>
@@ -3585,7 +3570,7 @@
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>25372</t>
+          <t>25363</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3603,10 +3588,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>66544642</v>
+        <v>66544649</v>
       </c>
       <c r="B27" t="n">
-        <v>89410</v>
+        <v>81236</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3619,21 +3604,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3643,10 +3628,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>561096.8231878708</v>
+        <v>561139.9464785276</v>
       </c>
       <c r="R27" t="n">
-        <v>7308799.96586439</v>
+        <v>7308736.66569937</v>
       </c>
       <c r="S27" t="n">
         <v>50</v>
@@ -3702,7 +3687,7 @@
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>25365</t>
+          <t>25372</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3720,10 +3705,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>66544623</v>
+        <v>66544642</v>
       </c>
       <c r="B28" t="n">
-        <v>89673</v>
+        <v>89410</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3736,38 +3721,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Djupfors V, Ly lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>561044.5755368763</v>
+        <v>561096.8231878708</v>
       </c>
       <c r="R28" t="n">
-        <v>7308849.572017924</v>
+        <v>7308799.96586439</v>
       </c>
       <c r="S28" t="n">
         <v>50</v>
@@ -3823,7 +3804,7 @@
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>25347</t>
+          <t>25365</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3841,10 +3822,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>66544341</v>
+        <v>66544623</v>
       </c>
       <c r="B29" t="n">
-        <v>77506</v>
+        <v>89673</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3857,34 +3838,38 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Djupfors V, Ly lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>561008.5625325058</v>
+        <v>561044.5755368763</v>
       </c>
       <c r="R29" t="n">
-        <v>7308906.069035768</v>
+        <v>7308849.572017924</v>
       </c>
       <c r="S29" t="n">
         <v>50</v>
@@ -3940,7 +3925,7 @@
       </c>
       <c r="AR29" t="inlineStr">
         <is>
-          <t>25082</t>
+          <t>25347</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3951,14 +3936,14 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Via Malin Sahlin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>66544622</v>
+        <v>66544341</v>
       </c>
       <c r="B30" t="n">
         <v>77506</v>
@@ -3991,21 +3976,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Djupfors V, Ly lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>561027.2184662716</v>
+        <v>561008.5625325058</v>
       </c>
       <c r="R30" t="n">
-        <v>7308856.973397947</v>
+        <v>7308906.069035768</v>
       </c>
       <c r="S30" t="n">
         <v>50</v>
@@ -4061,7 +4042,7 @@
       </c>
       <c r="AR30" t="inlineStr">
         <is>
-          <t>25346</t>
+          <t>25082</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4072,17 +4053,17 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Via Malin Sahlin</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>66544651</v>
+        <v>66544622</v>
       </c>
       <c r="B31" t="n">
-        <v>89673</v>
+        <v>77506</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4095,34 +4076,38 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Djupfors V, Ly lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>561139.9464785276</v>
+        <v>561027.2184662716</v>
       </c>
       <c r="R31" t="n">
-        <v>7308736.66569937</v>
+        <v>7308856.973397947</v>
       </c>
       <c r="S31" t="n">
         <v>50</v>
@@ -4178,7 +4163,7 @@
       </c>
       <c r="AR31" t="inlineStr">
         <is>
-          <t>25373</t>
+          <t>25346</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4196,10 +4181,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>66544631</v>
+        <v>66544651</v>
       </c>
       <c r="B32" t="n">
-        <v>77506</v>
+        <v>89673</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4212,38 +4197,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Djupfors V, Ly lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>561061.5146522231</v>
+        <v>561139.9464785276</v>
       </c>
       <c r="R32" t="n">
-        <v>7308842.570840668</v>
+        <v>7308736.66569937</v>
       </c>
       <c r="S32" t="n">
         <v>50</v>
@@ -4299,7 +4280,7 @@
       </c>
       <c r="AR32" t="inlineStr">
         <is>
-          <t>25354</t>
+          <t>25373</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4317,10 +4298,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>66544621</v>
+        <v>66544631</v>
       </c>
       <c r="B33" t="n">
-        <v>56395</v>
+        <v>77506</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4333,34 +4314,38 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Djupfors V, Ly lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>561027.2184662716</v>
+        <v>561061.5146522231</v>
       </c>
       <c r="R33" t="n">
-        <v>7308856.973397947</v>
+        <v>7308842.570840668</v>
       </c>
       <c r="S33" t="n">
         <v>50</v>
@@ -4416,7 +4401,7 @@
       </c>
       <c r="AR33" t="inlineStr">
         <is>
-          <t>25345</t>
+          <t>25354</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4434,10 +4419,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>66544647</v>
+        <v>66544621</v>
       </c>
       <c r="B34" t="n">
-        <v>77506</v>
+        <v>56395</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4450,38 +4435,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Djupfors V, Ly lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>561118.808368561</v>
+        <v>561027.2184662716</v>
       </c>
       <c r="R34" t="n">
-        <v>7308748.485677995</v>
+        <v>7308856.973397947</v>
       </c>
       <c r="S34" t="n">
         <v>50</v>
@@ -4537,7 +4518,7 @@
       </c>
       <c r="AR34" t="inlineStr">
         <is>
-          <t>25370</t>
+          <t>25345</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4555,7 +4536,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>66544635</v>
+        <v>66544647</v>
       </c>
       <c r="B35" t="n">
         <v>77506</v>
@@ -4599,10 +4580,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>561072.4974219487</v>
+        <v>561118.808368561</v>
       </c>
       <c r="R35" t="n">
-        <v>7308826.852570722</v>
+        <v>7308748.485677995</v>
       </c>
       <c r="S35" t="n">
         <v>50</v>
@@ -4658,7 +4639,7 @@
       </c>
       <c r="AR35" t="inlineStr">
         <is>
-          <t>25358</t>
+          <t>25370</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4676,10 +4657,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>66544648</v>
+        <v>66544635</v>
       </c>
       <c r="B36" t="n">
-        <v>85703</v>
+        <v>77506</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4692,34 +4673,38 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Djupfors V, Ly lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>561139.9464785276</v>
+        <v>561072.4974219487</v>
       </c>
       <c r="R36" t="n">
-        <v>7308736.66569937</v>
+        <v>7308826.852570722</v>
       </c>
       <c r="S36" t="n">
         <v>50</v>
@@ -4775,7 +4760,7 @@
       </c>
       <c r="AR36" t="inlineStr">
         <is>
-          <t>25371</t>
+          <t>25358</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4793,10 +4778,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>66544628</v>
+        <v>66544648</v>
       </c>
       <c r="B37" t="n">
-        <v>89388</v>
+        <v>85703</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4809,21 +4794,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1108</v>
+        <v>510</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4833,10 +4818,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>561044.5755368763</v>
+        <v>561139.9464785276</v>
       </c>
       <c r="R37" t="n">
-        <v>7308849.572017924</v>
+        <v>7308736.66569937</v>
       </c>
       <c r="S37" t="n">
         <v>50</v>
@@ -4892,7 +4877,7 @@
       </c>
       <c r="AR37" t="inlineStr">
         <is>
-          <t>25351</t>
+          <t>25371</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4910,10 +4895,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>66544645</v>
+        <v>66544628</v>
       </c>
       <c r="B38" t="n">
-        <v>89673</v>
+        <v>89388</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4926,21 +4911,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>658</v>
+        <v>1108</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4950,10 +4935,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>561118.808368561</v>
+        <v>561044.5755368763</v>
       </c>
       <c r="R38" t="n">
-        <v>7308748.485677995</v>
+        <v>7308849.572017924</v>
       </c>
       <c r="S38" t="n">
         <v>50</v>
@@ -5009,7 +4994,7 @@
       </c>
       <c r="AR38" t="inlineStr">
         <is>
-          <t>25368</t>
+          <t>25351</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5027,10 +5012,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>66544636</v>
+        <v>66544645</v>
       </c>
       <c r="B39" t="n">
-        <v>81236</v>
+        <v>89673</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5043,21 +5028,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5067,10 +5052,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>561072.4974219487</v>
+        <v>561118.808368561</v>
       </c>
       <c r="R39" t="n">
-        <v>7308826.852570722</v>
+        <v>7308748.485677995</v>
       </c>
       <c r="S39" t="n">
         <v>50</v>
@@ -5126,7 +5111,7 @@
       </c>
       <c r="AR39" t="inlineStr">
         <is>
-          <t>25359</t>
+          <t>25368</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5144,10 +5129,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>66544634</v>
+        <v>66544636</v>
       </c>
       <c r="B40" t="n">
-        <v>89356</v>
+        <v>81236</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5156,25 +5141,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5243,7 +5228,7 @@
       </c>
       <c r="AR40" t="inlineStr">
         <is>
-          <t>25357</t>
+          <t>25359</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5261,10 +5246,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>66544646</v>
+        <v>66544634</v>
       </c>
       <c r="B41" t="n">
-        <v>89392</v>
+        <v>89356</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5273,25 +5258,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5301,10 +5286,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>561118.808368561</v>
+        <v>561072.4974219487</v>
       </c>
       <c r="R41" t="n">
-        <v>7308748.485677995</v>
+        <v>7308826.852570722</v>
       </c>
       <c r="S41" t="n">
         <v>50</v>
@@ -5360,7 +5345,7 @@
       </c>
       <c r="AR41" t="inlineStr">
         <is>
-          <t>25369</t>
+          <t>25357</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5378,10 +5363,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>66544632</v>
+        <v>66544646</v>
       </c>
       <c r="B42" t="n">
-        <v>81236</v>
+        <v>89392</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5394,21 +5379,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5418,10 +5403,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>561061.5146522231</v>
+        <v>561118.808368561</v>
       </c>
       <c r="R42" t="n">
-        <v>7308842.570840668</v>
+        <v>7308748.485677995</v>
       </c>
       <c r="S42" t="n">
         <v>50</v>
@@ -5477,7 +5462,7 @@
       </c>
       <c r="AR42" t="inlineStr">
         <is>
-          <t>25355</t>
+          <t>25369</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5495,10 +5480,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>66544625</v>
+        <v>66544632</v>
       </c>
       <c r="B43" t="n">
-        <v>56395</v>
+        <v>81236</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5511,21 +5496,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5535,10 +5520,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>561044.5755368763</v>
+        <v>561061.5146522231</v>
       </c>
       <c r="R43" t="n">
-        <v>7308849.572017924</v>
+        <v>7308842.570840668</v>
       </c>
       <c r="S43" t="n">
         <v>50</v>
@@ -5594,7 +5579,7 @@
       </c>
       <c r="AR43" t="inlineStr">
         <is>
-          <t>25348</t>
+          <t>25355</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5612,10 +5597,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>66544643</v>
+        <v>66544625</v>
       </c>
       <c r="B44" t="n">
-        <v>77506</v>
+        <v>56395</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5628,38 +5613,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Djupfors V, Ly lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>561108.4689856211</v>
+        <v>561044.5755368763</v>
       </c>
       <c r="R44" t="n">
-        <v>7308772.399080777</v>
+        <v>7308849.572017924</v>
       </c>
       <c r="S44" t="n">
         <v>50</v>
@@ -5715,7 +5696,7 @@
       </c>
       <c r="AR44" t="inlineStr">
         <is>
-          <t>25366</t>
+          <t>25348</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5733,10 +5714,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>66544644</v>
+        <v>66544643</v>
       </c>
       <c r="B45" t="n">
-        <v>81236</v>
+        <v>77506</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5749,24 +5730,28 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Djupfors V, Ly lm</t>
@@ -5832,7 +5817,7 @@
       </c>
       <c r="AR45" t="inlineStr">
         <is>
-          <t>25367</t>
+          <t>25366</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -5850,10 +5835,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>66544629</v>
+        <v>66544644</v>
       </c>
       <c r="B46" t="n">
-        <v>89406</v>
+        <v>81236</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5866,21 +5851,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5890,10 +5875,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>561061.5146522231</v>
+        <v>561108.4689856211</v>
       </c>
       <c r="R46" t="n">
-        <v>7308842.570840668</v>
+        <v>7308772.399080777</v>
       </c>
       <c r="S46" t="n">
         <v>50</v>
@@ -5949,7 +5934,7 @@
       </c>
       <c r="AR46" t="inlineStr">
         <is>
-          <t>25352</t>
+          <t>25367</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5967,10 +5952,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>66544653</v>
+        <v>66544629</v>
       </c>
       <c r="B47" t="n">
-        <v>89388</v>
+        <v>89406</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5983,21 +5968,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1108</v>
+        <v>1204</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6007,10 +5992,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>561132.2069487682</v>
+        <v>561061.5146522231</v>
       </c>
       <c r="R47" t="n">
-        <v>7308696.41208922</v>
+        <v>7308842.570840668</v>
       </c>
       <c r="S47" t="n">
         <v>50</v>
@@ -6066,7 +6051,7 @@
       </c>
       <c r="AR47" t="inlineStr">
         <is>
-          <t>25375</t>
+          <t>25352</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6084,10 +6069,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>66544652</v>
+        <v>66544653</v>
       </c>
       <c r="B48" t="n">
-        <v>81236</v>
+        <v>89388</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6100,21 +6085,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6183,7 +6168,7 @@
       </c>
       <c r="AR48" t="inlineStr">
         <is>
-          <t>25374</t>
+          <t>25375</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6198,6 +6183,123 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>66544652</v>
+      </c>
+      <c r="B49" t="n">
+        <v>81236</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Djupfors V, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>561132.2069487682</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7308696.41208922</v>
+      </c>
+      <c r="S49" t="n">
+        <v>50</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2014-09-05</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2014-09-05</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR49" t="inlineStr">
+        <is>
+          <t>25374</t>
+        </is>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Malin Sahlin</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Via Malin Sahlin</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 8219-2025 artfynd.xlsx
+++ b/artfynd/A 8219-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>125605476</v>
       </c>
       <c r="B2" t="n">
-        <v>91180</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91234</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 8219-2025 artfynd.xlsx
+++ b/artfynd/A 8219-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125605476</v>
       </c>
       <c r="B2" t="n">
-        <v>91234</v>
+        <v>91241</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 8219-2025 artfynd.xlsx
+++ b/artfynd/A 8219-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125605476</v>
       </c>
       <c r="B2" t="n">
-        <v>91241</v>
+        <v>91242</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 8219-2025 artfynd.xlsx
+++ b/artfynd/A 8219-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125605476</v>
       </c>
       <c r="B2" t="n">
-        <v>91242</v>
+        <v>91246</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 8219-2025 artfynd.xlsx
+++ b/artfynd/A 8219-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125605476</v>
       </c>
       <c r="B2" t="n">
-        <v>91246</v>
+        <v>91248</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 8219-2025 artfynd.xlsx
+++ b/artfynd/A 8219-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125605476</v>
       </c>
       <c r="B2" t="n">
-        <v>91248</v>
+        <v>91250</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 8219-2025 artfynd.xlsx
+++ b/artfynd/A 8219-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125605476</v>
       </c>
       <c r="B2" t="n">
-        <v>91250</v>
+        <v>91252</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 8219-2025 artfynd.xlsx
+++ b/artfynd/A 8219-2025 artfynd.xlsx
@@ -976,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126356815</v>
+        <v>126356440</v>
       </c>
       <c r="B5" t="n">
-        <v>91256</v>
+        <v>91538</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,21 +987,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>559785</v>
+        <v>559675</v>
       </c>
       <c r="R5" t="n">
-        <v>7310073</v>
+        <v>7310094</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1078,10 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126356440</v>
+        <v>126356815</v>
       </c>
       <c r="B6" t="n">
-        <v>91538</v>
+        <v>91256</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1089,21 +1089,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>559675</v>
+        <v>559785</v>
       </c>
       <c r="R6" t="n">
-        <v>7310094</v>
+        <v>7310073</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -3272,10 +3272,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126357916</v>
+        <v>126358035</v>
       </c>
       <c r="B27" t="n">
-        <v>92029</v>
+        <v>75063</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3283,21 +3283,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>918</v>
+        <v>492</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3307,10 +3307,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>560301</v>
+        <v>560363</v>
       </c>
       <c r="R27" t="n">
-        <v>7309435</v>
+        <v>7309388</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3374,7 +3374,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126357490</v>
+        <v>126357916</v>
       </c>
       <c r="B28" t="n">
         <v>92029</v>
@@ -3405,14 +3405,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Järnforsen, Järnforsen, Ly lm</t>
+          <t>Jipmomyran, Jipmomyran, Ly lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>560120</v>
+        <v>560301</v>
       </c>
       <c r="R28" t="n">
-        <v>7309549</v>
+        <v>7309435</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3476,10 +3476,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126358035</v>
+        <v>126357490</v>
       </c>
       <c r="B29" t="n">
-        <v>75063</v>
+        <v>92029</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3487,34 +3487,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>492</v>
+        <v>918</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Jipmomyran, Jipmomyran, Ly lm</t>
+          <t>Järnforsen, Järnforsen, Ly lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>560363</v>
+        <v>560120</v>
       </c>
       <c r="R29" t="n">
-        <v>7309388</v>
+        <v>7309549</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3782,7 +3782,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126358404</v>
+        <v>126357428</v>
       </c>
       <c r="B32" t="n">
         <v>80080</v>
@@ -3813,14 +3813,14 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Jipmomyran, Jipmomyran, Ly lm</t>
+          <t>Järnforsen, Järnforsen, Ly lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>560173</v>
+        <v>560096</v>
       </c>
       <c r="R32" t="n">
-        <v>7309178</v>
+        <v>7309597</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3866,7 +3866,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Lövrik grannaturskog</t>
+          <t>Frodig gråalskog vid bäckdråg</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -3884,7 +3884,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126357428</v>
+        <v>126358404</v>
       </c>
       <c r="B33" t="n">
         <v>80080</v>
@@ -3915,14 +3915,14 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Järnforsen, Järnforsen, Ly lm</t>
+          <t>Jipmomyran, Jipmomyran, Ly lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>560096</v>
+        <v>560173</v>
       </c>
       <c r="R33" t="n">
-        <v>7309597</v>
+        <v>7309178</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3968,7 +3968,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Frodig gråalskog vid bäckdråg</t>
+          <t>Lövrik grannaturskog</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -6173,32 +6173,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126360392</v>
+        <v>126360389</v>
       </c>
       <c r="B54" t="n">
-        <v>91538</v>
+        <v>91696</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6279,32 +6279,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126360389</v>
+        <v>126360392</v>
       </c>
       <c r="B55" t="n">
-        <v>91696</v>
+        <v>91538</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>

--- a/artfynd/A 8219-2025 artfynd.xlsx
+++ b/artfynd/A 8219-2025 artfynd.xlsx
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126355489</v>
+        <v>126355483</v>
       </c>
       <c r="B3" t="n">
-        <v>91538</v>
+        <v>91696</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -874,32 +874,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126355483</v>
+        <v>126355489</v>
       </c>
       <c r="B4" t="n">
-        <v>91696</v>
+        <v>91538</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>

--- a/artfynd/A 8219-2025 artfynd.xlsx
+++ b/artfynd/A 8219-2025 artfynd.xlsx
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126355483</v>
+        <v>126355489</v>
       </c>
       <c r="B3" t="n">
-        <v>91696</v>
+        <v>91538</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -874,32 +874,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126355489</v>
+        <v>126355483</v>
       </c>
       <c r="B4" t="n">
-        <v>91538</v>
+        <v>91696</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -976,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126356440</v>
+        <v>126356815</v>
       </c>
       <c r="B5" t="n">
-        <v>91538</v>
+        <v>91256</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,21 +987,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>559675</v>
+        <v>559785</v>
       </c>
       <c r="R5" t="n">
-        <v>7310094</v>
+        <v>7310073</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1078,10 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126356815</v>
+        <v>126356440</v>
       </c>
       <c r="B6" t="n">
-        <v>91256</v>
+        <v>91538</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1089,21 +1089,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>559785</v>
+        <v>559675</v>
       </c>
       <c r="R6" t="n">
-        <v>7310073</v>
+        <v>7310094</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 8219-2025 artfynd.xlsx
+++ b/artfynd/A 8219-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>126355489</v>
       </c>
       <c r="B3" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>126355483</v>
       </c>
       <c r="B4" t="n">
-        <v>91696</v>
+        <v>91699</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>126356815</v>
       </c>
       <c r="B5" t="n">
-        <v>91256</v>
+        <v>91259</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>126356440</v>
       </c>
       <c r="B6" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>126356310</v>
       </c>
       <c r="B7" t="n">
-        <v>91260</v>
+        <v>91263</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>126355857</v>
       </c>
       <c r="B8" t="n">
-        <v>91256</v>
+        <v>91259</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
         <v>126356436</v>
       </c>
       <c r="B9" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>126356649</v>
       </c>
       <c r="B10" t="n">
-        <v>92177</v>
+        <v>92180</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>126355561</v>
       </c>
       <c r="B11" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>126355961</v>
       </c>
       <c r="B12" t="n">
-        <v>91256</v>
+        <v>91259</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1800,10 +1800,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126356806</v>
+        <v>126355571</v>
       </c>
       <c r="B13" t="n">
-        <v>91260</v>
+        <v>96614</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1811,21 +1811,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>53</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1835,10 +1835,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>559785</v>
+        <v>559812</v>
       </c>
       <c r="R13" t="n">
-        <v>7310073</v>
+        <v>7309847</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1884,7 +1884,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Bördig grannaturskog i brant terräng</t>
+          <t>Bördig grannaturskog vid bäckravin</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -1902,10 +1902,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126355571</v>
+        <v>126356806</v>
       </c>
       <c r="B14" t="n">
-        <v>96605</v>
+        <v>91263</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1913,21 +1913,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>53</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1937,10 +1937,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>559812</v>
+        <v>559785</v>
       </c>
       <c r="R14" t="n">
-        <v>7309847</v>
+        <v>7310073</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Bördig grannaturskog vid bäckravin</t>
+          <t>Bördig grannaturskog i brant terräng</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2007,7 +2007,7 @@
         <v>126355558</v>
       </c>
       <c r="B15" t="n">
-        <v>91260</v>
+        <v>91263</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>126356631</v>
       </c>
       <c r="B16" t="n">
-        <v>98256</v>
+        <v>98265</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2211,7 +2211,7 @@
         <v>126356490</v>
       </c>
       <c r="B17" t="n">
-        <v>91256</v>
+        <v>91259</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         <v>126356501</v>
       </c>
       <c r="B18" t="n">
-        <v>91238</v>
+        <v>91241</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>126357389</v>
       </c>
       <c r="B19" t="n">
-        <v>91238</v>
+        <v>91241</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>126359227</v>
       </c>
       <c r="B20" t="n">
-        <v>75072</v>
+        <v>75075</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
         <v>126359406</v>
       </c>
       <c r="B21" t="n">
-        <v>91260</v>
+        <v>91263</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         <v>126357387</v>
       </c>
       <c r="B22" t="n">
-        <v>91260</v>
+        <v>91263</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3173,7 +3173,7 @@
         <v>126358030</v>
       </c>
       <c r="B26" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>126358035</v>
       </c>
       <c r="B27" t="n">
-        <v>75063</v>
+        <v>75066</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         <v>126357916</v>
       </c>
       <c r="B28" t="n">
-        <v>92029</v>
+        <v>92032</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>126357490</v>
       </c>
       <c r="B29" t="n">
-        <v>92029</v>
+        <v>92032</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         <v>126357506</v>
       </c>
       <c r="B30" t="n">
-        <v>91238</v>
+        <v>91241</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>126359216</v>
       </c>
       <c r="B31" t="n">
-        <v>91238</v>
+        <v>91241</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         <v>126357428</v>
       </c>
       <c r="B32" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3887,7 +3887,7 @@
         <v>126358404</v>
       </c>
       <c r="B33" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3989,7 +3989,7 @@
         <v>126357748</v>
       </c>
       <c r="B34" t="n">
-        <v>80081</v>
+        <v>80084</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4091,7 +4091,7 @@
         <v>126357718</v>
       </c>
       <c r="B35" t="n">
-        <v>91238</v>
+        <v>91241</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
         <v>126357434</v>
       </c>
       <c r="B36" t="n">
-        <v>97428</v>
+        <v>97437</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         <v>126358063</v>
       </c>
       <c r="B37" t="n">
-        <v>75064</v>
+        <v>75067</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4397,7 +4397,7 @@
         <v>126357705</v>
       </c>
       <c r="B38" t="n">
-        <v>91260</v>
+        <v>91263</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4499,7 +4499,7 @@
         <v>126358040</v>
       </c>
       <c r="B39" t="n">
-        <v>75077</v>
+        <v>75080</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         <v>126358290</v>
       </c>
       <c r="B40" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4703,7 +4703,7 @@
         <v>126358410</v>
       </c>
       <c r="B41" t="n">
-        <v>80081</v>
+        <v>80084</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5858,7 +5858,7 @@
         <v>126360335</v>
       </c>
       <c r="B51" t="n">
-        <v>91260</v>
+        <v>91263</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5964,7 +5964,7 @@
         <v>126360324</v>
       </c>
       <c r="B52" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6070,7 +6070,7 @@
         <v>126360636</v>
       </c>
       <c r="B53" t="n">
-        <v>91238</v>
+        <v>91241</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6173,32 +6173,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126360389</v>
+        <v>126360392</v>
       </c>
       <c r="B54" t="n">
-        <v>91696</v>
+        <v>91541</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6279,32 +6279,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126360392</v>
+        <v>126360389</v>
       </c>
       <c r="B55" t="n">
-        <v>91538</v>
+        <v>91699</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6388,7 +6388,7 @@
         <v>126360330</v>
       </c>
       <c r="B56" t="n">
-        <v>91238</v>
+        <v>91241</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -10387,7 +10387,7 @@
         <v>126361165</v>
       </c>
       <c r="B90" t="n">
-        <v>91256</v>
+        <v>91259</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10489,7 +10489,7 @@
         <v>126361127</v>
       </c>
       <c r="B91" t="n">
-        <v>75063</v>
+        <v>75066</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10591,7 +10591,7 @@
         <v>126361121</v>
       </c>
       <c r="B92" t="n">
-        <v>75077</v>
+        <v>75080</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10693,7 +10693,7 @@
         <v>126361100</v>
       </c>
       <c r="B93" t="n">
-        <v>91260</v>
+        <v>91263</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>

--- a/artfynd/A 8219-2025 artfynd.xlsx
+++ b/artfynd/A 8219-2025 artfynd.xlsx
@@ -3272,10 +3272,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126358035</v>
+        <v>126357916</v>
       </c>
       <c r="B27" t="n">
-        <v>75066</v>
+        <v>92032</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3283,21 +3283,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>492</v>
+        <v>918</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3307,10 +3307,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>560363</v>
+        <v>560301</v>
       </c>
       <c r="R27" t="n">
-        <v>7309388</v>
+        <v>7309435</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3374,7 +3374,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126357916</v>
+        <v>126357490</v>
       </c>
       <c r="B28" t="n">
         <v>92032</v>
@@ -3405,14 +3405,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Jipmomyran, Jipmomyran, Ly lm</t>
+          <t>Järnforsen, Järnforsen, Ly lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>560301</v>
+        <v>560120</v>
       </c>
       <c r="R28" t="n">
-        <v>7309435</v>
+        <v>7309549</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3476,10 +3476,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126357490</v>
+        <v>126358035</v>
       </c>
       <c r="B29" t="n">
-        <v>92032</v>
+        <v>75066</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3487,34 +3487,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>918</v>
+        <v>492</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Järnforsen, Järnforsen, Ly lm</t>
+          <t>Jipmomyran, Jipmomyran, Ly lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>560120</v>
+        <v>560363</v>
       </c>
       <c r="R29" t="n">
-        <v>7309549</v>
+        <v>7309388</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -6173,32 +6173,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126360392</v>
+        <v>126360389</v>
       </c>
       <c r="B54" t="n">
-        <v>91541</v>
+        <v>91699</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6279,32 +6279,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126360389</v>
+        <v>126360392</v>
       </c>
       <c r="B55" t="n">
-        <v>91699</v>
+        <v>91541</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>

--- a/artfynd/A 8219-2025 artfynd.xlsx
+++ b/artfynd/A 8219-2025 artfynd.xlsx
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126355489</v>
+        <v>126355483</v>
       </c>
       <c r="B3" t="n">
-        <v>91541</v>
+        <v>91699</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -874,32 +874,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126355483</v>
+        <v>126355489</v>
       </c>
       <c r="B4" t="n">
-        <v>91699</v>
+        <v>91541</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -976,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126356815</v>
+        <v>126356440</v>
       </c>
       <c r="B5" t="n">
-        <v>91259</v>
+        <v>91541</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,21 +987,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>559785</v>
+        <v>559675</v>
       </c>
       <c r="R5" t="n">
-        <v>7310073</v>
+        <v>7310094</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1078,10 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126356440</v>
+        <v>126356815</v>
       </c>
       <c r="B6" t="n">
-        <v>91541</v>
+        <v>91259</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1089,21 +1089,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>559675</v>
+        <v>559785</v>
       </c>
       <c r="R6" t="n">
-        <v>7310094</v>
+        <v>7310073</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1592,45 +1592,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126355561</v>
+        <v>126355961</v>
       </c>
       <c r="B11" t="n">
-        <v>91605</v>
+        <v>91259</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2063</v>
+        <v>1204</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Järnforsen, Järnforsen, Ly lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>559811</v>
+        <v>559761</v>
       </c>
       <c r="R11" t="n">
-        <v>7309839</v>
+        <v>7309941</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1671,12 +1674,13 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Bördig grannaturskog vid bäckravin</t>
+          <t>Yngre, tidigare avverkad/gallrad skog med många lämnade lågor och naturvärdesträd.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1694,48 +1698,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126355961</v>
+        <v>126355561</v>
       </c>
       <c r="B12" t="n">
-        <v>91259</v>
+        <v>91605</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1204</v>
+        <v>2063</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Järnforsen, Järnforsen, Ly lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>559761</v>
+        <v>559811</v>
       </c>
       <c r="R12" t="n">
-        <v>7309941</v>
+        <v>7309839</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1776,13 +1777,12 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Yngre, tidigare avverkad/gallrad skog med många lämnade lågor och naturvärdesträd.</t>
+          <t>Bördig grannaturskog vid bäckravin</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -3578,7 +3578,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126357506</v>
+        <v>126359216</v>
       </c>
       <c r="B30" t="n">
         <v>91241</v>
@@ -3609,14 +3609,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Järnforsen, Järnforsen, Ly lm</t>
+          <t>Jipmomyran, Jipmomyran, Ly lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>560120</v>
+        <v>560542</v>
       </c>
       <c r="R30" t="n">
-        <v>7309549</v>
+        <v>7309328</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3662,7 +3662,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Frodig, urskogsartade granskog i brant terräng</t>
+          <t>Lövrik grannaturskog</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3680,7 +3680,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126359216</v>
+        <v>126357506</v>
       </c>
       <c r="B31" t="n">
         <v>91241</v>
@@ -3711,14 +3711,14 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Jipmomyran, Jipmomyran, Ly lm</t>
+          <t>Järnforsen, Järnforsen, Ly lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>560542</v>
+        <v>560120</v>
       </c>
       <c r="R31" t="n">
-        <v>7309328</v>
+        <v>7309549</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3764,7 +3764,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Lövrik grannaturskog</t>
+          <t>Frodig, urskogsartade granskog i brant terräng</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -3782,7 +3782,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126357428</v>
+        <v>126358404</v>
       </c>
       <c r="B32" t="n">
         <v>80083</v>
@@ -3813,14 +3813,14 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Järnforsen, Järnforsen, Ly lm</t>
+          <t>Jipmomyran, Jipmomyran, Ly lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>560096</v>
+        <v>560173</v>
       </c>
       <c r="R32" t="n">
-        <v>7309597</v>
+        <v>7309178</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3866,7 +3866,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Frodig gråalskog vid bäckdråg</t>
+          <t>Lövrik grannaturskog</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -3884,7 +3884,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126358404</v>
+        <v>126357428</v>
       </c>
       <c r="B33" t="n">
         <v>80083</v>
@@ -3915,14 +3915,14 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Jipmomyran, Jipmomyran, Ly lm</t>
+          <t>Järnforsen, Järnforsen, Ly lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>560173</v>
+        <v>560096</v>
       </c>
       <c r="R33" t="n">
-        <v>7309178</v>
+        <v>7309597</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3968,7 +3968,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Lövrik grannaturskog</t>
+          <t>Frodig gråalskog vid bäckdråg</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -6173,32 +6173,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126360389</v>
+        <v>126360392</v>
       </c>
       <c r="B54" t="n">
-        <v>91699</v>
+        <v>91541</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6279,32 +6279,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126360392</v>
+        <v>126360389</v>
       </c>
       <c r="B55" t="n">
-        <v>91541</v>
+        <v>91699</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>

--- a/artfynd/A 8219-2025 artfynd.xlsx
+++ b/artfynd/A 8219-2025 artfynd.xlsx
@@ -3272,10 +3272,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126357916</v>
+        <v>126358035</v>
       </c>
       <c r="B27" t="n">
-        <v>92032</v>
+        <v>75066</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3283,21 +3283,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>918</v>
+        <v>492</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3307,10 +3307,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>560301</v>
+        <v>560363</v>
       </c>
       <c r="R27" t="n">
-        <v>7309435</v>
+        <v>7309388</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3374,7 +3374,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126357490</v>
+        <v>126357916</v>
       </c>
       <c r="B28" t="n">
         <v>92032</v>
@@ -3405,14 +3405,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Järnforsen, Järnforsen, Ly lm</t>
+          <t>Jipmomyran, Jipmomyran, Ly lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>560120</v>
+        <v>560301</v>
       </c>
       <c r="R28" t="n">
-        <v>7309549</v>
+        <v>7309435</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3476,10 +3476,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126358035</v>
+        <v>126357490</v>
       </c>
       <c r="B29" t="n">
-        <v>75066</v>
+        <v>92032</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3487,34 +3487,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>492</v>
+        <v>918</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Jipmomyran, Jipmomyran, Ly lm</t>
+          <t>Järnforsen, Järnforsen, Ly lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>560363</v>
+        <v>560120</v>
       </c>
       <c r="R29" t="n">
-        <v>7309388</v>
+        <v>7309549</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>

--- a/artfynd/A 8219-2025 artfynd.xlsx
+++ b/artfynd/A 8219-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY95"/>
+  <dimension ref="A1:AY94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1592,48 +1592,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126355961</v>
+        <v>126355561</v>
       </c>
       <c r="B11" t="n">
-        <v>91259</v>
+        <v>91605</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1204</v>
+        <v>2063</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Järnforsen, Järnforsen, Ly lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>559761</v>
+        <v>559811</v>
       </c>
       <c r="R11" t="n">
-        <v>7309941</v>
+        <v>7309839</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1674,13 +1671,12 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Yngre, tidigare avverkad/gallrad skog med många lämnade lågor och naturvärdesträd.</t>
+          <t>Bördig grannaturskog vid bäckravin</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1698,32 +1694,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126355561</v>
+        <v>126355571</v>
       </c>
       <c r="B12" t="n">
-        <v>91605</v>
+        <v>96614</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2063</v>
+        <v>53</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1733,10 +1729,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>559811</v>
+        <v>559812</v>
       </c>
       <c r="R12" t="n">
-        <v>7309839</v>
+        <v>7309847</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1800,10 +1796,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126355571</v>
+        <v>126356806</v>
       </c>
       <c r="B13" t="n">
-        <v>96614</v>
+        <v>91263</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1811,21 +1807,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>53</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1835,10 +1831,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>559812</v>
+        <v>559785</v>
       </c>
       <c r="R13" t="n">
-        <v>7309847</v>
+        <v>7310073</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1884,7 +1880,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Bördig grannaturskog vid bäckravin</t>
+          <t>Bördig grannaturskog i brant terräng</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -1902,7 +1898,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126356806</v>
+        <v>126355558</v>
       </c>
       <c r="B14" t="n">
         <v>91263</v>
@@ -1937,10 +1933,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>559785</v>
+        <v>559811</v>
       </c>
       <c r="R14" t="n">
-        <v>7310073</v>
+        <v>7309839</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1986,7 +1982,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Bördig grannaturskog i brant terräng</t>
+          <t>Bördig grannaturskog vid bäckravin</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2004,32 +2000,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126355558</v>
+        <v>126356631</v>
       </c>
       <c r="B15" t="n">
-        <v>91263</v>
+        <v>98265</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>220093</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2039,10 +2035,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>559811</v>
+        <v>559746</v>
       </c>
       <c r="R15" t="n">
-        <v>7309839</v>
+        <v>7310122</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2088,7 +2084,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Bördig grannaturskog vid bäckravin</t>
+          <t>Bördig grannaturskog i brant terräng</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2106,32 +2102,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126356631</v>
+        <v>126356490</v>
       </c>
       <c r="B16" t="n">
-        <v>98265</v>
+        <v>91259</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220093</v>
+        <v>1204</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2141,10 +2137,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>559746</v>
+        <v>559674</v>
       </c>
       <c r="R16" t="n">
-        <v>7310122</v>
+        <v>7310125</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2208,10 +2204,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126356490</v>
+        <v>126356501</v>
       </c>
       <c r="B17" t="n">
-        <v>91259</v>
+        <v>91241</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2219,21 +2215,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1204</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2243,7 +2239,7 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>559674</v>
+        <v>559697</v>
       </c>
       <c r="R17" t="n">
         <v>7310125</v>
@@ -2310,7 +2306,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126356501</v>
+        <v>126357389</v>
       </c>
       <c r="B18" t="n">
         <v>91241</v>
@@ -2339,16 +2335,19 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Järnforsen, Järnforsen, Ly lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>559697</v>
+        <v>560081</v>
       </c>
       <c r="R18" t="n">
-        <v>7310125</v>
+        <v>7309611</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2389,6 +2388,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2412,10 +2412,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126357389</v>
+        <v>126359227</v>
       </c>
       <c r="B19" t="n">
-        <v>91241</v>
+        <v>75075</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2423,37 +2423,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Järnforsen, Järnforsen, Ly lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>560081</v>
+        <v>560045</v>
       </c>
       <c r="R19" t="n">
-        <v>7309611</v>
+        <v>7309792</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2494,13 +2491,12 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Bördig grannaturskog i brant terräng</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2518,10 +2514,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126359227</v>
+        <v>126359406</v>
       </c>
       <c r="B20" t="n">
-        <v>75075</v>
+        <v>91263</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2529,21 +2525,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2553,10 +2549,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>560045</v>
+        <v>560158</v>
       </c>
       <c r="R20" t="n">
-        <v>7309792</v>
+        <v>7309726</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2620,7 +2616,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126359406</v>
+        <v>126357387</v>
       </c>
       <c r="B21" t="n">
         <v>91263</v>
@@ -2655,10 +2651,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>560158</v>
+        <v>560081</v>
       </c>
       <c r="R21" t="n">
-        <v>7309726</v>
+        <v>7309611</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2704,7 +2700,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Bördig grannaturskog i brant terräng</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2722,10 +2718,15 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126357387</v>
+        <v>66544349</v>
       </c>
       <c r="B22" t="n">
-        <v>91263</v>
+        <v>89388</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2733,37 +2734,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Järnforsen, Järnforsen, Ly lm</t>
+          <t>Djupfors V, Ly lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>560081</v>
+        <v>560829.2017359853</v>
       </c>
       <c r="R22" t="n">
-        <v>7309611</v>
+        <v>7309021.683959483</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2787,12 +2788,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2014-09-05</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2014-09-05</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2804,30 +2815,30 @@
       <c r="AG22" t="b">
         <v>0</v>
       </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>Bördig grannaturskog i brant terräng</t>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>25090</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Malin Sahlin</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>66544349</v>
+        <v>66544354</v>
       </c>
       <c r="B23" t="n">
-        <v>89388</v>
+        <v>89410</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2840,21 +2851,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2864,10 +2875,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>560829.2017359853</v>
+        <v>560817.2887951054</v>
       </c>
       <c r="R23" t="n">
-        <v>7309021.683959483</v>
+        <v>7309023.475668295</v>
       </c>
       <c r="S23" t="n">
         <v>50</v>
@@ -2923,7 +2934,7 @@
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>25090</t>
+          <t>25094</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -2941,10 +2952,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>66544354</v>
+        <v>119301540</v>
       </c>
       <c r="B24" t="n">
-        <v>89410</v>
+        <v>57257</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2953,41 +2964,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>102620</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Hökuggla</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Surnia ulula</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Djupfors V, Ly lm</t>
+          <t>Järnforsen, Ly lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>560817.2887951054</v>
+        <v>559939</v>
       </c>
       <c r="R24" t="n">
-        <v>7309023.475668295</v>
+        <v>7309726</v>
       </c>
       <c r="S24" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3011,22 +3022,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2014-09-05</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2014-09-05</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3037,74 +3048,64 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AR24" t="inlineStr">
-        <is>
-          <t>25094</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Malin Sahlin</t>
+          <t>Sonata Isaksson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Sonata Isaksson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119301540</v>
+        <v>126359216</v>
       </c>
       <c r="B25" t="n">
-        <v>57257</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91241</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>102620</v>
+        <v>1108</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hökuggla</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Surnia ulula</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Järnforsen, Ly lm</t>
+          <t>Jipmomyran, Jipmomyran, Ly lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>559939</v>
+        <v>560542</v>
       </c>
       <c r="R25" t="n">
-        <v>7309726</v>
+        <v>7309328</v>
       </c>
       <c r="S25" t="n">
-        <v>200</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3128,22 +3129,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>18:58</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>18:58</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3154,26 +3145,31 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Lövrik grannaturskog</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Sonata Isaksson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Sonata Isaksson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126358030</v>
+        <v>126357506</v>
       </c>
       <c r="B26" t="n">
-        <v>80083</v>
+        <v>91241</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3181,34 +3177,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Jipmomyran, Jipmomyran, Ly lm</t>
+          <t>Järnforsen, Järnforsen, Ly lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>560363</v>
+        <v>560120</v>
       </c>
       <c r="R26" t="n">
-        <v>7309388</v>
+        <v>7309549</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3272,32 +3268,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126358035</v>
+        <v>126358404</v>
       </c>
       <c r="B27" t="n">
-        <v>75066</v>
+        <v>80083</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>492</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3307,10 +3303,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>560363</v>
+        <v>560173</v>
       </c>
       <c r="R27" t="n">
-        <v>7309388</v>
+        <v>7309178</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3356,7 +3352,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Frodig, urskogsartade granskog i brant terräng</t>
+          <t>Lövrik grannaturskog</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3374,45 +3370,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126357916</v>
+        <v>126357428</v>
       </c>
       <c r="B28" t="n">
-        <v>92032</v>
+        <v>80083</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>918</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Jipmomyran, Jipmomyran, Ly lm</t>
+          <t>Järnforsen, Järnforsen, Ly lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>560301</v>
+        <v>560096</v>
       </c>
       <c r="R28" t="n">
-        <v>7309435</v>
+        <v>7309597</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3458,7 +3454,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Frodig, urskogsartade granskog i brant terräng</t>
+          <t>Frodig gråalskog vid bäckdråg</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3476,32 +3472,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126357490</v>
+        <v>126357434</v>
       </c>
       <c r="B29" t="n">
-        <v>92032</v>
+        <v>97437</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>918</v>
+        <v>220250</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Matteuccia struthiopteris</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(L.) Tod.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3511,10 +3507,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>560120</v>
+        <v>560096</v>
       </c>
       <c r="R29" t="n">
-        <v>7309549</v>
+        <v>7309597</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3560,7 +3556,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Frodig, urskogsartade granskog i brant terräng</t>
+          <t>Frodig gråalskog vid bäckdråg</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3578,10 +3574,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126359216</v>
+        <v>126358063</v>
       </c>
       <c r="B30" t="n">
-        <v>91241</v>
+        <v>75067</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3589,21 +3585,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1108</v>
+        <v>308</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3613,10 +3609,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>560542</v>
+        <v>560358</v>
       </c>
       <c r="R30" t="n">
-        <v>7309328</v>
+        <v>7309396</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3662,7 +3658,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Lövrik grannaturskog</t>
+          <t>Frodig, urskogsartade granskog i brant terräng</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3680,10 +3676,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126357506</v>
+        <v>126357705</v>
       </c>
       <c r="B31" t="n">
-        <v>91241</v>
+        <v>91263</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3691,34 +3687,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Järnforsen, Järnforsen, Ly lm</t>
+          <t>Jipmomyran, Jipmomyran, Ly lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>560120</v>
+        <v>560260</v>
       </c>
       <c r="R31" t="n">
-        <v>7309549</v>
+        <v>7309464</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3782,10 +3778,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126358404</v>
+        <v>126358410</v>
       </c>
       <c r="B32" t="n">
-        <v>80083</v>
+        <v>80084</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3793,21 +3789,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3884,7 +3880,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126357428</v>
+        <v>126358030</v>
       </c>
       <c r="B33" t="n">
         <v>80083</v>
@@ -3913,16 +3909,19 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Järnforsen, Järnforsen, Ly lm</t>
+          <t>Jipmomyran, Jipmomyran, Ly lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>560096</v>
+        <v>560363</v>
       </c>
       <c r="R33" t="n">
-        <v>7309597</v>
+        <v>7309388</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3963,12 +3962,13 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Frodig gråalskog vid bäckdråg</t>
+          <t>Frodig, urskogsartad granskog i brant terräng</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -3986,45 +3986,48 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126357748</v>
+        <v>126358035</v>
       </c>
       <c r="B34" t="n">
-        <v>80084</v>
+        <v>75066</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2081</v>
+        <v>492</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Jipmomyran, Jipmomyran, Ly lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>560277</v>
+        <v>560363</v>
       </c>
       <c r="R34" t="n">
-        <v>7309435</v>
+        <v>7309388</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4065,12 +4068,13 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>Frodig, urskogsartade granskog i brant terräng</t>
+          <t>Frodig, urskogsartad granskog i brant terräng</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4088,45 +4092,48 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126357718</v>
+        <v>126357490</v>
       </c>
       <c r="B35" t="n">
-        <v>91241</v>
+        <v>92032</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1108</v>
+        <v>918</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Jipmomyran, Jipmomyran, Ly lm</t>
+          <t>Järnforsen, Järnforsen, Ly lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>560264</v>
+        <v>560120</v>
       </c>
       <c r="R35" t="n">
-        <v>7309462</v>
+        <v>7309549</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4167,12 +4174,13 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>Frodig, urskogsartade granskog i brant terräng</t>
+          <t>Frodig, urskogsartad granskog i brant terräng</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4190,45 +4198,48 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126357434</v>
+        <v>126357916</v>
       </c>
       <c r="B36" t="n">
-        <v>97437</v>
+        <v>92032</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220250</v>
+        <v>918</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Järnforsen, Järnforsen, Ly lm</t>
+          <t>Jipmomyran, Jipmomyran, Ly lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>560096</v>
+        <v>560301</v>
       </c>
       <c r="R36" t="n">
-        <v>7309597</v>
+        <v>7309435</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4269,12 +4280,13 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>Frodig gråalskog vid bäckdråg</t>
+          <t>Frodig, urskogsartad granskog i brant terräng</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4292,10 +4304,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126358063</v>
+        <v>126357748</v>
       </c>
       <c r="B37" t="n">
-        <v>75067</v>
+        <v>80084</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4303,34 +4315,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>308</v>
+        <v>2081</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Jipmomyran, Jipmomyran, Ly lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>560358</v>
+        <v>560277</v>
       </c>
       <c r="R37" t="n">
-        <v>7309396</v>
+        <v>7309435</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4371,12 +4386,13 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Frodig, urskogsartade granskog i brant terräng</t>
+          <t>Frodig, urskogsartad granskog i brant terräng</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4394,10 +4410,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126357705</v>
+        <v>126357718</v>
       </c>
       <c r="B38" t="n">
-        <v>91263</v>
+        <v>91241</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4405,34 +4421,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Jipmomyran, Jipmomyran, Ly lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>560260</v>
+        <v>560264</v>
       </c>
       <c r="R38" t="n">
-        <v>7309464</v>
+        <v>7309462</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4473,12 +4492,13 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>Frodig, urskogsartade granskog i brant terräng</t>
+          <t>Frodig, urskogsartad granskog i brant terräng</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -4525,6 +4545,9 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Jipmomyran, Jipmomyran, Ly lm</t>
@@ -4575,12 +4598,13 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>Frodig, urskogsartade granskog i brant terräng</t>
+          <t>Frodig, urskogsartad granskog i brant terräng</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -4627,6 +4651,9 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Jipmomyran, Jipmomyran, Ly lm</t>
@@ -4677,12 +4704,13 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>Frodig, urskogsartade granskog i brant terräng</t>
+          <t>Frodig, urskogsartad granskog i brant terräng</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -4700,10 +4728,15 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126358410</v>
+        <v>66544347</v>
       </c>
       <c r="B41" t="n">
-        <v>80084</v>
+        <v>89392</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4711,37 +4744,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Jipmomyran, Jipmomyran, Ly lm</t>
+          <t>Djupfors V, Ly lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>560173</v>
+        <v>560878.5341145619</v>
       </c>
       <c r="R41" t="n">
-        <v>7309178</v>
+        <v>7308993.284323963</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4765,12 +4798,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2014-09-05</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2014-09-05</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4782,27 +4825,27 @@
       <c r="AG41" t="b">
         <v>0</v>
       </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>Lövrik grannaturskog</t>
+      <c r="AR41" t="inlineStr">
+        <is>
+          <t>25088</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Malin Sahlin</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>66544347</v>
+        <v>66544345</v>
       </c>
       <c r="B42" t="n">
         <v>89392</v>
@@ -4842,10 +4885,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>560878.5341145619</v>
+        <v>560921.9021753618</v>
       </c>
       <c r="R42" t="n">
-        <v>7308993.284323963</v>
+        <v>7308956.577612261</v>
       </c>
       <c r="S42" t="n">
         <v>50</v>
@@ -4901,7 +4944,7 @@
       </c>
       <c r="AR42" t="inlineStr">
         <is>
-          <t>25088</t>
+          <t>25086</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -4919,10 +4962,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>66544345</v>
+        <v>66544351</v>
       </c>
       <c r="B43" t="n">
-        <v>89392</v>
+        <v>89673</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4935,21 +4978,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4959,10 +5002,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>560921.9021753618</v>
+        <v>560857.1901938798</v>
       </c>
       <c r="R43" t="n">
-        <v>7308956.577612261</v>
+        <v>7309014.91711883</v>
       </c>
       <c r="S43" t="n">
         <v>50</v>
@@ -5018,7 +5061,7 @@
       </c>
       <c r="AR43" t="inlineStr">
         <is>
-          <t>25086</t>
+          <t>25092</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5036,10 +5079,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>66544351</v>
+        <v>66544353</v>
       </c>
       <c r="B44" t="n">
-        <v>89673</v>
+        <v>89356</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5048,25 +5091,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5135,7 +5178,7 @@
       </c>
       <c r="AR44" t="inlineStr">
         <is>
-          <t>25092</t>
+          <t>25093</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5153,10 +5196,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>66544353</v>
+        <v>66544343</v>
       </c>
       <c r="B45" t="n">
-        <v>89356</v>
+        <v>89392</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5165,25 +5208,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5193,10 +5236,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>560857.1901938798</v>
+        <v>560933.9809844483</v>
       </c>
       <c r="R45" t="n">
-        <v>7309014.91711883</v>
+        <v>7308947.018279012</v>
       </c>
       <c r="S45" t="n">
         <v>50</v>
@@ -5252,7 +5295,7 @@
       </c>
       <c r="AR45" t="inlineStr">
         <is>
-          <t>25093</t>
+          <t>25084</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -5270,10 +5313,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>66544343</v>
+        <v>66544348</v>
       </c>
       <c r="B46" t="n">
-        <v>89392</v>
+        <v>89388</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5286,21 +5329,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5310,10 +5353,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>560933.9809844483</v>
+        <v>560863.3901593408</v>
       </c>
       <c r="R46" t="n">
-        <v>7308947.018279012</v>
+        <v>7308992.96197705</v>
       </c>
       <c r="S46" t="n">
         <v>50</v>
@@ -5369,7 +5412,7 @@
       </c>
       <c r="AR46" t="inlineStr">
         <is>
-          <t>25084</t>
+          <t>25089</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5387,10 +5430,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>66544348</v>
+        <v>66544344</v>
       </c>
       <c r="B47" t="n">
-        <v>89388</v>
+        <v>89780</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5399,25 +5442,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1108</v>
+        <v>4217</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5427,10 +5470,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>560863.3901593408</v>
+        <v>560933.9809844483</v>
       </c>
       <c r="R47" t="n">
-        <v>7308992.96197705</v>
+        <v>7308947.018279012</v>
       </c>
       <c r="S47" t="n">
         <v>50</v>
@@ -5486,7 +5529,7 @@
       </c>
       <c r="AR47" t="inlineStr">
         <is>
-          <t>25089</t>
+          <t>25085</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -5504,10 +5547,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>66544344</v>
+        <v>66544346</v>
       </c>
       <c r="B48" t="n">
-        <v>89780</v>
+        <v>77506</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5516,25 +5559,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4217</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5544,10 +5587,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>560933.9809844483</v>
+        <v>560921.9021753618</v>
       </c>
       <c r="R48" t="n">
-        <v>7308947.018279012</v>
+        <v>7308956.577612261</v>
       </c>
       <c r="S48" t="n">
         <v>50</v>
@@ -5603,7 +5646,7 @@
       </c>
       <c r="AR48" t="inlineStr">
         <is>
-          <t>25085</t>
+          <t>25087</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -5621,10 +5664,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>66544346</v>
+        <v>66544350</v>
       </c>
       <c r="B49" t="n">
-        <v>77506</v>
+        <v>89392</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5637,21 +5680,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5661,10 +5704,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>560921.9021753618</v>
+        <v>560857.1901938798</v>
       </c>
       <c r="R49" t="n">
-        <v>7308956.577612261</v>
+        <v>7309014.91711883</v>
       </c>
       <c r="S49" t="n">
         <v>50</v>
@@ -5720,7 +5763,7 @@
       </c>
       <c r="AR49" t="inlineStr">
         <is>
-          <t>25087</t>
+          <t>25091</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -5738,15 +5781,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>66544350</v>
+        <v>126360335</v>
       </c>
       <c r="B50" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91263</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5754,37 +5792,40 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Djupfors V, Ly lm</t>
+          <t>Jipmomyran, Jipmomyran, Ly lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>560857.1901938798</v>
+        <v>560893</v>
       </c>
       <c r="R50" t="n">
-        <v>7309014.91711883</v>
+        <v>7308996</v>
       </c>
       <c r="S50" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5808,22 +5849,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2014-09-05</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2014-09-05</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5832,33 +5863,34 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
-      <c r="AR50" t="inlineStr">
-        <is>
-          <t>25091</t>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>Grannaturskog/gransumpskog</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Malin Sahlin</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126360335</v>
+        <v>126360324</v>
       </c>
       <c r="B51" t="n">
-        <v>91263</v>
+        <v>91245</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5866,21 +5898,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5961,10 +5993,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126360324</v>
+        <v>126360636</v>
       </c>
       <c r="B52" t="n">
-        <v>91245</v>
+        <v>91241</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5972,21 +6004,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5999,10 +6031,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>560893</v>
+        <v>560870</v>
       </c>
       <c r="R52" t="n">
-        <v>7308996</v>
+        <v>7309007</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6067,10 +6099,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126360636</v>
+        <v>126360392</v>
       </c>
       <c r="B53" t="n">
-        <v>91241</v>
+        <v>91541</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6078,21 +6110,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1108</v>
+        <v>658</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6173,32 +6205,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126360392</v>
+        <v>126360389</v>
       </c>
       <c r="B54" t="n">
-        <v>91541</v>
+        <v>91699</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6279,32 +6311,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126360389</v>
+        <v>126360330</v>
       </c>
       <c r="B55" t="n">
-        <v>91699</v>
+        <v>91241</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1209</v>
+        <v>1108</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6317,10 +6349,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>560870</v>
+        <v>560893</v>
       </c>
       <c r="R55" t="n">
-        <v>7309007</v>
+        <v>7308996</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6385,51 +6417,53 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126360330</v>
+        <v>66544342</v>
       </c>
       <c r="B56" t="n">
-        <v>91241</v>
+        <v>90074</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Jipmomyran, Jipmomyran, Ly lm</t>
+          <t>Djupfors V, Ly lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>560893</v>
+        <v>560960.3945341655</v>
       </c>
       <c r="R56" t="n">
-        <v>7308996</v>
+        <v>7308918.130968786</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6453,12 +6487,22 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2014-09-05</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2014-09-05</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6467,34 +6511,33 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
-      <c r="AI56" t="inlineStr">
-        <is>
-          <t>Grannaturskog/gransumpskog</t>
+      <c r="AR56" t="inlineStr">
+        <is>
+          <t>25083</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Malin Sahlin</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>66544342</v>
+        <v>66544630</v>
       </c>
       <c r="B57" t="n">
-        <v>90074</v>
+        <v>89388</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6503,25 +6546,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6531,10 +6574,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>560960.3945341655</v>
+        <v>561061.5146522231</v>
       </c>
       <c r="R57" t="n">
-        <v>7308918.130968786</v>
+        <v>7308842.570840668</v>
       </c>
       <c r="S57" t="n">
         <v>50</v>
@@ -6590,7 +6633,7 @@
       </c>
       <c r="AR57" t="inlineStr">
         <is>
-          <t>25083</t>
+          <t>25353</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -6601,17 +6644,17 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Via Malin Sahlin</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>66544630</v>
+        <v>66544637</v>
       </c>
       <c r="B58" t="n">
-        <v>89388</v>
+        <v>89410</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6624,21 +6667,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6648,10 +6691,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>561061.5146522231</v>
+        <v>561099.626093693</v>
       </c>
       <c r="R58" t="n">
-        <v>7308842.570840668</v>
+        <v>7308822.114403572</v>
       </c>
       <c r="S58" t="n">
         <v>50</v>
@@ -6707,7 +6750,7 @@
       </c>
       <c r="AR58" t="inlineStr">
         <is>
-          <t>25353</t>
+          <t>25360</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -6725,10 +6768,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>66544637</v>
+        <v>66544633</v>
       </c>
       <c r="B59" t="n">
-        <v>89410</v>
+        <v>90160</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6737,25 +6780,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5432</v>
+        <v>918</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6765,10 +6808,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>561099.626093693</v>
+        <v>561072.4974219487</v>
       </c>
       <c r="R59" t="n">
-        <v>7308822.114403572</v>
+        <v>7308826.852570722</v>
       </c>
       <c r="S59" t="n">
         <v>50</v>
@@ -6824,7 +6867,7 @@
       </c>
       <c r="AR59" t="inlineStr">
         <is>
-          <t>25360</t>
+          <t>25356</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -6842,10 +6885,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>66544633</v>
+        <v>66544627</v>
       </c>
       <c r="B60" t="n">
-        <v>90160</v>
+        <v>89392</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6854,25 +6897,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>918</v>
+        <v>1202</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6882,10 +6925,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>561072.4974219487</v>
+        <v>561044.5755368763</v>
       </c>
       <c r="R60" t="n">
-        <v>7308826.852570722</v>
+        <v>7308849.572017924</v>
       </c>
       <c r="S60" t="n">
         <v>50</v>
@@ -6941,7 +6984,7 @@
       </c>
       <c r="AR60" t="inlineStr">
         <is>
-          <t>25356</t>
+          <t>25350</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -6959,10 +7002,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>66544627</v>
+        <v>66544641</v>
       </c>
       <c r="B61" t="n">
-        <v>89392</v>
+        <v>89832</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6971,25 +7014,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6999,10 +7042,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>561044.5755368763</v>
+        <v>561099.626093693</v>
       </c>
       <c r="R61" t="n">
-        <v>7308849.572017924</v>
+        <v>7308822.114403572</v>
       </c>
       <c r="S61" t="n">
         <v>50</v>
@@ -7058,7 +7101,7 @@
       </c>
       <c r="AR61" t="inlineStr">
         <is>
-          <t>25350</t>
+          <t>25364</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7076,10 +7119,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>66544641</v>
+        <v>66544639</v>
       </c>
       <c r="B62" t="n">
-        <v>89832</v>
+        <v>77506</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7088,28 +7131,32 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Djupfors V, Ly lm</t>
@@ -7175,7 +7222,7 @@
       </c>
       <c r="AR62" t="inlineStr">
         <is>
-          <t>25364</t>
+          <t>25362</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -7193,10 +7240,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>66544639</v>
+        <v>66544619</v>
       </c>
       <c r="B63" t="n">
-        <v>77506</v>
+        <v>81236</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7209,38 +7256,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Djupfors V, Ly lm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>561099.626093693</v>
+        <v>561027.2184662716</v>
       </c>
       <c r="R63" t="n">
-        <v>7308822.114403572</v>
+        <v>7308856.973397947</v>
       </c>
       <c r="S63" t="n">
         <v>50</v>
@@ -7296,7 +7339,7 @@
       </c>
       <c r="AR63" t="inlineStr">
         <is>
-          <t>25362</t>
+          <t>25343</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -7314,10 +7357,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>66544619</v>
+        <v>66544626</v>
       </c>
       <c r="B64" t="n">
-        <v>81236</v>
+        <v>77506</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7330,34 +7373,38 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Djupfors V, Ly lm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>561027.2184662716</v>
+        <v>561044.5755368763</v>
       </c>
       <c r="R64" t="n">
-        <v>7308856.973397947</v>
+        <v>7308849.572017924</v>
       </c>
       <c r="S64" t="n">
         <v>50</v>
@@ -7413,7 +7460,7 @@
       </c>
       <c r="AR64" t="inlineStr">
         <is>
-          <t>25343</t>
+          <t>25349</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -7431,10 +7478,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>66544626</v>
+        <v>66544638</v>
       </c>
       <c r="B65" t="n">
-        <v>77506</v>
+        <v>89673</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7447,38 +7494,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Djupfors V, Ly lm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>561044.5755368763</v>
+        <v>561099.626093693</v>
       </c>
       <c r="R65" t="n">
-        <v>7308849.572017924</v>
+        <v>7308822.114403572</v>
       </c>
       <c r="S65" t="n">
         <v>50</v>
@@ -7534,7 +7577,7 @@
       </c>
       <c r="AR65" t="inlineStr">
         <is>
-          <t>25349</t>
+          <t>25361</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -7552,10 +7595,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>66544638</v>
+        <v>66544620</v>
       </c>
       <c r="B66" t="n">
-        <v>89673</v>
+        <v>89410</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7568,21 +7611,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7592,10 +7635,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>561099.626093693</v>
+        <v>561027.2184662716</v>
       </c>
       <c r="R66" t="n">
-        <v>7308822.114403572</v>
+        <v>7308856.973397947</v>
       </c>
       <c r="S66" t="n">
         <v>50</v>
@@ -7651,7 +7694,7 @@
       </c>
       <c r="AR66" t="inlineStr">
         <is>
-          <t>25361</t>
+          <t>25344</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -7669,10 +7712,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>66544620</v>
+        <v>66544640</v>
       </c>
       <c r="B67" t="n">
-        <v>89410</v>
+        <v>89392</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7685,21 +7728,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7709,10 +7752,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>561027.2184662716</v>
+        <v>561099.626093693</v>
       </c>
       <c r="R67" t="n">
-        <v>7308856.973397947</v>
+        <v>7308822.114403572</v>
       </c>
       <c r="S67" t="n">
         <v>50</v>
@@ -7768,7 +7811,7 @@
       </c>
       <c r="AR67" t="inlineStr">
         <is>
-          <t>25344</t>
+          <t>25363</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -7786,10 +7829,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>66544640</v>
+        <v>66544649</v>
       </c>
       <c r="B68" t="n">
-        <v>89392</v>
+        <v>81236</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7802,21 +7845,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7826,10 +7869,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>561099.626093693</v>
+        <v>561139.9464785276</v>
       </c>
       <c r="R68" t="n">
-        <v>7308822.114403572</v>
+        <v>7308736.66569937</v>
       </c>
       <c r="S68" t="n">
         <v>50</v>
@@ -7885,7 +7928,7 @@
       </c>
       <c r="AR68" t="inlineStr">
         <is>
-          <t>25363</t>
+          <t>25372</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -7903,10 +7946,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>66544649</v>
+        <v>66544642</v>
       </c>
       <c r="B69" t="n">
-        <v>81236</v>
+        <v>89410</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7919,21 +7962,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7943,10 +7986,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>561139.9464785276</v>
+        <v>561096.8231878708</v>
       </c>
       <c r="R69" t="n">
-        <v>7308736.66569937</v>
+        <v>7308799.96586439</v>
       </c>
       <c r="S69" t="n">
         <v>50</v>
@@ -8002,7 +8045,7 @@
       </c>
       <c r="AR69" t="inlineStr">
         <is>
-          <t>25372</t>
+          <t>25365</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8020,10 +8063,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>66544642</v>
+        <v>66544623</v>
       </c>
       <c r="B70" t="n">
-        <v>89410</v>
+        <v>89673</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8036,34 +8079,38 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Djupfors V, Ly lm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>561096.8231878708</v>
+        <v>561044.5755368763</v>
       </c>
       <c r="R70" t="n">
-        <v>7308799.96586439</v>
+        <v>7308849.572017924</v>
       </c>
       <c r="S70" t="n">
         <v>50</v>
@@ -8119,7 +8166,7 @@
       </c>
       <c r="AR70" t="inlineStr">
         <is>
-          <t>25365</t>
+          <t>25347</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -8137,10 +8184,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>66544623</v>
+        <v>66544341</v>
       </c>
       <c r="B71" t="n">
-        <v>89673</v>
+        <v>77506</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8153,38 +8200,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Djupfors V, Ly lm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>561044.5755368763</v>
+        <v>561008.5625325058</v>
       </c>
       <c r="R71" t="n">
-        <v>7308849.572017924</v>
+        <v>7308906.069035768</v>
       </c>
       <c r="S71" t="n">
         <v>50</v>
@@ -8240,7 +8283,7 @@
       </c>
       <c r="AR71" t="inlineStr">
         <is>
-          <t>25347</t>
+          <t>25082</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -8251,14 +8294,14 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Via Malin Sahlin</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>66544341</v>
+        <v>66544622</v>
       </c>
       <c r="B72" t="n">
         <v>77506</v>
@@ -8291,17 +8334,21 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr"/>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Djupfors V, Ly lm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>561008.5625325058</v>
+        <v>561027.2184662716</v>
       </c>
       <c r="R72" t="n">
-        <v>7308906.069035768</v>
+        <v>7308856.973397947</v>
       </c>
       <c r="S72" t="n">
         <v>50</v>
@@ -8357,7 +8404,7 @@
       </c>
       <c r="AR72" t="inlineStr">
         <is>
-          <t>25082</t>
+          <t>25346</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -8368,17 +8415,17 @@
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Via Malin Sahlin</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>66544622</v>
+        <v>66544651</v>
       </c>
       <c r="B73" t="n">
-        <v>77506</v>
+        <v>89673</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8391,38 +8438,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Djupfors V, Ly lm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>561027.2184662716</v>
+        <v>561139.9464785276</v>
       </c>
       <c r="R73" t="n">
-        <v>7308856.973397947</v>
+        <v>7308736.66569937</v>
       </c>
       <c r="S73" t="n">
         <v>50</v>
@@ -8478,7 +8521,7 @@
       </c>
       <c r="AR73" t="inlineStr">
         <is>
-          <t>25346</t>
+          <t>25373</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -8496,10 +8539,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>66544651</v>
+        <v>66544631</v>
       </c>
       <c r="B74" t="n">
-        <v>89673</v>
+        <v>77506</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8512,34 +8555,38 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Djupfors V, Ly lm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>561139.9464785276</v>
+        <v>561061.5146522231</v>
       </c>
       <c r="R74" t="n">
-        <v>7308736.66569937</v>
+        <v>7308842.570840668</v>
       </c>
       <c r="S74" t="n">
         <v>50</v>
@@ -8595,7 +8642,7 @@
       </c>
       <c r="AR74" t="inlineStr">
         <is>
-          <t>25373</t>
+          <t>25354</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -8613,10 +8660,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>66544631</v>
+        <v>66544621</v>
       </c>
       <c r="B75" t="n">
-        <v>77506</v>
+        <v>56395</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8629,38 +8676,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Djupfors V, Ly lm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>561061.5146522231</v>
+        <v>561027.2184662716</v>
       </c>
       <c r="R75" t="n">
-        <v>7308842.570840668</v>
+        <v>7308856.973397947</v>
       </c>
       <c r="S75" t="n">
         <v>50</v>
@@ -8716,7 +8759,7 @@
       </c>
       <c r="AR75" t="inlineStr">
         <is>
-          <t>25354</t>
+          <t>25345</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -8734,10 +8777,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>66544621</v>
+        <v>66544647</v>
       </c>
       <c r="B76" t="n">
-        <v>56395</v>
+        <v>77506</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8750,34 +8793,38 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Djupfors V, Ly lm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>561027.2184662716</v>
+        <v>561118.808368561</v>
       </c>
       <c r="R76" t="n">
-        <v>7308856.973397947</v>
+        <v>7308748.485677995</v>
       </c>
       <c r="S76" t="n">
         <v>50</v>
@@ -8833,7 +8880,7 @@
       </c>
       <c r="AR76" t="inlineStr">
         <is>
-          <t>25345</t>
+          <t>25370</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -8851,7 +8898,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>66544647</v>
+        <v>66544635</v>
       </c>
       <c r="B77" t="n">
         <v>77506</v>
@@ -8895,10 +8942,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>561118.808368561</v>
+        <v>561072.4974219487</v>
       </c>
       <c r="R77" t="n">
-        <v>7308748.485677995</v>
+        <v>7308826.852570722</v>
       </c>
       <c r="S77" t="n">
         <v>50</v>
@@ -8954,7 +9001,7 @@
       </c>
       <c r="AR77" t="inlineStr">
         <is>
-          <t>25370</t>
+          <t>25358</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -8972,10 +9019,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>66544635</v>
+        <v>66544648</v>
       </c>
       <c r="B78" t="n">
-        <v>77506</v>
+        <v>85703</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8988,38 +9035,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Djupfors V, Ly lm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>561072.4974219487</v>
+        <v>561139.9464785276</v>
       </c>
       <c r="R78" t="n">
-        <v>7308826.852570722</v>
+        <v>7308736.66569937</v>
       </c>
       <c r="S78" t="n">
         <v>50</v>
@@ -9075,7 +9118,7 @@
       </c>
       <c r="AR78" t="inlineStr">
         <is>
-          <t>25358</t>
+          <t>25371</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -9093,10 +9136,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>66544648</v>
+        <v>66544628</v>
       </c>
       <c r="B79" t="n">
-        <v>85703</v>
+        <v>89388</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9109,21 +9152,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>510</v>
+        <v>1108</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9133,10 +9176,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>561139.9464785276</v>
+        <v>561044.5755368763</v>
       </c>
       <c r="R79" t="n">
-        <v>7308736.66569937</v>
+        <v>7308849.572017924</v>
       </c>
       <c r="S79" t="n">
         <v>50</v>
@@ -9192,7 +9235,7 @@
       </c>
       <c r="AR79" t="inlineStr">
         <is>
-          <t>25371</t>
+          <t>25351</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -9210,10 +9253,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>66544628</v>
+        <v>66544645</v>
       </c>
       <c r="B80" t="n">
-        <v>89388</v>
+        <v>89673</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9226,21 +9269,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1108</v>
+        <v>658</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9250,10 +9293,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>561044.5755368763</v>
+        <v>561118.808368561</v>
       </c>
       <c r="R80" t="n">
-        <v>7308849.572017924</v>
+        <v>7308748.485677995</v>
       </c>
       <c r="S80" t="n">
         <v>50</v>
@@ -9309,7 +9352,7 @@
       </c>
       <c r="AR80" t="inlineStr">
         <is>
-          <t>25351</t>
+          <t>25368</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -9327,10 +9370,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>66544645</v>
+        <v>66544636</v>
       </c>
       <c r="B81" t="n">
-        <v>89673</v>
+        <v>81236</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9343,21 +9386,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9367,10 +9410,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>561118.808368561</v>
+        <v>561072.4974219487</v>
       </c>
       <c r="R81" t="n">
-        <v>7308748.485677995</v>
+        <v>7308826.852570722</v>
       </c>
       <c r="S81" t="n">
         <v>50</v>
@@ -9426,7 +9469,7 @@
       </c>
       <c r="AR81" t="inlineStr">
         <is>
-          <t>25368</t>
+          <t>25359</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -9444,10 +9487,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>66544636</v>
+        <v>66544634</v>
       </c>
       <c r="B82" t="n">
-        <v>81236</v>
+        <v>89356</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9456,25 +9499,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9543,7 +9586,7 @@
       </c>
       <c r="AR82" t="inlineStr">
         <is>
-          <t>25359</t>
+          <t>25357</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -9561,10 +9604,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>66544634</v>
+        <v>66544646</v>
       </c>
       <c r="B83" t="n">
-        <v>89356</v>
+        <v>89392</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9573,25 +9616,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9601,10 +9644,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>561072.4974219487</v>
+        <v>561118.808368561</v>
       </c>
       <c r="R83" t="n">
-        <v>7308826.852570722</v>
+        <v>7308748.485677995</v>
       </c>
       <c r="S83" t="n">
         <v>50</v>
@@ -9660,7 +9703,7 @@
       </c>
       <c r="AR83" t="inlineStr">
         <is>
-          <t>25357</t>
+          <t>25369</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -9678,10 +9721,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>66544646</v>
+        <v>66544632</v>
       </c>
       <c r="B84" t="n">
-        <v>89392</v>
+        <v>81236</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9694,21 +9737,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9718,10 +9761,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>561118.808368561</v>
+        <v>561061.5146522231</v>
       </c>
       <c r="R84" t="n">
-        <v>7308748.485677995</v>
+        <v>7308842.570840668</v>
       </c>
       <c r="S84" t="n">
         <v>50</v>
@@ -9777,7 +9820,7 @@
       </c>
       <c r="AR84" t="inlineStr">
         <is>
-          <t>25369</t>
+          <t>25355</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -9795,10 +9838,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>66544632</v>
+        <v>66544625</v>
       </c>
       <c r="B85" t="n">
-        <v>81236</v>
+        <v>56395</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9811,21 +9854,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9835,10 +9878,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>561061.5146522231</v>
+        <v>561044.5755368763</v>
       </c>
       <c r="R85" t="n">
-        <v>7308842.570840668</v>
+        <v>7308849.572017924</v>
       </c>
       <c r="S85" t="n">
         <v>50</v>
@@ -9894,7 +9937,7 @@
       </c>
       <c r="AR85" t="inlineStr">
         <is>
-          <t>25355</t>
+          <t>25348</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -9912,10 +9955,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>66544625</v>
+        <v>66544643</v>
       </c>
       <c r="B86" t="n">
-        <v>56395</v>
+        <v>77506</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9928,34 +9971,38 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Djupfors V, Ly lm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>561044.5755368763</v>
+        <v>561108.4689856211</v>
       </c>
       <c r="R86" t="n">
-        <v>7308849.572017924</v>
+        <v>7308772.399080777</v>
       </c>
       <c r="S86" t="n">
         <v>50</v>
@@ -10011,7 +10058,7 @@
       </c>
       <c r="AR86" t="inlineStr">
         <is>
-          <t>25348</t>
+          <t>25366</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -10029,10 +10076,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>66544643</v>
+        <v>66544644</v>
       </c>
       <c r="B87" t="n">
-        <v>77506</v>
+        <v>81236</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10045,28 +10092,24 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Djupfors V, Ly lm</t>
@@ -10132,7 +10175,7 @@
       </c>
       <c r="AR87" t="inlineStr">
         <is>
-          <t>25366</t>
+          <t>25367</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -10150,10 +10193,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>66544644</v>
+        <v>66544629</v>
       </c>
       <c r="B88" t="n">
-        <v>81236</v>
+        <v>89406</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10166,21 +10209,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10190,10 +10233,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>561108.4689856211</v>
+        <v>561061.5146522231</v>
       </c>
       <c r="R88" t="n">
-        <v>7308772.399080777</v>
+        <v>7308842.570840668</v>
       </c>
       <c r="S88" t="n">
         <v>50</v>
@@ -10249,7 +10292,7 @@
       </c>
       <c r="AR88" t="inlineStr">
         <is>
-          <t>25367</t>
+          <t>25352</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -10267,15 +10310,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>66544629</v>
+        <v>126361165</v>
       </c>
       <c r="B89" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91259</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10303,17 +10341,17 @@
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Djupfors V, Ly lm</t>
+          <t>Djupselet, Djupselet, Ly lm</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>561061.5146522231</v>
+        <v>561436</v>
       </c>
       <c r="R89" t="n">
-        <v>7308842.570840668</v>
+        <v>7308968</v>
       </c>
       <c r="S89" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10337,22 +10375,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2014-09-05</t>
-        </is>
-      </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2014-09-05</t>
-        </is>
-      </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10364,52 +10392,52 @@
       <c r="AG89" t="b">
         <v>0</v>
       </c>
-      <c r="AR89" t="inlineStr">
-        <is>
-          <t>25352</t>
+      <c r="AI89" t="inlineStr">
+        <is>
+          <t>Bördig, grovvuxen grannaturskog</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Malin Sahlin</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Via Malin Sahlin</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126361165</v>
+        <v>126361127</v>
       </c>
       <c r="B90" t="n">
-        <v>91259</v>
+        <v>75066</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1204</v>
+        <v>492</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10419,10 +10447,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>561436</v>
+        <v>561403</v>
       </c>
       <c r="R90" t="n">
-        <v>7308968</v>
+        <v>7308978</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10486,32 +10514,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126361127</v>
+        <v>126361121</v>
       </c>
       <c r="B91" t="n">
-        <v>75066</v>
+        <v>75080</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>492</v>
+        <v>1467</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10588,10 +10616,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126361121</v>
+        <v>126361100</v>
       </c>
       <c r="B92" t="n">
-        <v>75080</v>
+        <v>91263</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10599,21 +10627,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1467</v>
+        <v>5432</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10623,10 +10651,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>561403</v>
+        <v>561396</v>
       </c>
       <c r="R92" t="n">
-        <v>7308978</v>
+        <v>7308982</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10690,10 +10718,15 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126361100</v>
+        <v>66544653</v>
       </c>
       <c r="B93" t="n">
-        <v>91263</v>
+        <v>89388</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10701,37 +10734,37 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Djupselet, Djupselet, Ly lm</t>
+          <t>Djupfors V, Ly lm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>561396</v>
+        <v>561132.2069487682</v>
       </c>
       <c r="R93" t="n">
-        <v>7308982</v>
+        <v>7308696.41208922</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10755,12 +10788,22 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2014-09-05</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2014-09-05</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10772,30 +10815,30 @@
       <c r="AG93" t="b">
         <v>0</v>
       </c>
-      <c r="AI93" t="inlineStr">
-        <is>
-          <t>Bördig, grovvuxen grannaturskog</t>
+      <c r="AR93" t="inlineStr">
+        <is>
+          <t>25375</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Malin Sahlin</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Via Malin Sahlin</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>66544653</v>
+        <v>66544652</v>
       </c>
       <c r="B94" t="n">
-        <v>89388</v>
+        <v>81236</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10808,21 +10851,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1108</v>
+        <v>1312</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10891,7 +10934,7 @@
       </c>
       <c r="AR94" t="inlineStr">
         <is>
-          <t>25375</t>
+          <t>25374</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -10906,123 +10949,6 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" t="n">
-        <v>66544652</v>
-      </c>
-      <c r="B95" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E95" t="n">
-        <v>1312</v>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>Gammelgransskål</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>Pseudographis pinicola</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
-      <c r="P95" t="inlineStr">
-        <is>
-          <t>Djupfors V, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q95" t="n">
-        <v>561132.2069487682</v>
-      </c>
-      <c r="R95" t="n">
-        <v>7308696.41208922</v>
-      </c>
-      <c r="S95" t="n">
-        <v>50</v>
-      </c>
-      <c r="T95" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U95" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="V95" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W95" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="Y95" t="inlineStr">
-        <is>
-          <t>2014-09-05</t>
-        </is>
-      </c>
-      <c r="Z95" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA95" t="inlineStr">
-        <is>
-          <t>2014-09-05</t>
-        </is>
-      </c>
-      <c r="AB95" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD95" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE95" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG95" t="b">
-        <v>0</v>
-      </c>
-      <c r="AR95" t="inlineStr">
-        <is>
-          <t>25374</t>
-        </is>
-      </c>
-      <c r="AT95" t="inlineStr"/>
-      <c r="AW95" t="inlineStr">
-        <is>
-          <t>Malin Sahlin</t>
-        </is>
-      </c>
-      <c r="AX95" t="inlineStr">
-        <is>
-          <t>Via Malin Sahlin</t>
-        </is>
-      </c>
-      <c r="AY95" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 8219-2025 artfynd.xlsx
+++ b/artfynd/A 8219-2025 artfynd.xlsx
@@ -3986,10 +3986,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126358035</v>
+        <v>126357916</v>
       </c>
       <c r="B34" t="n">
-        <v>75066</v>
+        <v>92032</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3997,21 +3997,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>492</v>
+        <v>918</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4024,10 +4024,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>560363</v>
+        <v>560301</v>
       </c>
       <c r="R34" t="n">
-        <v>7309388</v>
+        <v>7309435</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4092,10 +4092,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126357490</v>
+        <v>126358035</v>
       </c>
       <c r="B35" t="n">
-        <v>92032</v>
+        <v>75066</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4103,21 +4103,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>918</v>
+        <v>492</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4126,14 +4126,14 @@
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Järnforsen, Järnforsen, Ly lm</t>
+          <t>Jipmomyran, Jipmomyran, Ly lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>560120</v>
+        <v>560363</v>
       </c>
       <c r="R35" t="n">
-        <v>7309549</v>
+        <v>7309388</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4198,7 +4198,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126357916</v>
+        <v>126357490</v>
       </c>
       <c r="B36" t="n">
         <v>92032</v>
@@ -4232,14 +4232,14 @@
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Jipmomyran, Jipmomyran, Ly lm</t>
+          <t>Järnforsen, Järnforsen, Ly lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>560301</v>
+        <v>560120</v>
       </c>
       <c r="R36" t="n">
-        <v>7309435</v>
+        <v>7309549</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>

--- a/artfynd/A 8219-2025 artfynd.xlsx
+++ b/artfynd/A 8219-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY94"/>
+  <dimension ref="A1:AY95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2306,10 +2306,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126357389</v>
+        <v>127275517</v>
       </c>
       <c r="B18" t="n">
-        <v>91241</v>
+        <v>80115</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2317,21 +2317,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2344,10 +2344,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>560081</v>
+        <v>559782</v>
       </c>
       <c r="R18" t="n">
-        <v>7309611</v>
+        <v>7310143</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2374,12 +2374,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2392,30 +2392,25 @@
       <c r="AG18" t="b">
         <v>0</v>
       </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>Bördig grannaturskog i brant terräng</t>
-        </is>
-      </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Olle Amcoff</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Olle Amcoff</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126359227</v>
+        <v>126357389</v>
       </c>
       <c r="B19" t="n">
-        <v>75075</v>
+        <v>91241</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2423,34 +2418,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>1108</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Järnforsen, Järnforsen, Ly lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>560045</v>
+        <v>560081</v>
       </c>
       <c r="R19" t="n">
-        <v>7309792</v>
+        <v>7309611</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2491,12 +2489,13 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Bördig grannaturskog i brant terräng</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2514,10 +2513,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126359406</v>
+        <v>126359227</v>
       </c>
       <c r="B20" t="n">
-        <v>91263</v>
+        <v>75075</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2525,21 +2524,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2549,10 +2548,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>560158</v>
+        <v>560045</v>
       </c>
       <c r="R20" t="n">
-        <v>7309726</v>
+        <v>7309792</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2616,7 +2615,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126357387</v>
+        <v>126359406</v>
       </c>
       <c r="B21" t="n">
         <v>91263</v>
@@ -2651,10 +2650,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>560081</v>
+        <v>560158</v>
       </c>
       <c r="R21" t="n">
-        <v>7309611</v>
+        <v>7309726</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2700,7 +2699,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Bördig grannaturskog i brant terräng</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2718,15 +2717,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>66544349</v>
+        <v>126357387</v>
       </c>
       <c r="B22" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91263</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2734,37 +2728,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Djupfors V, Ly lm</t>
+          <t>Järnforsen, Järnforsen, Ly lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>560829.2017359853</v>
+        <v>560081</v>
       </c>
       <c r="R22" t="n">
-        <v>7309021.683959483</v>
+        <v>7309611</v>
       </c>
       <c r="S22" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2788,22 +2782,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2014-09-05</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2014-09-05</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2815,30 +2799,30 @@
       <c r="AG22" t="b">
         <v>0</v>
       </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>25090</t>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Bördig grannaturskog i brant terräng</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Malin Sahlin</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>66544354</v>
+        <v>66544349</v>
       </c>
       <c r="B23" t="n">
-        <v>89410</v>
+        <v>89388</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2851,21 +2835,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2875,10 +2859,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>560817.2887951054</v>
+        <v>560829.2017359853</v>
       </c>
       <c r="R23" t="n">
-        <v>7309023.475668295</v>
+        <v>7309021.683959483</v>
       </c>
       <c r="S23" t="n">
         <v>50</v>
@@ -2934,7 +2918,7 @@
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>25094</t>
+          <t>25090</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -2952,10 +2936,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119301540</v>
+        <v>66544354</v>
       </c>
       <c r="B24" t="n">
-        <v>57257</v>
+        <v>89410</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2964,41 +2948,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>102620</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hökuggla</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Surnia ulula</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Järnforsen, Ly lm</t>
+          <t>Djupfors V, Ly lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>559939</v>
+        <v>560817.2887951054</v>
       </c>
       <c r="R24" t="n">
-        <v>7309726</v>
+        <v>7309023.475668295</v>
       </c>
       <c r="S24" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3022,22 +3006,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2014-09-05</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2014-09-05</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3048,64 +3032,74 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>25094</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Sonata Isaksson</t>
+          <t>Malin Sahlin</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Sonata Isaksson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126359216</v>
+        <v>119301540</v>
       </c>
       <c r="B25" t="n">
-        <v>91241</v>
+        <v>57257</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1108</v>
+        <v>102620</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Hökuggla</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Surnia ulula</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Jipmomyran, Jipmomyran, Ly lm</t>
+          <t>Järnforsen, Ly lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>560542</v>
+        <v>559939</v>
       </c>
       <c r="R25" t="n">
-        <v>7309328</v>
+        <v>7309726</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>200</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3129,12 +3123,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3145,28 +3149,23 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>Lövrik grannaturskog</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Sonata Isaksson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Sonata Isaksson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126357506</v>
+        <v>126359216</v>
       </c>
       <c r="B26" t="n">
         <v>91241</v>
@@ -3197,14 +3196,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Järnforsen, Järnforsen, Ly lm</t>
+          <t>Jipmomyran, Jipmomyran, Ly lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>560120</v>
+        <v>560542</v>
       </c>
       <c r="R26" t="n">
-        <v>7309549</v>
+        <v>7309328</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3250,7 +3249,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Frodig, urskogsartade granskog i brant terräng</t>
+          <t>Lövrik grannaturskog</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3268,10 +3267,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126358404</v>
+        <v>126357506</v>
       </c>
       <c r="B27" t="n">
-        <v>80083</v>
+        <v>91241</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3279,34 +3278,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Jipmomyran, Jipmomyran, Ly lm</t>
+          <t>Järnforsen, Järnforsen, Ly lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>560173</v>
+        <v>560120</v>
       </c>
       <c r="R27" t="n">
-        <v>7309178</v>
+        <v>7309549</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3352,7 +3351,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Lövrik grannaturskog</t>
+          <t>Frodig, urskogsartade granskog i brant terräng</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3370,7 +3369,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126357428</v>
+        <v>126358404</v>
       </c>
       <c r="B28" t="n">
         <v>80083</v>
@@ -3401,14 +3400,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Järnforsen, Järnforsen, Ly lm</t>
+          <t>Jipmomyran, Jipmomyran, Ly lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>560096</v>
+        <v>560173</v>
       </c>
       <c r="R28" t="n">
-        <v>7309597</v>
+        <v>7309178</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3454,7 +3453,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Frodig gråalskog vid bäckdråg</t>
+          <t>Lövrik grannaturskog</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3472,32 +3471,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126357434</v>
+        <v>126357428</v>
       </c>
       <c r="B29" t="n">
-        <v>97437</v>
+        <v>80083</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220250</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3574,45 +3573,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126358063</v>
+        <v>126357434</v>
       </c>
       <c r="B30" t="n">
-        <v>75067</v>
+        <v>97437</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>308</v>
+        <v>220250</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Matteuccia struthiopteris</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Tod.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Jipmomyran, Jipmomyran, Ly lm</t>
+          <t>Järnforsen, Järnforsen, Ly lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>560358</v>
+        <v>560096</v>
       </c>
       <c r="R30" t="n">
-        <v>7309396</v>
+        <v>7309597</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3658,7 +3657,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Frodig, urskogsartade granskog i brant terräng</t>
+          <t>Frodig gråalskog vid bäckdråg</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3676,10 +3675,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126357705</v>
+        <v>126358063</v>
       </c>
       <c r="B31" t="n">
-        <v>91263</v>
+        <v>75067</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3687,21 +3686,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>308</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3711,10 +3710,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>560260</v>
+        <v>560358</v>
       </c>
       <c r="R31" t="n">
-        <v>7309464</v>
+        <v>7309396</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3778,10 +3777,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126358410</v>
+        <v>126357705</v>
       </c>
       <c r="B32" t="n">
-        <v>80084</v>
+        <v>91263</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3789,21 +3788,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3813,10 +3812,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>560173</v>
+        <v>560260</v>
       </c>
       <c r="R32" t="n">
-        <v>7309178</v>
+        <v>7309464</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3862,7 +3861,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Lövrik grannaturskog</t>
+          <t>Frodig, urskogsartade granskog i brant terräng</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -3880,10 +3879,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126358030</v>
+        <v>126358410</v>
       </c>
       <c r="B33" t="n">
-        <v>80083</v>
+        <v>80084</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3891,37 +3890,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Jipmomyran, Jipmomyran, Ly lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>560363</v>
+        <v>560173</v>
       </c>
       <c r="R33" t="n">
-        <v>7309388</v>
+        <v>7309178</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3962,13 +3958,12 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Frodig, urskogsartad granskog i brant terräng</t>
+          <t>Lövrik grannaturskog</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -3986,32 +3981,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126357490</v>
+        <v>126358030</v>
       </c>
       <c r="B34" t="n">
-        <v>92032</v>
+        <v>80114</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>918</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4020,14 +4015,14 @@
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Järnforsen, Järnforsen, Ly lm</t>
+          <t>Jipmomyran, Jipmomyran, Ly lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>560120</v>
+        <v>560363</v>
       </c>
       <c r="R34" t="n">
-        <v>7309549</v>
+        <v>7309388</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4092,10 +4087,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126357916</v>
+        <v>126358035</v>
       </c>
       <c r="B35" t="n">
-        <v>92032</v>
+        <v>75126</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4103,21 +4098,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>918</v>
+        <v>492</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4130,10 +4125,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>560301</v>
+        <v>560363</v>
       </c>
       <c r="R35" t="n">
-        <v>7309435</v>
+        <v>7309388</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4198,10 +4193,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126358035</v>
+        <v>126357916</v>
       </c>
       <c r="B36" t="n">
-        <v>75066</v>
+        <v>92106</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4209,21 +4204,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>492</v>
+        <v>918</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4236,10 +4231,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>560363</v>
+        <v>560301</v>
       </c>
       <c r="R36" t="n">
-        <v>7309388</v>
+        <v>7309435</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4304,32 +4299,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126357748</v>
+        <v>126357490</v>
       </c>
       <c r="B37" t="n">
-        <v>80084</v>
+        <v>92106</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2081</v>
+        <v>918</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4338,14 +4333,14 @@
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Jipmomyran, Jipmomyran, Ly lm</t>
+          <t>Järnforsen, Järnforsen, Ly lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>560277</v>
+        <v>560120</v>
       </c>
       <c r="R37" t="n">
-        <v>7309435</v>
+        <v>7309549</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4410,10 +4405,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126357718</v>
+        <v>126357748</v>
       </c>
       <c r="B38" t="n">
-        <v>91241</v>
+        <v>80115</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4421,21 +4416,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4448,10 +4443,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>560264</v>
+        <v>560277</v>
       </c>
       <c r="R38" t="n">
-        <v>7309462</v>
+        <v>7309435</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4516,10 +4511,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126358040</v>
+        <v>126357718</v>
       </c>
       <c r="B39" t="n">
-        <v>75080</v>
+        <v>91315</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4527,21 +4522,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1467</v>
+        <v>1108</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4554,10 +4549,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>560363</v>
+        <v>560264</v>
       </c>
       <c r="R39" t="n">
-        <v>7309388</v>
+        <v>7309462</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4622,10 +4617,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126358290</v>
+        <v>126358040</v>
       </c>
       <c r="B40" t="n">
-        <v>78980</v>
+        <v>75140</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4633,21 +4628,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4660,10 +4655,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>560224</v>
+        <v>560363</v>
       </c>
       <c r="R40" t="n">
-        <v>7309210</v>
+        <v>7309388</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4728,15 +4723,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>66544347</v>
+        <v>126358290</v>
       </c>
       <c r="B41" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79011</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4744,37 +4734,40 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Djupfors V, Ly lm</t>
+          <t>Jipmomyran, Jipmomyran, Ly lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>560878.5341145619</v>
+        <v>560224</v>
       </c>
       <c r="R41" t="n">
-        <v>7308993.284323963</v>
+        <v>7309210</v>
       </c>
       <c r="S41" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4798,22 +4791,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2014-09-05</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2014-09-05</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4822,30 +4805,31 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
-      <c r="AR41" t="inlineStr">
-        <is>
-          <t>25088</t>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>Frodig, urskogsartad granskog i brant terräng</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Malin Sahlin</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>66544345</v>
+        <v>66544347</v>
       </c>
       <c r="B42" t="n">
         <v>89392</v>
@@ -4885,10 +4869,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>560921.9021753618</v>
+        <v>560878.5341145619</v>
       </c>
       <c r="R42" t="n">
-        <v>7308956.577612261</v>
+        <v>7308993.284323963</v>
       </c>
       <c r="S42" t="n">
         <v>50</v>
@@ -4944,7 +4928,7 @@
       </c>
       <c r="AR42" t="inlineStr">
         <is>
-          <t>25086</t>
+          <t>25088</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -4962,10 +4946,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>66544351</v>
+        <v>66544345</v>
       </c>
       <c r="B43" t="n">
-        <v>89673</v>
+        <v>89392</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4978,21 +4962,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5002,10 +4986,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>560857.1901938798</v>
+        <v>560921.9021753618</v>
       </c>
       <c r="R43" t="n">
-        <v>7309014.91711883</v>
+        <v>7308956.577612261</v>
       </c>
       <c r="S43" t="n">
         <v>50</v>
@@ -5061,7 +5045,7 @@
       </c>
       <c r="AR43" t="inlineStr">
         <is>
-          <t>25092</t>
+          <t>25086</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5079,10 +5063,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>66544353</v>
+        <v>66544351</v>
       </c>
       <c r="B44" t="n">
-        <v>89356</v>
+        <v>89673</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5091,25 +5075,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5178,7 +5162,7 @@
       </c>
       <c r="AR44" t="inlineStr">
         <is>
-          <t>25093</t>
+          <t>25092</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5196,10 +5180,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>66544343</v>
+        <v>66544353</v>
       </c>
       <c r="B45" t="n">
-        <v>89392</v>
+        <v>89356</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5208,25 +5192,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5236,10 +5220,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>560933.9809844483</v>
+        <v>560857.1901938798</v>
       </c>
       <c r="R45" t="n">
-        <v>7308947.018279012</v>
+        <v>7309014.91711883</v>
       </c>
       <c r="S45" t="n">
         <v>50</v>
@@ -5295,7 +5279,7 @@
       </c>
       <c r="AR45" t="inlineStr">
         <is>
-          <t>25084</t>
+          <t>25093</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -5313,10 +5297,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>66544348</v>
+        <v>66544343</v>
       </c>
       <c r="B46" t="n">
-        <v>89388</v>
+        <v>89392</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5329,21 +5313,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5353,10 +5337,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>560863.3901593408</v>
+        <v>560933.9809844483</v>
       </c>
       <c r="R46" t="n">
-        <v>7308992.96197705</v>
+        <v>7308947.018279012</v>
       </c>
       <c r="S46" t="n">
         <v>50</v>
@@ -5412,7 +5396,7 @@
       </c>
       <c r="AR46" t="inlineStr">
         <is>
-          <t>25089</t>
+          <t>25084</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5430,10 +5414,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>66544344</v>
+        <v>66544348</v>
       </c>
       <c r="B47" t="n">
-        <v>89780</v>
+        <v>89388</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5442,25 +5426,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4217</v>
+        <v>1108</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5470,10 +5454,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>560933.9809844483</v>
+        <v>560863.3901593408</v>
       </c>
       <c r="R47" t="n">
-        <v>7308947.018279012</v>
+        <v>7308992.96197705</v>
       </c>
       <c r="S47" t="n">
         <v>50</v>
@@ -5529,7 +5513,7 @@
       </c>
       <c r="AR47" t="inlineStr">
         <is>
-          <t>25085</t>
+          <t>25089</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -5547,10 +5531,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>66544346</v>
+        <v>66544344</v>
       </c>
       <c r="B48" t="n">
-        <v>77506</v>
+        <v>89780</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5559,25 +5543,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>4217</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5587,10 +5571,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>560921.9021753618</v>
+        <v>560933.9809844483</v>
       </c>
       <c r="R48" t="n">
-        <v>7308956.577612261</v>
+        <v>7308947.018279012</v>
       </c>
       <c r="S48" t="n">
         <v>50</v>
@@ -5646,7 +5630,7 @@
       </c>
       <c r="AR48" t="inlineStr">
         <is>
-          <t>25087</t>
+          <t>25085</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -5664,10 +5648,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>66544350</v>
+        <v>66544346</v>
       </c>
       <c r="B49" t="n">
-        <v>89392</v>
+        <v>77506</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5680,21 +5664,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5704,10 +5688,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>560857.1901938798</v>
+        <v>560921.9021753618</v>
       </c>
       <c r="R49" t="n">
-        <v>7309014.91711883</v>
+        <v>7308956.577612261</v>
       </c>
       <c r="S49" t="n">
         <v>50</v>
@@ -5763,7 +5747,7 @@
       </c>
       <c r="AR49" t="inlineStr">
         <is>
-          <t>25091</t>
+          <t>25087</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -5781,10 +5765,15 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126360335</v>
+        <v>66544350</v>
       </c>
       <c r="B50" t="n">
-        <v>91263</v>
+        <v>89392</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5792,40 +5781,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Jipmomyran, Jipmomyran, Ly lm</t>
+          <t>Djupfors V, Ly lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>560893</v>
+        <v>560857.1901938798</v>
       </c>
       <c r="R50" t="n">
-        <v>7308996</v>
+        <v>7309014.91711883</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5849,12 +5835,22 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2014-09-05</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2014-09-05</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5863,34 +5859,33 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
-      <c r="AI50" t="inlineStr">
-        <is>
-          <t>Grannaturskog/gransumpskog</t>
+      <c r="AR50" t="inlineStr">
+        <is>
+          <t>25091</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Malin Sahlin</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126360324</v>
+        <v>126360335</v>
       </c>
       <c r="B51" t="n">
-        <v>91245</v>
+        <v>91263</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5898,21 +5893,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5993,10 +5988,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126360636</v>
+        <v>126360324</v>
       </c>
       <c r="B52" t="n">
-        <v>91241</v>
+        <v>91245</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6004,21 +5999,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6031,10 +6026,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>560870</v>
+        <v>560893</v>
       </c>
       <c r="R52" t="n">
-        <v>7309007</v>
+        <v>7308996</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6099,10 +6094,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126360392</v>
+        <v>126360636</v>
       </c>
       <c r="B53" t="n">
-        <v>91541</v>
+        <v>91241</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6110,21 +6105,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>658</v>
+        <v>1108</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6205,32 +6200,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126360389</v>
+        <v>126360392</v>
       </c>
       <c r="B54" t="n">
-        <v>91699</v>
+        <v>91541</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6311,32 +6306,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126360330</v>
+        <v>126360389</v>
       </c>
       <c r="B55" t="n">
-        <v>91241</v>
+        <v>91699</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1108</v>
+        <v>1209</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6349,10 +6344,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>560893</v>
+        <v>560870</v>
       </c>
       <c r="R55" t="n">
-        <v>7308996</v>
+        <v>7309007</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6417,53 +6412,51 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>66544342</v>
+        <v>126360330</v>
       </c>
       <c r="B56" t="n">
-        <v>90074</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91241</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Djupfors V, Ly lm</t>
+          <t>Jipmomyran, Jipmomyran, Ly lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>560960.3945341655</v>
+        <v>560893</v>
       </c>
       <c r="R56" t="n">
-        <v>7308918.130968786</v>
+        <v>7308996</v>
       </c>
       <c r="S56" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6487,22 +6480,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2014-09-05</t>
-        </is>
-      </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2014-09-05</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6511,33 +6494,34 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
-      <c r="AR56" t="inlineStr">
-        <is>
-          <t>25083</t>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>Grannaturskog/gransumpskog</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Malin Sahlin</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>66544630</v>
+        <v>66544342</v>
       </c>
       <c r="B57" t="n">
-        <v>89388</v>
+        <v>90074</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6546,25 +6530,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6574,10 +6558,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>561061.5146522231</v>
+        <v>560960.3945341655</v>
       </c>
       <c r="R57" t="n">
-        <v>7308842.570840668</v>
+        <v>7308918.130968786</v>
       </c>
       <c r="S57" t="n">
         <v>50</v>
@@ -6633,7 +6617,7 @@
       </c>
       <c r="AR57" t="inlineStr">
         <is>
-          <t>25353</t>
+          <t>25083</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -6644,17 +6628,17 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Via Malin Sahlin</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>66544637</v>
+        <v>66544630</v>
       </c>
       <c r="B58" t="n">
-        <v>89410</v>
+        <v>89388</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6667,21 +6651,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6691,10 +6675,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>561099.626093693</v>
+        <v>561061.5146522231</v>
       </c>
       <c r="R58" t="n">
-        <v>7308822.114403572</v>
+        <v>7308842.570840668</v>
       </c>
       <c r="S58" t="n">
         <v>50</v>
@@ -6750,7 +6734,7 @@
       </c>
       <c r="AR58" t="inlineStr">
         <is>
-          <t>25360</t>
+          <t>25353</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -6768,10 +6752,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>66544633</v>
+        <v>66544637</v>
       </c>
       <c r="B59" t="n">
-        <v>90160</v>
+        <v>89410</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6780,25 +6764,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>918</v>
+        <v>5432</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6808,10 +6792,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>561072.4974219487</v>
+        <v>561099.626093693</v>
       </c>
       <c r="R59" t="n">
-        <v>7308826.852570722</v>
+        <v>7308822.114403572</v>
       </c>
       <c r="S59" t="n">
         <v>50</v>
@@ -6867,7 +6851,7 @@
       </c>
       <c r="AR59" t="inlineStr">
         <is>
-          <t>25356</t>
+          <t>25360</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -6885,10 +6869,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>66544627</v>
+        <v>66544633</v>
       </c>
       <c r="B60" t="n">
-        <v>89392</v>
+        <v>90160</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6897,25 +6881,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1202</v>
+        <v>918</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6925,10 +6909,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>561044.5755368763</v>
+        <v>561072.4974219487</v>
       </c>
       <c r="R60" t="n">
-        <v>7308849.572017924</v>
+        <v>7308826.852570722</v>
       </c>
       <c r="S60" t="n">
         <v>50</v>
@@ -6984,7 +6968,7 @@
       </c>
       <c r="AR60" t="inlineStr">
         <is>
-          <t>25350</t>
+          <t>25356</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7002,10 +6986,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>66544641</v>
+        <v>66544627</v>
       </c>
       <c r="B61" t="n">
-        <v>89832</v>
+        <v>89392</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7014,25 +6998,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7042,10 +7026,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>561099.626093693</v>
+        <v>561044.5755368763</v>
       </c>
       <c r="R61" t="n">
-        <v>7308822.114403572</v>
+        <v>7308849.572017924</v>
       </c>
       <c r="S61" t="n">
         <v>50</v>
@@ -7101,7 +7085,7 @@
       </c>
       <c r="AR61" t="inlineStr">
         <is>
-          <t>25364</t>
+          <t>25350</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7119,10 +7103,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>66544639</v>
+        <v>66544641</v>
       </c>
       <c r="B62" t="n">
-        <v>77506</v>
+        <v>89832</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7131,32 +7115,28 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Djupfors V, Ly lm</t>
@@ -7222,7 +7202,7 @@
       </c>
       <c r="AR62" t="inlineStr">
         <is>
-          <t>25362</t>
+          <t>25364</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -7240,10 +7220,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>66544619</v>
+        <v>66544639</v>
       </c>
       <c r="B63" t="n">
-        <v>81236</v>
+        <v>77506</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7256,34 +7236,38 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Djupfors V, Ly lm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>561027.2184662716</v>
+        <v>561099.626093693</v>
       </c>
       <c r="R63" t="n">
-        <v>7308856.973397947</v>
+        <v>7308822.114403572</v>
       </c>
       <c r="S63" t="n">
         <v>50</v>
@@ -7339,7 +7323,7 @@
       </c>
       <c r="AR63" t="inlineStr">
         <is>
-          <t>25343</t>
+          <t>25362</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -7357,10 +7341,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>66544626</v>
+        <v>66544619</v>
       </c>
       <c r="B64" t="n">
-        <v>77506</v>
+        <v>81236</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7373,38 +7357,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Djupfors V, Ly lm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>561044.5755368763</v>
+        <v>561027.2184662716</v>
       </c>
       <c r="R64" t="n">
-        <v>7308849.572017924</v>
+        <v>7308856.973397947</v>
       </c>
       <c r="S64" t="n">
         <v>50</v>
@@ -7460,7 +7440,7 @@
       </c>
       <c r="AR64" t="inlineStr">
         <is>
-          <t>25349</t>
+          <t>25343</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -7478,10 +7458,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>66544638</v>
+        <v>66544626</v>
       </c>
       <c r="B65" t="n">
-        <v>89673</v>
+        <v>77506</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7494,34 +7474,38 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Djupfors V, Ly lm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>561099.626093693</v>
+        <v>561044.5755368763</v>
       </c>
       <c r="R65" t="n">
-        <v>7308822.114403572</v>
+        <v>7308849.572017924</v>
       </c>
       <c r="S65" t="n">
         <v>50</v>
@@ -7577,7 +7561,7 @@
       </c>
       <c r="AR65" t="inlineStr">
         <is>
-          <t>25361</t>
+          <t>25349</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -7595,10 +7579,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>66544620</v>
+        <v>66544638</v>
       </c>
       <c r="B66" t="n">
-        <v>89410</v>
+        <v>89673</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7611,21 +7595,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7635,10 +7619,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>561027.2184662716</v>
+        <v>561099.626093693</v>
       </c>
       <c r="R66" t="n">
-        <v>7308856.973397947</v>
+        <v>7308822.114403572</v>
       </c>
       <c r="S66" t="n">
         <v>50</v>
@@ -7694,7 +7678,7 @@
       </c>
       <c r="AR66" t="inlineStr">
         <is>
-          <t>25344</t>
+          <t>25361</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -7712,10 +7696,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>66544640</v>
+        <v>66544620</v>
       </c>
       <c r="B67" t="n">
-        <v>89392</v>
+        <v>89410</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7728,21 +7712,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7752,10 +7736,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>561099.626093693</v>
+        <v>561027.2184662716</v>
       </c>
       <c r="R67" t="n">
-        <v>7308822.114403572</v>
+        <v>7308856.973397947</v>
       </c>
       <c r="S67" t="n">
         <v>50</v>
@@ -7811,7 +7795,7 @@
       </c>
       <c r="AR67" t="inlineStr">
         <is>
-          <t>25363</t>
+          <t>25344</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -7829,10 +7813,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>66544649</v>
+        <v>66544640</v>
       </c>
       <c r="B68" t="n">
-        <v>81236</v>
+        <v>89392</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7845,21 +7829,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7869,10 +7853,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>561139.9464785276</v>
+        <v>561099.626093693</v>
       </c>
       <c r="R68" t="n">
-        <v>7308736.66569937</v>
+        <v>7308822.114403572</v>
       </c>
       <c r="S68" t="n">
         <v>50</v>
@@ -7928,7 +7912,7 @@
       </c>
       <c r="AR68" t="inlineStr">
         <is>
-          <t>25372</t>
+          <t>25363</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -7946,10 +7930,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>66544642</v>
+        <v>66544649</v>
       </c>
       <c r="B69" t="n">
-        <v>89410</v>
+        <v>81236</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7962,21 +7946,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7986,10 +7970,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>561096.8231878708</v>
+        <v>561139.9464785276</v>
       </c>
       <c r="R69" t="n">
-        <v>7308799.96586439</v>
+        <v>7308736.66569937</v>
       </c>
       <c r="S69" t="n">
         <v>50</v>
@@ -8045,7 +8029,7 @@
       </c>
       <c r="AR69" t="inlineStr">
         <is>
-          <t>25365</t>
+          <t>25372</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8063,10 +8047,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>66544623</v>
+        <v>66544642</v>
       </c>
       <c r="B70" t="n">
-        <v>89673</v>
+        <v>89410</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8079,38 +8063,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Djupfors V, Ly lm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>561044.5755368763</v>
+        <v>561096.8231878708</v>
       </c>
       <c r="R70" t="n">
-        <v>7308849.572017924</v>
+        <v>7308799.96586439</v>
       </c>
       <c r="S70" t="n">
         <v>50</v>
@@ -8166,7 +8146,7 @@
       </c>
       <c r="AR70" t="inlineStr">
         <is>
-          <t>25347</t>
+          <t>25365</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -8184,10 +8164,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>66544341</v>
+        <v>66544623</v>
       </c>
       <c r="B71" t="n">
-        <v>77506</v>
+        <v>89673</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8200,34 +8180,38 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Djupfors V, Ly lm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>561008.5625325058</v>
+        <v>561044.5755368763</v>
       </c>
       <c r="R71" t="n">
-        <v>7308906.069035768</v>
+        <v>7308849.572017924</v>
       </c>
       <c r="S71" t="n">
         <v>50</v>
@@ -8283,7 +8267,7 @@
       </c>
       <c r="AR71" t="inlineStr">
         <is>
-          <t>25082</t>
+          <t>25347</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -8294,14 +8278,14 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Via Malin Sahlin</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>66544622</v>
+        <v>66544341</v>
       </c>
       <c r="B72" t="n">
         <v>77506</v>
@@ -8334,21 +8318,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Djupfors V, Ly lm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>561027.2184662716</v>
+        <v>561008.5625325058</v>
       </c>
       <c r="R72" t="n">
-        <v>7308856.973397947</v>
+        <v>7308906.069035768</v>
       </c>
       <c r="S72" t="n">
         <v>50</v>
@@ -8404,7 +8384,7 @@
       </c>
       <c r="AR72" t="inlineStr">
         <is>
-          <t>25346</t>
+          <t>25082</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -8415,17 +8395,17 @@
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Via Malin Sahlin</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>66544651</v>
+        <v>66544622</v>
       </c>
       <c r="B73" t="n">
-        <v>89673</v>
+        <v>77506</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8438,34 +8418,38 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Djupfors V, Ly lm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>561139.9464785276</v>
+        <v>561027.2184662716</v>
       </c>
       <c r="R73" t="n">
-        <v>7308736.66569937</v>
+        <v>7308856.973397947</v>
       </c>
       <c r="S73" t="n">
         <v>50</v>
@@ -8521,7 +8505,7 @@
       </c>
       <c r="AR73" t="inlineStr">
         <is>
-          <t>25373</t>
+          <t>25346</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -8539,10 +8523,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>66544631</v>
+        <v>66544651</v>
       </c>
       <c r="B74" t="n">
-        <v>77506</v>
+        <v>89673</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8555,38 +8539,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Djupfors V, Ly lm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>561061.5146522231</v>
+        <v>561139.9464785276</v>
       </c>
       <c r="R74" t="n">
-        <v>7308842.570840668</v>
+        <v>7308736.66569937</v>
       </c>
       <c r="S74" t="n">
         <v>50</v>
@@ -8642,7 +8622,7 @@
       </c>
       <c r="AR74" t="inlineStr">
         <is>
-          <t>25354</t>
+          <t>25373</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -8660,10 +8640,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>66544621</v>
+        <v>66544631</v>
       </c>
       <c r="B75" t="n">
-        <v>56395</v>
+        <v>77506</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8676,34 +8656,38 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Djupfors V, Ly lm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>561027.2184662716</v>
+        <v>561061.5146522231</v>
       </c>
       <c r="R75" t="n">
-        <v>7308856.973397947</v>
+        <v>7308842.570840668</v>
       </c>
       <c r="S75" t="n">
         <v>50</v>
@@ -8759,7 +8743,7 @@
       </c>
       <c r="AR75" t="inlineStr">
         <is>
-          <t>25345</t>
+          <t>25354</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -8777,10 +8761,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>66544647</v>
+        <v>66544621</v>
       </c>
       <c r="B76" t="n">
-        <v>77506</v>
+        <v>56395</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8793,38 +8777,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Djupfors V, Ly lm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>561118.808368561</v>
+        <v>561027.2184662716</v>
       </c>
       <c r="R76" t="n">
-        <v>7308748.485677995</v>
+        <v>7308856.973397947</v>
       </c>
       <c r="S76" t="n">
         <v>50</v>
@@ -8880,7 +8860,7 @@
       </c>
       <c r="AR76" t="inlineStr">
         <is>
-          <t>25370</t>
+          <t>25345</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -8898,7 +8878,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>66544635</v>
+        <v>66544647</v>
       </c>
       <c r="B77" t="n">
         <v>77506</v>
@@ -8942,10 +8922,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>561072.4974219487</v>
+        <v>561118.808368561</v>
       </c>
       <c r="R77" t="n">
-        <v>7308826.852570722</v>
+        <v>7308748.485677995</v>
       </c>
       <c r="S77" t="n">
         <v>50</v>
@@ -9001,7 +8981,7 @@
       </c>
       <c r="AR77" t="inlineStr">
         <is>
-          <t>25358</t>
+          <t>25370</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -9019,10 +8999,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>66544648</v>
+        <v>66544635</v>
       </c>
       <c r="B78" t="n">
-        <v>85703</v>
+        <v>77506</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9035,34 +9015,38 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Djupfors V, Ly lm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>561139.9464785276</v>
+        <v>561072.4974219487</v>
       </c>
       <c r="R78" t="n">
-        <v>7308736.66569937</v>
+        <v>7308826.852570722</v>
       </c>
       <c r="S78" t="n">
         <v>50</v>
@@ -9118,7 +9102,7 @@
       </c>
       <c r="AR78" t="inlineStr">
         <is>
-          <t>25371</t>
+          <t>25358</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -9136,10 +9120,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>66544628</v>
+        <v>66544648</v>
       </c>
       <c r="B79" t="n">
-        <v>89388</v>
+        <v>85703</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9152,21 +9136,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1108</v>
+        <v>510</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9176,10 +9160,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>561044.5755368763</v>
+        <v>561139.9464785276</v>
       </c>
       <c r="R79" t="n">
-        <v>7308849.572017924</v>
+        <v>7308736.66569937</v>
       </c>
       <c r="S79" t="n">
         <v>50</v>
@@ -9235,7 +9219,7 @@
       </c>
       <c r="AR79" t="inlineStr">
         <is>
-          <t>25351</t>
+          <t>25371</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -9253,10 +9237,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>66544645</v>
+        <v>66544628</v>
       </c>
       <c r="B80" t="n">
-        <v>89673</v>
+        <v>89388</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9269,21 +9253,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>658</v>
+        <v>1108</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9293,10 +9277,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>561118.808368561</v>
+        <v>561044.5755368763</v>
       </c>
       <c r="R80" t="n">
-        <v>7308748.485677995</v>
+        <v>7308849.572017924</v>
       </c>
       <c r="S80" t="n">
         <v>50</v>
@@ -9352,7 +9336,7 @@
       </c>
       <c r="AR80" t="inlineStr">
         <is>
-          <t>25368</t>
+          <t>25351</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -9370,10 +9354,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>66544636</v>
+        <v>66544645</v>
       </c>
       <c r="B81" t="n">
-        <v>81236</v>
+        <v>89673</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9386,21 +9370,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9410,10 +9394,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>561072.4974219487</v>
+        <v>561118.808368561</v>
       </c>
       <c r="R81" t="n">
-        <v>7308826.852570722</v>
+        <v>7308748.485677995</v>
       </c>
       <c r="S81" t="n">
         <v>50</v>
@@ -9469,7 +9453,7 @@
       </c>
       <c r="AR81" t="inlineStr">
         <is>
-          <t>25359</t>
+          <t>25368</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -9487,10 +9471,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>66544634</v>
+        <v>66544636</v>
       </c>
       <c r="B82" t="n">
-        <v>89356</v>
+        <v>81236</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9499,25 +9483,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9586,7 +9570,7 @@
       </c>
       <c r="AR82" t="inlineStr">
         <is>
-          <t>25357</t>
+          <t>25359</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -9604,10 +9588,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>66544646</v>
+        <v>66544634</v>
       </c>
       <c r="B83" t="n">
-        <v>89392</v>
+        <v>89356</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9616,25 +9600,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9644,10 +9628,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>561118.808368561</v>
+        <v>561072.4974219487</v>
       </c>
       <c r="R83" t="n">
-        <v>7308748.485677995</v>
+        <v>7308826.852570722</v>
       </c>
       <c r="S83" t="n">
         <v>50</v>
@@ -9703,7 +9687,7 @@
       </c>
       <c r="AR83" t="inlineStr">
         <is>
-          <t>25369</t>
+          <t>25357</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -9721,10 +9705,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>66544632</v>
+        <v>66544646</v>
       </c>
       <c r="B84" t="n">
-        <v>81236</v>
+        <v>89392</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9737,21 +9721,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9761,10 +9745,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>561061.5146522231</v>
+        <v>561118.808368561</v>
       </c>
       <c r="R84" t="n">
-        <v>7308842.570840668</v>
+        <v>7308748.485677995</v>
       </c>
       <c r="S84" t="n">
         <v>50</v>
@@ -9820,7 +9804,7 @@
       </c>
       <c r="AR84" t="inlineStr">
         <is>
-          <t>25355</t>
+          <t>25369</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -9838,10 +9822,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>66544625</v>
+        <v>66544632</v>
       </c>
       <c r="B85" t="n">
-        <v>56395</v>
+        <v>81236</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9854,21 +9838,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9878,10 +9862,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>561044.5755368763</v>
+        <v>561061.5146522231</v>
       </c>
       <c r="R85" t="n">
-        <v>7308849.572017924</v>
+        <v>7308842.570840668</v>
       </c>
       <c r="S85" t="n">
         <v>50</v>
@@ -9937,7 +9921,7 @@
       </c>
       <c r="AR85" t="inlineStr">
         <is>
-          <t>25348</t>
+          <t>25355</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -9955,10 +9939,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>66544643</v>
+        <v>66544625</v>
       </c>
       <c r="B86" t="n">
-        <v>77506</v>
+        <v>56395</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9971,38 +9955,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Djupfors V, Ly lm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>561108.4689856211</v>
+        <v>561044.5755368763</v>
       </c>
       <c r="R86" t="n">
-        <v>7308772.399080777</v>
+        <v>7308849.572017924</v>
       </c>
       <c r="S86" t="n">
         <v>50</v>
@@ -10058,7 +10038,7 @@
       </c>
       <c r="AR86" t="inlineStr">
         <is>
-          <t>25366</t>
+          <t>25348</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -10076,10 +10056,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>66544644</v>
+        <v>66544643</v>
       </c>
       <c r="B87" t="n">
-        <v>81236</v>
+        <v>77506</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10092,24 +10072,28 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Djupfors V, Ly lm</t>
@@ -10175,7 +10159,7 @@
       </c>
       <c r="AR87" t="inlineStr">
         <is>
-          <t>25367</t>
+          <t>25366</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -10193,10 +10177,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>66544629</v>
+        <v>66544644</v>
       </c>
       <c r="B88" t="n">
-        <v>89406</v>
+        <v>81236</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10209,21 +10193,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10233,10 +10217,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>561061.5146522231</v>
+        <v>561108.4689856211</v>
       </c>
       <c r="R88" t="n">
-        <v>7308842.570840668</v>
+        <v>7308772.399080777</v>
       </c>
       <c r="S88" t="n">
         <v>50</v>
@@ -10292,7 +10276,7 @@
       </c>
       <c r="AR88" t="inlineStr">
         <is>
-          <t>25352</t>
+          <t>25367</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -10310,10 +10294,15 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126361165</v>
+        <v>66544629</v>
       </c>
       <c r="B89" t="n">
-        <v>91259</v>
+        <v>89406</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10341,17 +10330,17 @@
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Djupselet, Djupselet, Ly lm</t>
+          <t>Djupfors V, Ly lm</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>561436</v>
+        <v>561061.5146522231</v>
       </c>
       <c r="R89" t="n">
-        <v>7308968</v>
+        <v>7308842.570840668</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10375,12 +10364,22 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2014-09-05</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2014-09-05</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10392,52 +10391,52 @@
       <c r="AG89" t="b">
         <v>0</v>
       </c>
-      <c r="AI89" t="inlineStr">
-        <is>
-          <t>Bördig, grovvuxen grannaturskog</t>
+      <c r="AR89" t="inlineStr">
+        <is>
+          <t>25352</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Malin Sahlin</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Via Malin Sahlin</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126361127</v>
+        <v>126361165</v>
       </c>
       <c r="B90" t="n">
-        <v>75066</v>
+        <v>91259</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>492</v>
+        <v>1204</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10447,10 +10446,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>561403</v>
+        <v>561436</v>
       </c>
       <c r="R90" t="n">
-        <v>7308978</v>
+        <v>7308968</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10514,32 +10513,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126361121</v>
+        <v>126361127</v>
       </c>
       <c r="B91" t="n">
-        <v>75080</v>
+        <v>75066</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1467</v>
+        <v>492</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10616,10 +10615,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126361100</v>
+        <v>126361121</v>
       </c>
       <c r="B92" t="n">
-        <v>91263</v>
+        <v>75080</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10627,21 +10626,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>5432</v>
+        <v>1467</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10651,10 +10650,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>561396</v>
+        <v>561403</v>
       </c>
       <c r="R92" t="n">
-        <v>7308982</v>
+        <v>7308978</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10718,15 +10717,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>66544653</v>
+        <v>126361100</v>
       </c>
       <c r="B93" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91263</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10734,37 +10728,37 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Djupfors V, Ly lm</t>
+          <t>Djupselet, Djupselet, Ly lm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>561132.2069487682</v>
+        <v>561396</v>
       </c>
       <c r="R93" t="n">
-        <v>7308696.41208922</v>
+        <v>7308982</v>
       </c>
       <c r="S93" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10788,22 +10782,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2014-09-05</t>
-        </is>
-      </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2014-09-05</t>
-        </is>
-      </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10815,30 +10799,30 @@
       <c r="AG93" t="b">
         <v>0</v>
       </c>
-      <c r="AR93" t="inlineStr">
-        <is>
-          <t>25375</t>
+      <c r="AI93" t="inlineStr">
+        <is>
+          <t>Bördig, grovvuxen grannaturskog</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Malin Sahlin</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Via Malin Sahlin</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>66544652</v>
+        <v>66544653</v>
       </c>
       <c r="B94" t="n">
-        <v>81236</v>
+        <v>89388</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10851,21 +10835,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10934,7 +10918,7 @@
       </c>
       <c r="AR94" t="inlineStr">
         <is>
-          <t>25374</t>
+          <t>25375</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -10949,6 +10933,123 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>66544652</v>
+      </c>
+      <c r="B95" t="n">
+        <v>81236</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Djupfors V, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>561132.2069487682</v>
+      </c>
+      <c r="R95" t="n">
+        <v>7308696.41208922</v>
+      </c>
+      <c r="S95" t="n">
+        <v>50</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2014-09-05</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2014-09-05</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR95" t="inlineStr">
+        <is>
+          <t>25374</t>
+        </is>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Malin Sahlin</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Via Malin Sahlin</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 8219-2025 artfynd.xlsx
+++ b/artfynd/A 8219-2025 artfynd.xlsx
@@ -2309,7 +2309,7 @@
         <v>127275517</v>
       </c>
       <c r="B18" t="n">
-        <v>80115</v>
+        <v>80118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3984,7 +3984,7 @@
         <v>126358030</v>
       </c>
       <c r="B34" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4090,7 +4090,7 @@
         <v>126358035</v>
       </c>
       <c r="B35" t="n">
-        <v>75126</v>
+        <v>75129</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         <v>126357916</v>
       </c>
       <c r="B36" t="n">
-        <v>92106</v>
+        <v>92112</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4302,7 +4302,7 @@
         <v>126357490</v>
       </c>
       <c r="B37" t="n">
-        <v>92106</v>
+        <v>92112</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4408,7 +4408,7 @@
         <v>126357748</v>
       </c>
       <c r="B38" t="n">
-        <v>80115</v>
+        <v>80118</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         <v>126357718</v>
       </c>
       <c r="B39" t="n">
-        <v>91315</v>
+        <v>91321</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4620,7 +4620,7 @@
         <v>126358040</v>
       </c>
       <c r="B40" t="n">
-        <v>75140</v>
+        <v>75143</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4726,7 +4726,7 @@
         <v>126358290</v>
       </c>
       <c r="B41" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 8219-2025 artfynd.xlsx
+++ b/artfynd/A 8219-2025 artfynd.xlsx
@@ -2309,7 +2309,7 @@
         <v>127275517</v>
       </c>
       <c r="B18" t="n">
-        <v>80118</v>
+        <v>80122</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 8219-2025 artfynd.xlsx
+++ b/artfynd/A 8219-2025 artfynd.xlsx
@@ -2309,7 +2309,7 @@
         <v>127275517</v>
       </c>
       <c r="B18" t="n">
-        <v>80122</v>
+        <v>80124</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 8219-2025 artfynd.xlsx
+++ b/artfynd/A 8219-2025 artfynd.xlsx
@@ -2309,7 +2309,7 @@
         <v>127275517</v>
       </c>
       <c r="B18" t="n">
-        <v>80124</v>
+        <v>80127</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 8219-2025 artfynd.xlsx
+++ b/artfynd/A 8219-2025 artfynd.xlsx
@@ -2309,7 +2309,7 @@
         <v>127275517</v>
       </c>
       <c r="B18" t="n">
-        <v>80127</v>
+        <v>80133</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 8219-2025 artfynd.xlsx
+++ b/artfynd/A 8219-2025 artfynd.xlsx
@@ -2309,7 +2309,7 @@
         <v>127275517</v>
       </c>
       <c r="B18" t="n">
-        <v>80133</v>
+        <v>80115</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3984,7 +3984,7 @@
         <v>126358030</v>
       </c>
       <c r="B34" t="n">
-        <v>80117</v>
+        <v>80114</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4090,7 +4090,7 @@
         <v>126358035</v>
       </c>
       <c r="B35" t="n">
-        <v>75129</v>
+        <v>75126</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         <v>126357916</v>
       </c>
       <c r="B36" t="n">
-        <v>92112</v>
+        <v>92106</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4302,7 +4302,7 @@
         <v>126357490</v>
       </c>
       <c r="B37" t="n">
-        <v>92112</v>
+        <v>92106</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4408,7 +4408,7 @@
         <v>126357748</v>
       </c>
       <c r="B38" t="n">
-        <v>80118</v>
+        <v>80115</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         <v>126357718</v>
       </c>
       <c r="B39" t="n">
-        <v>91321</v>
+        <v>91315</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4620,7 +4620,7 @@
         <v>126358040</v>
       </c>
       <c r="B40" t="n">
-        <v>75143</v>
+        <v>75140</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4726,7 +4726,7 @@
         <v>126358290</v>
       </c>
       <c r="B41" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 8219-2025 artfynd.xlsx
+++ b/artfynd/A 8219-2025 artfynd.xlsx
@@ -2309,7 +2309,7 @@
         <v>127275517</v>
       </c>
       <c r="B18" t="n">
-        <v>80115</v>
+        <v>80133</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3984,7 +3984,7 @@
         <v>126358030</v>
       </c>
       <c r="B34" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4090,7 +4090,7 @@
         <v>126358035</v>
       </c>
       <c r="B35" t="n">
-        <v>75126</v>
+        <v>75129</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         <v>126357916</v>
       </c>
       <c r="B36" t="n">
-        <v>92106</v>
+        <v>92112</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4302,7 +4302,7 @@
         <v>126357490</v>
       </c>
       <c r="B37" t="n">
-        <v>92106</v>
+        <v>92112</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4408,7 +4408,7 @@
         <v>126357748</v>
       </c>
       <c r="B38" t="n">
-        <v>80115</v>
+        <v>80118</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         <v>126357718</v>
       </c>
       <c r="B39" t="n">
-        <v>91315</v>
+        <v>91321</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4620,7 +4620,7 @@
         <v>126358040</v>
       </c>
       <c r="B40" t="n">
-        <v>75140</v>
+        <v>75143</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4726,7 +4726,7 @@
         <v>126358290</v>
       </c>
       <c r="B41" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 8219-2025 artfynd.xlsx
+++ b/artfynd/A 8219-2025 artfynd.xlsx
@@ -3576,7 +3576,7 @@
         <v>126357434</v>
       </c>
       <c r="B30" t="n">
-        <v>97437</v>
+        <v>98090</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3602,6 +3602,10 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Järnforsen, Järnforsen, Ly lm</t>
@@ -3652,6 +3656,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3678,7 +3683,7 @@
         <v>126358063</v>
       </c>
       <c r="B31" t="n">
-        <v>75067</v>
+        <v>83221</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3704,6 +3709,9 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Jipmomyran, Jipmomyran, Ly lm</t>
@@ -3754,12 +3762,13 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Frodig, urskogsartade granskog i brant terräng</t>
+          <t>Frodig, urskogsartad granskog i brant terräng</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4196,7 +4205,7 @@
         <v>126357916</v>
       </c>
       <c r="B36" t="n">
-        <v>92112</v>
+        <v>92628</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4408,7 +4417,7 @@
         <v>126357748</v>
       </c>
       <c r="B38" t="n">
-        <v>80118</v>
+        <v>80355</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4620,7 +4629,7 @@
         <v>126358040</v>
       </c>
       <c r="B40" t="n">
-        <v>75143</v>
+        <v>83234</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 8219-2025 artfynd.xlsx
+++ b/artfynd/A 8219-2025 artfynd.xlsx
@@ -3576,7 +3576,7 @@
         <v>126357434</v>
       </c>
       <c r="B30" t="n">
-        <v>98090</v>
+        <v>98091</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>126358063</v>
       </c>
       <c r="B31" t="n">
-        <v>83221</v>
+        <v>83222</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4205,7 +4205,7 @@
         <v>126357916</v>
       </c>
       <c r="B36" t="n">
-        <v>92628</v>
+        <v>92629</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4417,7 +4417,7 @@
         <v>126357748</v>
       </c>
       <c r="B38" t="n">
-        <v>80355</v>
+        <v>80356</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4629,7 +4629,7 @@
         <v>126358040</v>
       </c>
       <c r="B40" t="n">
-        <v>83234</v>
+        <v>83235</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 8219-2025 artfynd.xlsx
+++ b/artfynd/A 8219-2025 artfynd.xlsx
@@ -3576,7 +3576,7 @@
         <v>126357434</v>
       </c>
       <c r="B30" t="n">
-        <v>98091</v>
+        <v>98094</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>126358063</v>
       </c>
       <c r="B31" t="n">
-        <v>83222</v>
+        <v>83225</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4205,7 +4205,7 @@
         <v>126357916</v>
       </c>
       <c r="B36" t="n">
-        <v>92629</v>
+        <v>92632</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4417,7 +4417,7 @@
         <v>126357748</v>
       </c>
       <c r="B38" t="n">
-        <v>80356</v>
+        <v>80359</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4629,7 +4629,7 @@
         <v>126358040</v>
       </c>
       <c r="B40" t="n">
-        <v>83235</v>
+        <v>83238</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 8219-2025 artfynd.xlsx
+++ b/artfynd/A 8219-2025 artfynd.xlsx
@@ -3576,7 +3576,7 @@
         <v>126357434</v>
       </c>
       <c r="B30" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>126358063</v>
       </c>
       <c r="B31" t="n">
-        <v>83225</v>
+        <v>83226</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4205,7 +4205,7 @@
         <v>126357916</v>
       </c>
       <c r="B36" t="n">
-        <v>92632</v>
+        <v>92633</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4417,7 +4417,7 @@
         <v>126357748</v>
       </c>
       <c r="B38" t="n">
-        <v>80359</v>
+        <v>80360</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4629,7 +4629,7 @@
         <v>126358040</v>
       </c>
       <c r="B40" t="n">
-        <v>83238</v>
+        <v>83239</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 8219-2025 artfynd.xlsx
+++ b/artfynd/A 8219-2025 artfynd.xlsx
@@ -3576,7 +3576,7 @@
         <v>126357434</v>
       </c>
       <c r="B30" t="n">
-        <v>98095</v>
+        <v>98101</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>126358063</v>
       </c>
       <c r="B31" t="n">
-        <v>83226</v>
+        <v>83232</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4205,7 +4205,7 @@
         <v>126357916</v>
       </c>
       <c r="B36" t="n">
-        <v>92633</v>
+        <v>92639</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4417,7 +4417,7 @@
         <v>126357748</v>
       </c>
       <c r="B38" t="n">
-        <v>80360</v>
+        <v>80366</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4629,7 +4629,7 @@
         <v>126358040</v>
       </c>
       <c r="B40" t="n">
-        <v>83239</v>
+        <v>83245</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 8219-2025 artfynd.xlsx
+++ b/artfynd/A 8219-2025 artfynd.xlsx
@@ -3576,7 +3576,7 @@
         <v>126357434</v>
       </c>
       <c r="B30" t="n">
-        <v>98101</v>
+        <v>98102</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4205,7 +4205,7 @@
         <v>126357916</v>
       </c>
       <c r="B36" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 8219-2025 artfynd.xlsx
+++ b/artfynd/A 8219-2025 artfynd.xlsx
@@ -3576,7 +3576,7 @@
         <v>126357434</v>
       </c>
       <c r="B30" t="n">
-        <v>98102</v>
+        <v>98103</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>126358063</v>
       </c>
       <c r="B31" t="n">
-        <v>83232</v>
+        <v>83233</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4205,7 +4205,7 @@
         <v>126357916</v>
       </c>
       <c r="B36" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4417,7 +4417,7 @@
         <v>126357748</v>
       </c>
       <c r="B38" t="n">
-        <v>80366</v>
+        <v>80367</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4629,7 +4629,7 @@
         <v>126358040</v>
       </c>
       <c r="B40" t="n">
-        <v>83245</v>
+        <v>83246</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 8219-2025 artfynd.xlsx
+++ b/artfynd/A 8219-2025 artfynd.xlsx
@@ -3576,7 +3576,7 @@
         <v>126357434</v>
       </c>
       <c r="B30" t="n">
-        <v>98103</v>
+        <v>98106</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>126358063</v>
       </c>
       <c r="B31" t="n">
-        <v>83233</v>
+        <v>83236</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4205,7 +4205,7 @@
         <v>126357916</v>
       </c>
       <c r="B36" t="n">
-        <v>92641</v>
+        <v>92644</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4417,7 +4417,7 @@
         <v>126357748</v>
       </c>
       <c r="B38" t="n">
-        <v>80367</v>
+        <v>80370</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4629,7 +4629,7 @@
         <v>126358040</v>
       </c>
       <c r="B40" t="n">
-        <v>83246</v>
+        <v>83249</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 8219-2025 artfynd.xlsx
+++ b/artfynd/A 8219-2025 artfynd.xlsx
@@ -3576,7 +3576,7 @@
         <v>126357434</v>
       </c>
       <c r="B30" t="n">
-        <v>98106</v>
+        <v>98112</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>126358063</v>
       </c>
       <c r="B31" t="n">
-        <v>83236</v>
+        <v>83238</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4205,7 +4205,7 @@
         <v>126357916</v>
       </c>
       <c r="B36" t="n">
-        <v>92644</v>
+        <v>92650</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4417,7 +4417,7 @@
         <v>126357748</v>
       </c>
       <c r="B38" t="n">
-        <v>80370</v>
+        <v>80372</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4629,7 +4629,7 @@
         <v>126358040</v>
       </c>
       <c r="B40" t="n">
-        <v>83249</v>
+        <v>83251</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 8219-2025 artfynd.xlsx
+++ b/artfynd/A 8219-2025 artfynd.xlsx
@@ -3576,7 +3576,7 @@
         <v>126357434</v>
       </c>
       <c r="B30" t="n">
-        <v>98112</v>
+        <v>98115</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>126358063</v>
       </c>
       <c r="B31" t="n">
-        <v>83238</v>
+        <v>83241</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4205,7 +4205,7 @@
         <v>126357916</v>
       </c>
       <c r="B36" t="n">
-        <v>92650</v>
+        <v>92653</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4417,7 +4417,7 @@
         <v>126357748</v>
       </c>
       <c r="B38" t="n">
-        <v>80372</v>
+        <v>80375</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4629,7 +4629,7 @@
         <v>126358040</v>
       </c>
       <c r="B40" t="n">
-        <v>83251</v>
+        <v>83254</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 8219-2025 artfynd.xlsx
+++ b/artfynd/A 8219-2025 artfynd.xlsx
@@ -3576,7 +3576,7 @@
         <v>126357434</v>
       </c>
       <c r="B30" t="n">
-        <v>98115</v>
+        <v>98120</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>126358063</v>
       </c>
       <c r="B31" t="n">
-        <v>83241</v>
+        <v>83246</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4205,7 +4205,7 @@
         <v>126357916</v>
       </c>
       <c r="B36" t="n">
-        <v>92653</v>
+        <v>92658</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4417,7 +4417,7 @@
         <v>126357748</v>
       </c>
       <c r="B38" t="n">
-        <v>80375</v>
+        <v>80380</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4629,7 +4629,7 @@
         <v>126358040</v>
       </c>
       <c r="B40" t="n">
-        <v>83254</v>
+        <v>83259</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 8219-2025 artfynd.xlsx
+++ b/artfynd/A 8219-2025 artfynd.xlsx
@@ -3576,7 +3576,7 @@
         <v>126357434</v>
       </c>
       <c r="B30" t="n">
-        <v>98120</v>
+        <v>98122</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>126358063</v>
       </c>
       <c r="B31" t="n">
-        <v>83246</v>
+        <v>83248</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4205,7 +4205,7 @@
         <v>126357916</v>
       </c>
       <c r="B36" t="n">
-        <v>92658</v>
+        <v>92660</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4417,7 +4417,7 @@
         <v>126357748</v>
       </c>
       <c r="B38" t="n">
-        <v>80380</v>
+        <v>80382</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4629,7 +4629,7 @@
         <v>126358040</v>
       </c>
       <c r="B40" t="n">
-        <v>83259</v>
+        <v>83261</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 8219-2025 artfynd.xlsx
+++ b/artfynd/A 8219-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY95"/>
+  <dimension ref="A1:AY84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125605476</v>
+        <v>126355489</v>
       </c>
       <c r="B2" t="n">
-        <v>91252</v>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Järnforsen, Ly lm</t>
+          <t>Järnforsen, Järnforsen, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>559981</v>
+        <v>559858</v>
       </c>
       <c r="R2" t="n">
-        <v>7309888</v>
+        <v>7309831</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -756,26 +756,31 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Bördig grannaturskog vid bäckravin</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126355483</v>
+        <v>125605476</v>
       </c>
       <c r="B3" t="n">
-        <v>91699</v>
+        <v>91923</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,34 +788,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1209</v>
+        <v>1204</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Järnforsen, Järnforsen, Ly lm</t>
+          <t>Järnforsen, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>559858</v>
+        <v>559981</v>
       </c>
       <c r="R3" t="n">
-        <v>7309831</v>
+        <v>7309888</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -837,12 +842,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -853,31 +858,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Bördig grannaturskog vid bäckravin</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126355489</v>
+        <v>126355483</v>
       </c>
       <c r="B4" t="n">
-        <v>91541</v>
+        <v>92369</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -976,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126356440</v>
+        <v>126355571</v>
       </c>
       <c r="B5" t="n">
-        <v>91541</v>
+        <v>97358</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,21 +987,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>559675</v>
+        <v>559812</v>
       </c>
       <c r="R5" t="n">
-        <v>7310094</v>
+        <v>7309847</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1060,7 +1060,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Bördig grannaturskog i brant terräng</t>
+          <t>Bördig grannaturskog vid bäckravin</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1078,10 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126356815</v>
+        <v>126356440</v>
       </c>
       <c r="B6" t="n">
-        <v>91259</v>
+        <v>92208</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1089,21 +1089,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>559785</v>
+        <v>559675</v>
       </c>
       <c r="R6" t="n">
-        <v>7310073</v>
+        <v>7310094</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126356310</v>
+        <v>126356501</v>
       </c>
       <c r="B7" t="n">
-        <v>91263</v>
+        <v>91905</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>559670</v>
+        <v>559697</v>
       </c>
       <c r="R7" t="n">
-        <v>7310089</v>
+        <v>7310125</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1282,10 +1282,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126355857</v>
+        <v>126356436</v>
       </c>
       <c r="B8" t="n">
-        <v>91259</v>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1293,37 +1293,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Järnforsen, Järnforsen, Ly lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>559755</v>
+        <v>559675</v>
       </c>
       <c r="R8" t="n">
-        <v>7309933</v>
+        <v>7310094</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1364,13 +1361,12 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Yngre, tidigare avverkad/gallrad skog med många lämnade lågor och naturvärdesträd.</t>
+          <t>Bördig grannaturskog i brant terräng</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1388,45 +1384,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126356436</v>
+        <v>126355857</v>
       </c>
       <c r="B9" t="n">
-        <v>91245</v>
+        <v>91923</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Järnforsen, Järnforsen, Ly lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>559675</v>
+        <v>559755</v>
       </c>
       <c r="R9" t="n">
-        <v>7310094</v>
+        <v>7309933</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1467,12 +1466,13 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Bördig grannaturskog i brant terräng</t>
+          <t>Yngre, tidigare avverkad/gallrad skog med många lämnade lågor och naturvärdesträd.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1490,32 +1490,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126356649</v>
+        <v>126356490</v>
       </c>
       <c r="B10" t="n">
-        <v>92180</v>
+        <v>91923</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4769</v>
+        <v>1204</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1525,10 +1525,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>559746</v>
+        <v>559674</v>
       </c>
       <c r="R10" t="n">
-        <v>7310123</v>
+        <v>7310125</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1592,10 +1592,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126355561</v>
+        <v>126356815</v>
       </c>
       <c r="B11" t="n">
-        <v>91605</v>
+        <v>91923</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1603,21 +1603,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2063</v>
+        <v>1204</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1627,10 +1627,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>559811</v>
+        <v>559785</v>
       </c>
       <c r="R11" t="n">
-        <v>7309839</v>
+        <v>7310073</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1676,7 +1676,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Bördig grannaturskog vid bäckravin</t>
+          <t>Bördig grannaturskog i brant terräng</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1694,32 +1694,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126355571</v>
+        <v>126357095</v>
       </c>
       <c r="B12" t="n">
-        <v>96614</v>
+        <v>91923</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>53</v>
+        <v>1204</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1729,10 +1729,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>559812</v>
+        <v>559794</v>
       </c>
       <c r="R12" t="n">
-        <v>7309847</v>
+        <v>7309792</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Bördig grannaturskog vid bäckravin</t>
+          <t>Bördig grannaturskog i brant terräng</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1796,32 +1796,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126356806</v>
+        <v>126355561</v>
       </c>
       <c r="B13" t="n">
-        <v>91263</v>
+        <v>92283</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>2063</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1831,10 +1831,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>559785</v>
+        <v>559811</v>
       </c>
       <c r="R13" t="n">
-        <v>7310073</v>
+        <v>7309839</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Bördig grannaturskog i brant terräng</t>
+          <t>Bördig grannaturskog vid bäckravin</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -1898,10 +1898,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126355558</v>
+        <v>127275517</v>
       </c>
       <c r="B14" t="n">
-        <v>91263</v>
+        <v>80433</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1909,34 +1909,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Järnforsen, Järnforsen, Ly lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>559811</v>
+        <v>559782</v>
       </c>
       <c r="R14" t="n">
-        <v>7309839</v>
+        <v>7310143</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1963,12 +1966,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1977,33 +1980,29 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Bördig grannaturskog vid bäckravin</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Olle Amcoff</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Olle Amcoff</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126356631</v>
+        <v>126356649</v>
       </c>
       <c r="B15" t="n">
-        <v>98265</v>
+        <v>92869</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2011,21 +2010,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220093</v>
+        <v>4769</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2038,7 +2037,7 @@
         <v>559746</v>
       </c>
       <c r="R15" t="n">
-        <v>7310122</v>
+        <v>7310123</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2102,10 +2101,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126356490</v>
+        <v>127274996</v>
       </c>
       <c r="B16" t="n">
-        <v>91259</v>
+        <v>79413</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2113,21 +2112,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1204</v>
+        <v>6450</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2137,10 +2136,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>559674</v>
+        <v>559768</v>
       </c>
       <c r="R16" t="n">
-        <v>7310125</v>
+        <v>7310262</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2167,12 +2166,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2183,53 +2182,48 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>Bördig grannaturskog i brant terräng</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Olle Amcoff</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Olle Amcoff</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126356501</v>
+        <v>127274895</v>
       </c>
       <c r="B17" t="n">
-        <v>91241</v>
+        <v>80467</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>6463</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2239,13 +2233,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>559697</v>
+        <v>559774</v>
       </c>
       <c r="R17" t="n">
-        <v>7310125</v>
+        <v>7310261</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2269,12 +2263,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2285,69 +2279,61 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>Bördig grannaturskog i brant terräng</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Olle Amcoff</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Olle Amcoff</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127275517</v>
+        <v>126356631</v>
       </c>
       <c r="B18" t="n">
-        <v>80133</v>
+        <v>99022</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>220093</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Järnforsen, Järnforsen, Ly lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>559782</v>
+        <v>559746</v>
       </c>
       <c r="R18" t="n">
-        <v>7310143</v>
+        <v>7310122</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2374,12 +2360,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2388,19 +2374,23 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Bördig grannaturskog i brant terräng</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Olle Amcoff</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Olle Amcoff</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2410,7 +2400,7 @@
         <v>126357389</v>
       </c>
       <c r="B19" t="n">
-        <v>91241</v>
+        <v>91905</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2516,7 +2506,7 @@
         <v>126359227</v>
       </c>
       <c r="B20" t="n">
-        <v>75075</v>
+        <v>83307</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2615,10 +2605,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126359406</v>
+        <v>126358063</v>
       </c>
       <c r="B21" t="n">
-        <v>91263</v>
+        <v>83299</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2626,34 +2616,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>308</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Järnforsen, Järnforsen, Ly lm</t>
+          <t>Jipmomyran, Jipmomyran, Ly lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>560158</v>
+        <v>560358</v>
       </c>
       <c r="R21" t="n">
-        <v>7309726</v>
+        <v>7309396</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2694,12 +2687,13 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Frodig, urskogsartad granskog i brant terräng</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2717,45 +2711,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126357387</v>
+        <v>126358035</v>
       </c>
       <c r="B22" t="n">
-        <v>91263</v>
+        <v>83298</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>492</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Järnforsen, Järnforsen, Ly lm</t>
+          <t>Jipmomyran, Jipmomyran, Ly lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>560081</v>
+        <v>560363</v>
       </c>
       <c r="R22" t="n">
-        <v>7309611</v>
+        <v>7309388</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2796,12 +2793,13 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Bördig grannaturskog i brant terräng</t>
+          <t>Frodig, urskogsartad granskog i brant terräng</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -2819,53 +2817,51 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>66544349</v>
+        <v>126357490</v>
       </c>
       <c r="B23" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92721</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>918</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Djupfors V, Ly lm</t>
+          <t>Järnforsen, Järnforsen, Ly lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>560829.2017359853</v>
+        <v>560120</v>
       </c>
       <c r="R23" t="n">
-        <v>7309021.683959483</v>
+        <v>7309549</v>
       </c>
       <c r="S23" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2889,22 +2885,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2014-09-05</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2014-09-05</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2913,76 +2899,75 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>25090</t>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Frodig, urskogsartad granskog i brant terräng</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Malin Sahlin</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>66544354</v>
+        <v>126357916</v>
       </c>
       <c r="B24" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92721</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>918</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Djupfors V, Ly lm</t>
+          <t>Jipmomyran, Jipmomyran, Ly lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>560817.2887951054</v>
+        <v>560301</v>
       </c>
       <c r="R24" t="n">
-        <v>7309023.475668295</v>
+        <v>7309435</v>
       </c>
       <c r="S24" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3006,22 +2991,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2014-09-05</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2014-09-05</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3030,76 +3005,72 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
-      <c r="AR24" t="inlineStr">
-        <is>
-          <t>25094</t>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Frodig, urskogsartad granskog i brant terräng</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Malin Sahlin</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119301540</v>
+        <v>66544349</v>
       </c>
       <c r="B25" t="n">
-        <v>57257</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>102620</v>
+        <v>1108</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hökuggla</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Surnia ulula</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Järnforsen, Ly lm</t>
+          <t>Djupfors V, Ly lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>559939</v>
+        <v>560829</v>
       </c>
       <c r="R25" t="n">
-        <v>7309726</v>
+        <v>7309022</v>
       </c>
       <c r="S25" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3123,22 +3094,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>18:58</t>
+          <t>2014-09-05</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>18:58</t>
+          <t>2014-09-05</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3149,26 +3110,31 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>25090</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Sonata Isaksson</t>
+          <t>Malin Sahlin</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Sonata Isaksson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126359216</v>
+        <v>126357718</v>
       </c>
       <c r="B26" t="n">
-        <v>91241</v>
+        <v>91905</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3194,16 +3160,19 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Jipmomyran, Jipmomyran, Ly lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>560542</v>
+        <v>560264</v>
       </c>
       <c r="R26" t="n">
-        <v>7309328</v>
+        <v>7309462</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3244,12 +3213,13 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Lövrik grannaturskog</t>
+          <t>Frodig, urskogsartad granskog i brant terräng</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3267,10 +3237,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126357506</v>
+        <v>126359216</v>
       </c>
       <c r="B27" t="n">
-        <v>91241</v>
+        <v>91905</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3298,14 +3268,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Järnforsen, Järnforsen, Ly lm</t>
+          <t>Jipmomyran, Jipmomyran, Ly lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>560120</v>
+        <v>560542</v>
       </c>
       <c r="R27" t="n">
-        <v>7309549</v>
+        <v>7309328</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3351,7 +3321,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Frodig, urskogsartade granskog i brant terräng</t>
+          <t>Lövrik grannaturskog</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3369,10 +3339,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126358404</v>
+        <v>126358040</v>
       </c>
       <c r="B28" t="n">
-        <v>80083</v>
+        <v>83312</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3380,34 +3350,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>1467</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Jipmomyran, Jipmomyran, Ly lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>560173</v>
+        <v>560363</v>
       </c>
       <c r="R28" t="n">
-        <v>7309178</v>
+        <v>7309388</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3448,12 +3421,13 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Lövrik grannaturskog</t>
+          <t>Frodig, urskogsartad granskog i brant terräng</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3471,10 +3445,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126357428</v>
+        <v>126357748</v>
       </c>
       <c r="B29" t="n">
-        <v>80083</v>
+        <v>80433</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3482,34 +3456,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Järnforsen, Järnforsen, Ly lm</t>
+          <t>Jipmomyran, Jipmomyran, Ly lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>560096</v>
+        <v>560277</v>
       </c>
       <c r="R29" t="n">
-        <v>7309597</v>
+        <v>7309435</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3550,12 +3527,13 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Frodig gråalskog vid bäckdråg</t>
+          <t>Frodig, urskogsartad granskog i brant terräng</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3573,49 +3551,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126357434</v>
+        <v>126358410</v>
       </c>
       <c r="B30" t="n">
-        <v>98122</v>
+        <v>80433</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220250</v>
+        <v>2081</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Järnforsen, Järnforsen, Ly lm</t>
+          <t>Jipmomyran, Jipmomyran, Ly lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>560096</v>
+        <v>560173</v>
       </c>
       <c r="R30" t="n">
-        <v>7309597</v>
+        <v>7309178</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3656,13 +3630,12 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Frodig gråalskog vid bäckdråg</t>
+          <t>Lövrik grannaturskog</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3680,32 +3653,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126358063</v>
+        <v>126358290</v>
       </c>
       <c r="B31" t="n">
-        <v>83248</v>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3718,10 +3691,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>560358</v>
+        <v>560224</v>
       </c>
       <c r="R31" t="n">
-        <v>7309396</v>
+        <v>7309210</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3786,10 +3759,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126357705</v>
+        <v>126357428</v>
       </c>
       <c r="B32" t="n">
-        <v>91263</v>
+        <v>80432</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3797,34 +3770,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Jipmomyran, Jipmomyran, Ly lm</t>
+          <t>Järnforsen, Järnforsen, Ly lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>560260</v>
+        <v>560096</v>
       </c>
       <c r="R32" t="n">
-        <v>7309464</v>
+        <v>7309597</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3870,7 +3843,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Frodig, urskogsartade granskog i brant terräng</t>
+          <t>Frodig gråalskog vid bäckdråg</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -3888,10 +3861,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126358410</v>
+        <v>126358030</v>
       </c>
       <c r="B33" t="n">
-        <v>80084</v>
+        <v>80432</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3899,34 +3872,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Jipmomyran, Jipmomyran, Ly lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>560173</v>
+        <v>560363</v>
       </c>
       <c r="R33" t="n">
-        <v>7309178</v>
+        <v>7309388</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3967,12 +3943,13 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Lövrik grannaturskog</t>
+          <t>Frodig, urskogsartad granskog i brant terräng</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -3990,10 +3967,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126358030</v>
+        <v>126358404</v>
       </c>
       <c r="B34" t="n">
-        <v>80117</v>
+        <v>80432</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4019,19 +3996,16 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Jipmomyran, Jipmomyran, Ly lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>560363</v>
+        <v>560173</v>
       </c>
       <c r="R34" t="n">
-        <v>7309388</v>
+        <v>7309178</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4072,13 +4046,12 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>Frodig, urskogsartad granskog i brant terräng</t>
+          <t>Lövrik grannaturskog</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4096,48 +4069,49 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126358035</v>
+        <v>126357434</v>
       </c>
       <c r="B35" t="n">
-        <v>75129</v>
+        <v>98186</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>492</v>
+        <v>220250</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Matteuccia struthiopteris</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(L.) Tod.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Jipmomyran, Jipmomyran, Ly lm</t>
+          <t>Järnforsen, Järnforsen, Ly lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>560363</v>
+        <v>560096</v>
       </c>
       <c r="R35" t="n">
-        <v>7309388</v>
+        <v>7309597</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4184,7 +4158,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>Frodig, urskogsartad granskog i brant terräng</t>
+          <t>Frodig gråalskog vid bäckdråg</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4202,51 +4176,48 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126357916</v>
+        <v>66544351</v>
       </c>
       <c r="B36" t="n">
-        <v>92660</v>
+        <v>92208</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>918</v>
+        <v>658</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Jipmomyran, Jipmomyran, Ly lm</t>
+          <t>Djupfors V, Ly lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>560301</v>
+        <v>560857</v>
       </c>
       <c r="R36" t="n">
-        <v>7309435</v>
+        <v>7309015</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4270,12 +4241,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2014-09-05</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2014-09-05</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4284,56 +4255,55 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
-      <c r="AI36" t="inlineStr">
-        <is>
-          <t>Frodig, urskogsartad granskog i brant terräng</t>
+      <c r="AR36" t="inlineStr">
+        <is>
+          <t>25092</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Malin Sahlin</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126357490</v>
+        <v>126360392</v>
       </c>
       <c r="B37" t="n">
-        <v>92112</v>
+        <v>92208</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>918</v>
+        <v>658</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4342,14 +4312,14 @@
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Järnforsen, Järnforsen, Ly lm</t>
+          <t>Jipmomyran, Jipmomyran, Ly lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>560120</v>
+        <v>560870</v>
       </c>
       <c r="R37" t="n">
-        <v>7309549</v>
+        <v>7309007</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4396,7 +4366,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Frodig, urskogsartad granskog i brant terräng</t>
+          <t>Grannaturskog/gransumpskog</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4414,10 +4384,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126357748</v>
+        <v>66544348</v>
       </c>
       <c r="B38" t="n">
-        <v>80382</v>
+        <v>91905</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4425,40 +4395,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Jipmomyran, Jipmomyran, Ly lm</t>
+          <t>Djupfors V, Ly lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>560277</v>
+        <v>560863</v>
       </c>
       <c r="R38" t="n">
-        <v>7309435</v>
+        <v>7308993</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4482,12 +4449,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2014-09-05</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2014-09-05</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4496,34 +4463,33 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>Frodig, urskogsartad granskog i brant terräng</t>
+      <c r="AR38" t="inlineStr">
+        <is>
+          <t>25089</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Malin Sahlin</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126357718</v>
+        <v>126360330</v>
       </c>
       <c r="B39" t="n">
-        <v>91321</v>
+        <v>91905</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4558,10 +4524,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>560264</v>
+        <v>560893</v>
       </c>
       <c r="R39" t="n">
-        <v>7309462</v>
+        <v>7308996</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4608,7 +4574,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>Frodig, urskogsartad granskog i brant terräng</t>
+          <t>Grannaturskog/gransumpskog</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -4626,10 +4592,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126358040</v>
+        <v>126360636</v>
       </c>
       <c r="B40" t="n">
-        <v>83261</v>
+        <v>91905</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4637,21 +4603,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1467</v>
+        <v>1108</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4664,10 +4630,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>560363</v>
+        <v>560870</v>
       </c>
       <c r="R40" t="n">
-        <v>7309388</v>
+        <v>7309007</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4714,7 +4680,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>Frodig, urskogsartad granskog i brant terräng</t>
+          <t>Grannaturskog/gransumpskog</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -4732,10 +4698,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126358290</v>
+        <v>66544343</v>
       </c>
       <c r="B41" t="n">
-        <v>79014</v>
+        <v>91909</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4743,40 +4709,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Jipmomyran, Jipmomyran, Ly lm</t>
+          <t>Djupfors V, Ly lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>560224</v>
+        <v>560934</v>
       </c>
       <c r="R41" t="n">
-        <v>7309210</v>
+        <v>7308947</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4800,12 +4763,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2014-09-05</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2014-09-05</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4814,39 +4777,33 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>Frodig, urskogsartad granskog i brant terräng</t>
+      <c r="AR41" t="inlineStr">
+        <is>
+          <t>25084</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Malin Sahlin</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>66544347</v>
+        <v>66544345</v>
       </c>
       <c r="B42" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4878,10 +4835,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>560878.5341145619</v>
+        <v>560922</v>
       </c>
       <c r="R42" t="n">
-        <v>7308993.284323963</v>
+        <v>7308957</v>
       </c>
       <c r="S42" t="n">
         <v>50</v>
@@ -4911,21 +4868,11 @@
           <t>2014-09-05</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2014-09-05</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -4937,7 +4884,7 @@
       </c>
       <c r="AR42" t="inlineStr">
         <is>
-          <t>25088</t>
+          <t>25086</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -4955,15 +4902,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>66544345</v>
+        <v>66544347</v>
       </c>
       <c r="B43" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4995,10 +4937,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>560921.9021753618</v>
+        <v>560879</v>
       </c>
       <c r="R43" t="n">
-        <v>7308956.577612261</v>
+        <v>7308993</v>
       </c>
       <c r="S43" t="n">
         <v>50</v>
@@ -5028,21 +4970,11 @@
           <t>2014-09-05</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2014-09-05</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5054,7 +4986,7 @@
       </c>
       <c r="AR43" t="inlineStr">
         <is>
-          <t>25086</t>
+          <t>25088</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5072,15 +5004,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>66544351</v>
+        <v>66544350</v>
       </c>
       <c r="B44" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5088,21 +5015,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5112,10 +5039,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>560857.1901938798</v>
+        <v>560857</v>
       </c>
       <c r="R44" t="n">
-        <v>7309014.91711883</v>
+        <v>7309015</v>
       </c>
       <c r="S44" t="n">
         <v>50</v>
@@ -5145,21 +5072,11 @@
           <t>2014-09-05</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2014-09-05</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5171,7 +5088,7 @@
       </c>
       <c r="AR44" t="inlineStr">
         <is>
-          <t>25092</t>
+          <t>25091</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5189,53 +5106,51 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>66544353</v>
+        <v>126360324</v>
       </c>
       <c r="B45" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Djupfors V, Ly lm</t>
+          <t>Jipmomyran, Jipmomyran, Ly lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>560857.1901938798</v>
+        <v>560893</v>
       </c>
       <c r="R45" t="n">
-        <v>7309014.91711883</v>
+        <v>7308996</v>
       </c>
       <c r="S45" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5259,22 +5174,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2014-09-05</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2014-09-05</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5283,38 +5188,34 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
-      <c r="AR45" t="inlineStr">
-        <is>
-          <t>25093</t>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>Grannaturskog/gransumpskog</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Malin Sahlin</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>66544343</v>
+        <v>126360389</v>
       </c>
       <c r="B46" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5322,37 +5223,40 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Djupfors V, Ly lm</t>
+          <t>Jipmomyran, Jipmomyran, Ly lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>560933.9809844483</v>
+        <v>560870</v>
       </c>
       <c r="R46" t="n">
-        <v>7308947.018279012</v>
+        <v>7309007</v>
       </c>
       <c r="S46" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5376,22 +5280,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2014-09-05</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2014-09-05</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5400,60 +5294,56 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
-      <c r="AR46" t="inlineStr">
-        <is>
-          <t>25084</t>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>Grannaturskog/gransumpskog</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Malin Sahlin</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>66544348</v>
+        <v>66544344</v>
       </c>
       <c r="B47" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92333</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1108</v>
+        <v>4217</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5463,10 +5353,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>560863.3901593408</v>
+        <v>560934</v>
       </c>
       <c r="R47" t="n">
-        <v>7308992.96197705</v>
+        <v>7308947</v>
       </c>
       <c r="S47" t="n">
         <v>50</v>
@@ -5496,21 +5386,11 @@
           <t>2014-09-05</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2014-09-05</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -5522,7 +5402,7 @@
       </c>
       <c r="AR47" t="inlineStr">
         <is>
-          <t>25089</t>
+          <t>25085</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -5540,15 +5420,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>66544344</v>
+        <v>66544353</v>
       </c>
       <c r="B48" t="n">
-        <v>89780</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5556,21 +5431,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4217</v>
+        <v>5447</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5580,10 +5455,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>560933.9809844483</v>
+        <v>560857</v>
       </c>
       <c r="R48" t="n">
-        <v>7308947.018279012</v>
+        <v>7309015</v>
       </c>
       <c r="S48" t="n">
         <v>50</v>
@@ -5613,21 +5488,11 @@
           <t>2014-09-05</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2014-09-05</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -5639,7 +5504,7 @@
       </c>
       <c r="AR48" t="inlineStr">
         <is>
-          <t>25085</t>
+          <t>25093</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -5660,16 +5525,11 @@
         <v>66544346</v>
       </c>
       <c r="B49" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -5697,10 +5557,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>560921.9021753618</v>
+        <v>560922</v>
       </c>
       <c r="R49" t="n">
-        <v>7308956.577612261</v>
+        <v>7308957</v>
       </c>
       <c r="S49" t="n">
         <v>50</v>
@@ -5730,19 +5590,9 @@
           <t>2014-09-05</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2014-09-05</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5774,37 +5624,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>66544350</v>
+        <v>66544342</v>
       </c>
       <c r="B50" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5814,10 +5659,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>560857.1901938798</v>
+        <v>560960</v>
       </c>
       <c r="R50" t="n">
-        <v>7309014.91711883</v>
+        <v>7308918</v>
       </c>
       <c r="S50" t="n">
         <v>50</v>
@@ -5847,21 +5692,11 @@
           <t>2014-09-05</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2014-09-05</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -5873,7 +5708,7 @@
       </c>
       <c r="AR50" t="inlineStr">
         <is>
-          <t>25091</t>
+          <t>25083</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -5891,48 +5726,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126360335</v>
+        <v>126361127</v>
       </c>
       <c r="B51" t="n">
-        <v>91263</v>
+        <v>83298</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>492</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Jipmomyran, Jipmomyran, Ly lm</t>
+          <t>Djupselet, Djupselet, Ly lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>560893</v>
+        <v>561403</v>
       </c>
       <c r="R51" t="n">
-        <v>7308996</v>
+        <v>7308978</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5973,13 +5805,12 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>Grannaturskog/gransumpskog</t>
+          <t>Bördig, grovvuxen grannaturskog</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -5997,10 +5828,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126360324</v>
+        <v>66544648</v>
       </c>
       <c r="B52" t="n">
-        <v>91245</v>
+        <v>89292</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6008,40 +5839,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Jipmomyran, Jipmomyran, Ly lm</t>
+          <t>Djupfors V, Ly lm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>560893</v>
+        <v>561140</v>
       </c>
       <c r="R52" t="n">
-        <v>7308996</v>
+        <v>7308737</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6065,12 +5893,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2014-09-05</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2014-09-05</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6079,34 +5907,33 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
-      <c r="AI52" t="inlineStr">
-        <is>
-          <t>Grannaturskog/gransumpskog</t>
+      <c r="AR52" t="inlineStr">
+        <is>
+          <t>25371</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Malin Sahlin</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Via Malin Sahlin</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126360636</v>
+        <v>66544623</v>
       </c>
       <c r="B53" t="n">
-        <v>91241</v>
+        <v>92208</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6114,40 +5941,41 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1108</v>
+        <v>658</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Jipmomyran, Jipmomyran, Ly lm</t>
+          <t>Djupfors V, Ly lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>560870</v>
+        <v>561045</v>
       </c>
       <c r="R53" t="n">
-        <v>7309007</v>
+        <v>7308850</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6171,12 +5999,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2014-09-05</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2014-09-05</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6185,34 +6013,33 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
-      <c r="AI53" t="inlineStr">
-        <is>
-          <t>Grannaturskog/gransumpskog</t>
+      <c r="AR53" t="inlineStr">
+        <is>
+          <t>25347</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Malin Sahlin</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Via Malin Sahlin</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126360392</v>
+        <v>66544638</v>
       </c>
       <c r="B54" t="n">
-        <v>91541</v>
+        <v>92208</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6229,31 +6056,28 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Jipmomyran, Jipmomyran, Ly lm</t>
+          <t>Djupfors V, Ly lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>560870</v>
+        <v>561100</v>
       </c>
       <c r="R54" t="n">
-        <v>7309007</v>
+        <v>7308822</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6277,12 +6101,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2014-09-05</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2014-09-05</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6291,75 +6115,71 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
-      <c r="AI54" t="inlineStr">
-        <is>
-          <t>Grannaturskog/gransumpskog</t>
+      <c r="AR54" t="inlineStr">
+        <is>
+          <t>25361</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Malin Sahlin</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Via Malin Sahlin</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126360389</v>
+        <v>66544645</v>
       </c>
       <c r="B55" t="n">
-        <v>91699</v>
+        <v>92208</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Jipmomyran, Jipmomyran, Ly lm</t>
+          <t>Djupfors V, Ly lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>560870</v>
+        <v>561119</v>
       </c>
       <c r="R55" t="n">
-        <v>7309007</v>
+        <v>7308748</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6383,12 +6203,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2014-09-05</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2014-09-05</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6397,34 +6217,33 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
-      <c r="AI55" t="inlineStr">
-        <is>
-          <t>Grannaturskog/gransumpskog</t>
+      <c r="AR55" t="inlineStr">
+        <is>
+          <t>25368</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Malin Sahlin</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Via Malin Sahlin</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126360330</v>
+        <v>66544651</v>
       </c>
       <c r="B56" t="n">
-        <v>91241</v>
+        <v>92208</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6432,40 +6251,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1108</v>
+        <v>658</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Jipmomyran, Jipmomyran, Ly lm</t>
+          <t>Djupfors V, Ly lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>560893</v>
+        <v>561140</v>
       </c>
       <c r="R56" t="n">
-        <v>7308996</v>
+        <v>7308737</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6489,12 +6305,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2014-09-05</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2014-09-05</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6503,61 +6319,55 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
-      <c r="AI56" t="inlineStr">
-        <is>
-          <t>Grannaturskog/gransumpskog</t>
+      <c r="AR56" t="inlineStr">
+        <is>
+          <t>25373</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Malin Sahlin</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Via Malin Sahlin</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>66544342</v>
+        <v>66544633</v>
       </c>
       <c r="B57" t="n">
-        <v>90074</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92721</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3298</v>
+        <v>918</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6567,10 +6377,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>560960.3945341655</v>
+        <v>561072</v>
       </c>
       <c r="R57" t="n">
-        <v>7308918.130968786</v>
+        <v>7308827</v>
       </c>
       <c r="S57" t="n">
         <v>50</v>
@@ -6600,21 +6410,11 @@
           <t>2014-09-05</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2014-09-05</t>
         </is>
       </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -6626,7 +6426,7 @@
       </c>
       <c r="AR57" t="inlineStr">
         <is>
-          <t>25083</t>
+          <t>25356</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -6637,22 +6437,17 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Via Malin Sahlin</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>66544630</v>
+        <v>66544628</v>
       </c>
       <c r="B58" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6684,10 +6479,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>561061.5146522231</v>
+        <v>561045</v>
       </c>
       <c r="R58" t="n">
-        <v>7308842.570840668</v>
+        <v>7308850</v>
       </c>
       <c r="S58" t="n">
         <v>50</v>
@@ -6717,21 +6512,11 @@
           <t>2014-09-05</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2014-09-05</t>
         </is>
       </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -6743,7 +6528,7 @@
       </c>
       <c r="AR58" t="inlineStr">
         <is>
-          <t>25353</t>
+          <t>25351</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -6761,15 +6546,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>66544637</v>
+        <v>66544630</v>
       </c>
       <c r="B59" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6777,21 +6557,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6801,10 +6581,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>561099.626093693</v>
+        <v>561062</v>
       </c>
       <c r="R59" t="n">
-        <v>7308822.114403572</v>
+        <v>7308843</v>
       </c>
       <c r="S59" t="n">
         <v>50</v>
@@ -6834,21 +6614,11 @@
           <t>2014-09-05</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2014-09-05</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
@@ -6860,7 +6630,7 @@
       </c>
       <c r="AR59" t="inlineStr">
         <is>
-          <t>25360</t>
+          <t>25353</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -6878,37 +6648,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>66544633</v>
+        <v>66544627</v>
       </c>
       <c r="B60" t="n">
-        <v>90160</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>918</v>
+        <v>1202</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6918,10 +6683,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>561072.4974219487</v>
+        <v>561045</v>
       </c>
       <c r="R60" t="n">
-        <v>7308826.852570722</v>
+        <v>7308850</v>
       </c>
       <c r="S60" t="n">
         <v>50</v>
@@ -6951,21 +6716,11 @@
           <t>2014-09-05</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2014-09-05</t>
         </is>
       </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
@@ -6977,7 +6732,7 @@
       </c>
       <c r="AR60" t="inlineStr">
         <is>
-          <t>25356</t>
+          <t>25350</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -6995,15 +6750,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>66544627</v>
+        <v>66544640</v>
       </c>
       <c r="B61" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7035,10 +6785,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>561044.5755368763</v>
+        <v>561100</v>
       </c>
       <c r="R61" t="n">
-        <v>7308849.572017924</v>
+        <v>7308822</v>
       </c>
       <c r="S61" t="n">
         <v>50</v>
@@ -7068,21 +6818,11 @@
           <t>2014-09-05</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2014-09-05</t>
         </is>
       </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
@@ -7094,7 +6834,7 @@
       </c>
       <c r="AR61" t="inlineStr">
         <is>
-          <t>25350</t>
+          <t>25363</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7112,37 +6852,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>66544641</v>
+        <v>66544646</v>
       </c>
       <c r="B62" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7152,10 +6887,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>561099.626093693</v>
+        <v>561119</v>
       </c>
       <c r="R62" t="n">
-        <v>7308822.114403572</v>
+        <v>7308748</v>
       </c>
       <c r="S62" t="n">
         <v>50</v>
@@ -7185,21 +6920,11 @@
           <t>2014-09-05</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2014-09-05</t>
         </is>
       </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
@@ -7211,7 +6936,7 @@
       </c>
       <c r="AR62" t="inlineStr">
         <is>
-          <t>25364</t>
+          <t>25369</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -7229,54 +6954,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>66544639</v>
+        <v>66544629</v>
       </c>
       <c r="B63" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Djupfors V, Ly lm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>561099.626093693</v>
+        <v>561062</v>
       </c>
       <c r="R63" t="n">
-        <v>7308822.114403572</v>
+        <v>7308843</v>
       </c>
       <c r="S63" t="n">
         <v>50</v>
@@ -7306,21 +7022,11 @@
           <t>2014-09-05</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2014-09-05</t>
         </is>
       </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
@@ -7332,7 +7038,7 @@
       </c>
       <c r="AR63" t="inlineStr">
         <is>
-          <t>25362</t>
+          <t>25352</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -7350,53 +7056,48 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>66544619</v>
+        <v>126361165</v>
       </c>
       <c r="B64" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Djupfors V, Ly lm</t>
+          <t>Djupselet, Djupselet, Ly lm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>561027.2184662716</v>
+        <v>561436</v>
       </c>
       <c r="R64" t="n">
-        <v>7308856.973397947</v>
+        <v>7308968</v>
       </c>
       <c r="S64" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7420,22 +7121,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2014-09-05</t>
-        </is>
-      </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2014-09-05</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7447,35 +7138,30 @@
       <c r="AG64" t="b">
         <v>0</v>
       </c>
-      <c r="AR64" t="inlineStr">
-        <is>
-          <t>25343</t>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>Bördig, grovvuxen grannaturskog</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Malin Sahlin</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Via Malin Sahlin</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>66544626</v>
+        <v>66544641</v>
       </c>
       <c r="B65" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7483,38 +7169,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Djupfors V, Ly lm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>561044.5755368763</v>
+        <v>561100</v>
       </c>
       <c r="R65" t="n">
-        <v>7308849.572017924</v>
+        <v>7308822</v>
       </c>
       <c r="S65" t="n">
         <v>50</v>
@@ -7544,21 +7226,11 @@
           <t>2014-09-05</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2014-09-05</t>
         </is>
       </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -7570,7 +7242,7 @@
       </c>
       <c r="AR65" t="inlineStr">
         <is>
-          <t>25349</t>
+          <t>25364</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -7588,15 +7260,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>66544638</v>
+        <v>66544619</v>
       </c>
       <c r="B66" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7604,21 +7271,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7628,10 +7295,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>561099.626093693</v>
+        <v>561027</v>
       </c>
       <c r="R66" t="n">
-        <v>7308822.114403572</v>
+        <v>7308857</v>
       </c>
       <c r="S66" t="n">
         <v>50</v>
@@ -7661,21 +7328,11 @@
           <t>2014-09-05</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2014-09-05</t>
         </is>
       </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -7687,7 +7344,7 @@
       </c>
       <c r="AR66" t="inlineStr">
         <is>
-          <t>25361</t>
+          <t>25343</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -7705,15 +7362,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>66544620</v>
+        <v>66544632</v>
       </c>
       <c r="B67" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7721,21 +7373,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7745,10 +7397,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>561027.2184662716</v>
+        <v>561062</v>
       </c>
       <c r="R67" t="n">
-        <v>7308856.973397947</v>
+        <v>7308843</v>
       </c>
       <c r="S67" t="n">
         <v>50</v>
@@ -7778,21 +7430,11 @@
           <t>2014-09-05</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2014-09-05</t>
         </is>
       </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -7804,7 +7446,7 @@
       </c>
       <c r="AR67" t="inlineStr">
         <is>
-          <t>25344</t>
+          <t>25355</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -7822,15 +7464,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>66544640</v>
+        <v>66544636</v>
       </c>
       <c r="B68" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7838,21 +7475,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7862,10 +7499,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>561099.626093693</v>
+        <v>561072</v>
       </c>
       <c r="R68" t="n">
-        <v>7308822.114403572</v>
+        <v>7308827</v>
       </c>
       <c r="S68" t="n">
         <v>50</v>
@@ -7895,21 +7532,11 @@
           <t>2014-09-05</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2014-09-05</t>
         </is>
       </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -7921,7 +7548,7 @@
       </c>
       <c r="AR68" t="inlineStr">
         <is>
-          <t>25363</t>
+          <t>25359</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -7939,15 +7566,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>66544649</v>
+        <v>66544644</v>
       </c>
       <c r="B69" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7979,10 +7601,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>561139.9464785276</v>
+        <v>561108</v>
       </c>
       <c r="R69" t="n">
-        <v>7308736.66569937</v>
+        <v>7308772</v>
       </c>
       <c r="S69" t="n">
         <v>50</v>
@@ -8012,21 +7634,11 @@
           <t>2014-09-05</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2014-09-05</t>
         </is>
       </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -8038,7 +7650,7 @@
       </c>
       <c r="AR69" t="inlineStr">
         <is>
-          <t>25372</t>
+          <t>25367</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8056,15 +7668,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>66544642</v>
+        <v>66544649</v>
       </c>
       <c r="B70" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8072,21 +7679,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8096,10 +7703,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>561096.8231878708</v>
+        <v>561140</v>
       </c>
       <c r="R70" t="n">
-        <v>7308799.96586439</v>
+        <v>7308737</v>
       </c>
       <c r="S70" t="n">
         <v>50</v>
@@ -8129,21 +7736,11 @@
           <t>2014-09-05</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2014-09-05</t>
         </is>
       </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
@@ -8155,7 +7752,7 @@
       </c>
       <c r="AR70" t="inlineStr">
         <is>
-          <t>25365</t>
+          <t>25372</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -8173,15 +7770,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>66544623</v>
+        <v>126361121</v>
       </c>
       <c r="B71" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8189,41 +7781,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>658</v>
+        <v>1467</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Djupfors V, Ly lm</t>
+          <t>Djupselet, Djupselet, Ly lm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>561044.5755368763</v>
+        <v>561403</v>
       </c>
       <c r="R71" t="n">
-        <v>7308849.572017924</v>
+        <v>7308978</v>
       </c>
       <c r="S71" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8247,22 +7835,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2014-09-05</t>
-        </is>
-      </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2014-09-05</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8274,57 +7852,52 @@
       <c r="AG71" t="b">
         <v>0</v>
       </c>
-      <c r="AR71" t="inlineStr">
-        <is>
-          <t>25347</t>
+      <c r="AI71" t="inlineStr">
+        <is>
+          <t>Bördig, grovvuxen grannaturskog</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Malin Sahlin</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Via Malin Sahlin</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>66544341</v>
+        <v>66544634</v>
       </c>
       <c r="B72" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8334,10 +7907,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>561008.5625325058</v>
+        <v>561072</v>
       </c>
       <c r="R72" t="n">
-        <v>7308906.069035768</v>
+        <v>7308827</v>
       </c>
       <c r="S72" t="n">
         <v>50</v>
@@ -8367,21 +7940,11 @@
           <t>2014-09-05</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2014-09-05</t>
         </is>
       </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
@@ -8393,7 +7956,7 @@
       </c>
       <c r="AR72" t="inlineStr">
         <is>
-          <t>25082</t>
+          <t>25357</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -8404,26 +7967,21 @@
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Via Malin Sahlin</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>66544622</v>
+        <v>66544341</v>
       </c>
       <c r="B73" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
@@ -8444,21 +8002,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Djupfors V, Ly lm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>561027.2184662716</v>
+        <v>561009</v>
       </c>
       <c r="R73" t="n">
-        <v>7308856.973397947</v>
+        <v>7308906</v>
       </c>
       <c r="S73" t="n">
         <v>50</v>
@@ -8488,21 +8042,11 @@
           <t>2014-09-05</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2014-09-05</t>
         </is>
       </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
@@ -8514,7 +8058,7 @@
       </c>
       <c r="AR73" t="inlineStr">
         <is>
-          <t>25346</t>
+          <t>25082</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -8525,57 +8069,56 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Via Malin Sahlin</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>66544651</v>
+        <v>66544622</v>
       </c>
       <c r="B74" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Djupfors V, Ly lm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>561139.9464785276</v>
+        <v>561027</v>
       </c>
       <c r="R74" t="n">
-        <v>7308736.66569937</v>
+        <v>7308857</v>
       </c>
       <c r="S74" t="n">
         <v>50</v>
@@ -8605,21 +8148,11 @@
           <t>2014-09-05</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2014-09-05</t>
         </is>
       </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
@@ -8631,7 +8164,7 @@
       </c>
       <c r="AR74" t="inlineStr">
         <is>
-          <t>25373</t>
+          <t>25346</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -8649,19 +8182,14 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>66544631</v>
+        <v>66544626</v>
       </c>
       <c r="B75" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
@@ -8693,10 +8221,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>561061.5146522231</v>
+        <v>561045</v>
       </c>
       <c r="R75" t="n">
-        <v>7308842.570840668</v>
+        <v>7308850</v>
       </c>
       <c r="S75" t="n">
         <v>50</v>
@@ -8726,21 +8254,11 @@
           <t>2014-09-05</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2014-09-05</t>
         </is>
       </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
@@ -8752,7 +8270,7 @@
       </c>
       <c r="AR75" t="inlineStr">
         <is>
-          <t>25354</t>
+          <t>25349</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -8770,50 +8288,49 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>66544621</v>
+        <v>66544631</v>
       </c>
       <c r="B76" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Djupfors V, Ly lm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>561027.2184662716</v>
+        <v>561062</v>
       </c>
       <c r="R76" t="n">
-        <v>7308856.973397947</v>
+        <v>7308843</v>
       </c>
       <c r="S76" t="n">
         <v>50</v>
@@ -8843,21 +8360,11 @@
           <t>2014-09-05</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2014-09-05</t>
         </is>
       </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
@@ -8869,7 +8376,7 @@
       </c>
       <c r="AR76" t="inlineStr">
         <is>
-          <t>25345</t>
+          <t>25354</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -8887,19 +8394,14 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>66544647</v>
+        <v>66544635</v>
       </c>
       <c r="B77" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
@@ -8931,10 +8433,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>561118.808368561</v>
+        <v>561072</v>
       </c>
       <c r="R77" t="n">
-        <v>7308748.485677995</v>
+        <v>7308827</v>
       </c>
       <c r="S77" t="n">
         <v>50</v>
@@ -8964,21 +8466,11 @@
           <t>2014-09-05</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2014-09-05</t>
         </is>
       </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
@@ -8990,7 +8482,7 @@
       </c>
       <c r="AR77" t="inlineStr">
         <is>
-          <t>25370</t>
+          <t>25358</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -9008,19 +8500,14 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>66544635</v>
+        <v>66544639</v>
       </c>
       <c r="B78" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
@@ -9052,10 +8539,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>561072.4974219487</v>
+        <v>561100</v>
       </c>
       <c r="R78" t="n">
-        <v>7308826.852570722</v>
+        <v>7308822</v>
       </c>
       <c r="S78" t="n">
         <v>50</v>
@@ -9085,21 +8572,11 @@
           <t>2014-09-05</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2014-09-05</t>
         </is>
       </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
@@ -9111,7 +8588,7 @@
       </c>
       <c r="AR78" t="inlineStr">
         <is>
-          <t>25358</t>
+          <t>25362</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -9129,50 +8606,49 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>66544648</v>
+        <v>66544643</v>
       </c>
       <c r="B79" t="n">
-        <v>85703</v>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Djupfors V, Ly lm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>561139.9464785276</v>
+        <v>561108</v>
       </c>
       <c r="R79" t="n">
-        <v>7308736.66569937</v>
+        <v>7308772</v>
       </c>
       <c r="S79" t="n">
         <v>50</v>
@@ -9202,21 +8678,11 @@
           <t>2014-09-05</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2014-09-05</t>
         </is>
       </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
@@ -9228,7 +8694,7 @@
       </c>
       <c r="AR79" t="inlineStr">
         <is>
-          <t>25371</t>
+          <t>25366</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -9246,50 +8712,49 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>66544628</v>
+        <v>66544647</v>
       </c>
       <c r="B80" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Djupfors V, Ly lm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>561044.5755368763</v>
+        <v>561119</v>
       </c>
       <c r="R80" t="n">
-        <v>7308849.572017924</v>
+        <v>7308748</v>
       </c>
       <c r="S80" t="n">
         <v>50</v>
@@ -9319,21 +8784,11 @@
           <t>2014-09-05</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2014-09-05</t>
         </is>
       </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
@@ -9345,7 +8800,7 @@
       </c>
       <c r="AR80" t="inlineStr">
         <is>
-          <t>25351</t>
+          <t>25370</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -9363,15 +8818,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>66544645</v>
+        <v>66544621</v>
       </c>
       <c r="B81" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9379,21 +8829,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9403,10 +8853,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>561118.808368561</v>
+        <v>561027</v>
       </c>
       <c r="R81" t="n">
-        <v>7308748.485677995</v>
+        <v>7308857</v>
       </c>
       <c r="S81" t="n">
         <v>50</v>
@@ -9436,21 +8886,11 @@
           <t>2014-09-05</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2014-09-05</t>
         </is>
       </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
@@ -9462,7 +8902,7 @@
       </c>
       <c r="AR81" t="inlineStr">
         <is>
-          <t>25368</t>
+          <t>25345</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -9480,15 +8920,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>66544636</v>
+        <v>66544625</v>
       </c>
       <c r="B82" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9496,21 +8931,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9520,10 +8955,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>561072.4974219487</v>
+        <v>561045</v>
       </c>
       <c r="R82" t="n">
-        <v>7308826.852570722</v>
+        <v>7308850</v>
       </c>
       <c r="S82" t="n">
         <v>50</v>
@@ -9553,21 +8988,11 @@
           <t>2014-09-05</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2014-09-05</t>
         </is>
       </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
@@ -9579,7 +9004,7 @@
       </c>
       <c r="AR82" t="inlineStr">
         <is>
-          <t>25359</t>
+          <t>25348</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -9597,37 +9022,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>66544634</v>
+        <v>66544653</v>
       </c>
       <c r="B83" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5447</v>
+        <v>1108</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9637,10 +9057,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>561072.4974219487</v>
+        <v>561132</v>
       </c>
       <c r="R83" t="n">
-        <v>7308826.852570722</v>
+        <v>7308696</v>
       </c>
       <c r="S83" t="n">
         <v>50</v>
@@ -9670,21 +9090,11 @@
           <t>2014-09-05</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2014-09-05</t>
         </is>
       </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
@@ -9696,7 +9106,7 @@
       </c>
       <c r="AR83" t="inlineStr">
         <is>
-          <t>25357</t>
+          <t>25375</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -9714,15 +9124,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>66544646</v>
+        <v>66544652</v>
       </c>
       <c r="B84" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9730,21 +9135,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9754,10 +9159,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>561118.808368561</v>
+        <v>561132</v>
       </c>
       <c r="R84" t="n">
-        <v>7308748.485677995</v>
+        <v>7308696</v>
       </c>
       <c r="S84" t="n">
         <v>50</v>
@@ -9787,21 +9192,11 @@
           <t>2014-09-05</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2014-09-05</t>
         </is>
       </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
@@ -9813,7 +9208,7 @@
       </c>
       <c r="AR84" t="inlineStr">
         <is>
-          <t>25369</t>
+          <t>25374</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -9828,1237 +9223,6 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" t="n">
-        <v>66544632</v>
-      </c>
-      <c r="B85" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E85" t="n">
-        <v>1312</v>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>Gammelgransskål</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>Pseudographis pinicola</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
-      <c r="P85" t="inlineStr">
-        <is>
-          <t>Djupfors V, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q85" t="n">
-        <v>561061.5146522231</v>
-      </c>
-      <c r="R85" t="n">
-        <v>7308842.570840668</v>
-      </c>
-      <c r="S85" t="n">
-        <v>50</v>
-      </c>
-      <c r="T85" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U85" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="V85" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W85" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="Y85" t="inlineStr">
-        <is>
-          <t>2014-09-05</t>
-        </is>
-      </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA85" t="inlineStr">
-        <is>
-          <t>2014-09-05</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD85" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE85" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG85" t="b">
-        <v>0</v>
-      </c>
-      <c r="AR85" t="inlineStr">
-        <is>
-          <t>25355</t>
-        </is>
-      </c>
-      <c r="AT85" t="inlineStr"/>
-      <c r="AW85" t="inlineStr">
-        <is>
-          <t>Malin Sahlin</t>
-        </is>
-      </c>
-      <c r="AX85" t="inlineStr">
-        <is>
-          <t>Via Malin Sahlin</t>
-        </is>
-      </c>
-      <c r="AY85" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" t="n">
-        <v>66544625</v>
-      </c>
-      <c r="B86" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E86" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
-      <c r="P86" t="inlineStr">
-        <is>
-          <t>Djupfors V, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q86" t="n">
-        <v>561044.5755368763</v>
-      </c>
-      <c r="R86" t="n">
-        <v>7308849.572017924</v>
-      </c>
-      <c r="S86" t="n">
-        <v>50</v>
-      </c>
-      <c r="T86" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U86" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="V86" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W86" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="Y86" t="inlineStr">
-        <is>
-          <t>2014-09-05</t>
-        </is>
-      </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA86" t="inlineStr">
-        <is>
-          <t>2014-09-05</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD86" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE86" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG86" t="b">
-        <v>0</v>
-      </c>
-      <c r="AR86" t="inlineStr">
-        <is>
-          <t>25348</t>
-        </is>
-      </c>
-      <c r="AT86" t="inlineStr"/>
-      <c r="AW86" t="inlineStr">
-        <is>
-          <t>Malin Sahlin</t>
-        </is>
-      </c>
-      <c r="AX86" t="inlineStr">
-        <is>
-          <t>Via Malin Sahlin</t>
-        </is>
-      </c>
-      <c r="AY86" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" t="n">
-        <v>66544643</v>
-      </c>
-      <c r="B87" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E87" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="P87" t="inlineStr">
-        <is>
-          <t>Djupfors V, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q87" t="n">
-        <v>561108.4689856211</v>
-      </c>
-      <c r="R87" t="n">
-        <v>7308772.399080777</v>
-      </c>
-      <c r="S87" t="n">
-        <v>50</v>
-      </c>
-      <c r="T87" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U87" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="V87" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W87" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="Y87" t="inlineStr">
-        <is>
-          <t>2014-09-05</t>
-        </is>
-      </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA87" t="inlineStr">
-        <is>
-          <t>2014-09-05</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD87" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE87" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG87" t="b">
-        <v>0</v>
-      </c>
-      <c r="AR87" t="inlineStr">
-        <is>
-          <t>25366</t>
-        </is>
-      </c>
-      <c r="AT87" t="inlineStr"/>
-      <c r="AW87" t="inlineStr">
-        <is>
-          <t>Malin Sahlin</t>
-        </is>
-      </c>
-      <c r="AX87" t="inlineStr">
-        <is>
-          <t>Via Malin Sahlin</t>
-        </is>
-      </c>
-      <c r="AY87" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" t="n">
-        <v>66544644</v>
-      </c>
-      <c r="B88" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E88" t="n">
-        <v>1312</v>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>Gammelgransskål</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>Pseudographis pinicola</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
-      <c r="P88" t="inlineStr">
-        <is>
-          <t>Djupfors V, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q88" t="n">
-        <v>561108.4689856211</v>
-      </c>
-      <c r="R88" t="n">
-        <v>7308772.399080777</v>
-      </c>
-      <c r="S88" t="n">
-        <v>50</v>
-      </c>
-      <c r="T88" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U88" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="V88" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W88" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="Y88" t="inlineStr">
-        <is>
-          <t>2014-09-05</t>
-        </is>
-      </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA88" t="inlineStr">
-        <is>
-          <t>2014-09-05</t>
-        </is>
-      </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD88" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE88" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG88" t="b">
-        <v>0</v>
-      </c>
-      <c r="AR88" t="inlineStr">
-        <is>
-          <t>25367</t>
-        </is>
-      </c>
-      <c r="AT88" t="inlineStr"/>
-      <c r="AW88" t="inlineStr">
-        <is>
-          <t>Malin Sahlin</t>
-        </is>
-      </c>
-      <c r="AX88" t="inlineStr">
-        <is>
-          <t>Via Malin Sahlin</t>
-        </is>
-      </c>
-      <c r="AY88" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" t="n">
-        <v>66544629</v>
-      </c>
-      <c r="B89" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E89" t="n">
-        <v>1204</v>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>Gränsticka</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>Phellopilus nigrolimitatus</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
-      <c r="P89" t="inlineStr">
-        <is>
-          <t>Djupfors V, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q89" t="n">
-        <v>561061.5146522231</v>
-      </c>
-      <c r="R89" t="n">
-        <v>7308842.570840668</v>
-      </c>
-      <c r="S89" t="n">
-        <v>50</v>
-      </c>
-      <c r="T89" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U89" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="V89" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W89" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="Y89" t="inlineStr">
-        <is>
-          <t>2014-09-05</t>
-        </is>
-      </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA89" t="inlineStr">
-        <is>
-          <t>2014-09-05</t>
-        </is>
-      </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD89" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE89" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG89" t="b">
-        <v>0</v>
-      </c>
-      <c r="AR89" t="inlineStr">
-        <is>
-          <t>25352</t>
-        </is>
-      </c>
-      <c r="AT89" t="inlineStr"/>
-      <c r="AW89" t="inlineStr">
-        <is>
-          <t>Malin Sahlin</t>
-        </is>
-      </c>
-      <c r="AX89" t="inlineStr">
-        <is>
-          <t>Via Malin Sahlin</t>
-        </is>
-      </c>
-      <c r="AY89" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" t="n">
-        <v>126361165</v>
-      </c>
-      <c r="B90" t="n">
-        <v>91259</v>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E90" t="n">
-        <v>1204</v>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>Gränsticka</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>Phellopilus nigrolimitatus</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
-      <c r="P90" t="inlineStr">
-        <is>
-          <t>Djupselet, Djupselet, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q90" t="n">
-        <v>561436</v>
-      </c>
-      <c r="R90" t="n">
-        <v>7308968</v>
-      </c>
-      <c r="S90" t="n">
-        <v>10</v>
-      </c>
-      <c r="T90" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U90" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="V90" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W90" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="Y90" t="inlineStr">
-        <is>
-          <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AA90" t="inlineStr">
-        <is>
-          <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AD90" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE90" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG90" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI90" t="inlineStr">
-        <is>
-          <t>Bördig, grovvuxen grannaturskog</t>
-        </is>
-      </c>
-      <c r="AT90" t="inlineStr"/>
-      <c r="AW90" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AX90" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY90" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" t="n">
-        <v>126361127</v>
-      </c>
-      <c r="B91" t="n">
-        <v>75066</v>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E91" t="n">
-        <v>492</v>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>Smalskaftslav</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>Chaenotheca gracilenta</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
-      <c r="P91" t="inlineStr">
-        <is>
-          <t>Djupselet, Djupselet, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q91" t="n">
-        <v>561403</v>
-      </c>
-      <c r="R91" t="n">
-        <v>7308978</v>
-      </c>
-      <c r="S91" t="n">
-        <v>10</v>
-      </c>
-      <c r="T91" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U91" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="V91" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W91" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="Y91" t="inlineStr">
-        <is>
-          <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AA91" t="inlineStr">
-        <is>
-          <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AD91" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE91" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG91" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI91" t="inlineStr">
-        <is>
-          <t>Bördig, grovvuxen grannaturskog</t>
-        </is>
-      </c>
-      <c r="AT91" t="inlineStr"/>
-      <c r="AW91" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AX91" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY91" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" t="n">
-        <v>126361121</v>
-      </c>
-      <c r="B92" t="n">
-        <v>75080</v>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E92" t="n">
-        <v>1467</v>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>Rödbrun blekspik</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>Sclerophora coniophaea</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
-      <c r="P92" t="inlineStr">
-        <is>
-          <t>Djupselet, Djupselet, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q92" t="n">
-        <v>561403</v>
-      </c>
-      <c r="R92" t="n">
-        <v>7308978</v>
-      </c>
-      <c r="S92" t="n">
-        <v>10</v>
-      </c>
-      <c r="T92" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U92" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="V92" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W92" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="Y92" t="inlineStr">
-        <is>
-          <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AA92" t="inlineStr">
-        <is>
-          <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AD92" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE92" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG92" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI92" t="inlineStr">
-        <is>
-          <t>Bördig, grovvuxen grannaturskog</t>
-        </is>
-      </c>
-      <c r="AT92" t="inlineStr"/>
-      <c r="AW92" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AX92" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY92" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" t="n">
-        <v>126361100</v>
-      </c>
-      <c r="B93" t="n">
-        <v>91263</v>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E93" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
-      <c r="P93" t="inlineStr">
-        <is>
-          <t>Djupselet, Djupselet, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q93" t="n">
-        <v>561396</v>
-      </c>
-      <c r="R93" t="n">
-        <v>7308982</v>
-      </c>
-      <c r="S93" t="n">
-        <v>10</v>
-      </c>
-      <c r="T93" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U93" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="V93" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W93" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="Y93" t="inlineStr">
-        <is>
-          <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AA93" t="inlineStr">
-        <is>
-          <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AD93" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE93" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG93" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI93" t="inlineStr">
-        <is>
-          <t>Bördig, grovvuxen grannaturskog</t>
-        </is>
-      </c>
-      <c r="AT93" t="inlineStr"/>
-      <c r="AW93" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AX93" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY93" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" t="n">
-        <v>66544653</v>
-      </c>
-      <c r="B94" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E94" t="n">
-        <v>1108</v>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>Harticka</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
-      <c r="P94" t="inlineStr">
-        <is>
-          <t>Djupfors V, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q94" t="n">
-        <v>561132.2069487682</v>
-      </c>
-      <c r="R94" t="n">
-        <v>7308696.41208922</v>
-      </c>
-      <c r="S94" t="n">
-        <v>50</v>
-      </c>
-      <c r="T94" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U94" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="V94" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W94" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="Y94" t="inlineStr">
-        <is>
-          <t>2014-09-05</t>
-        </is>
-      </c>
-      <c r="Z94" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA94" t="inlineStr">
-        <is>
-          <t>2014-09-05</t>
-        </is>
-      </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD94" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE94" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG94" t="b">
-        <v>0</v>
-      </c>
-      <c r="AR94" t="inlineStr">
-        <is>
-          <t>25375</t>
-        </is>
-      </c>
-      <c r="AT94" t="inlineStr"/>
-      <c r="AW94" t="inlineStr">
-        <is>
-          <t>Malin Sahlin</t>
-        </is>
-      </c>
-      <c r="AX94" t="inlineStr">
-        <is>
-          <t>Via Malin Sahlin</t>
-        </is>
-      </c>
-      <c r="AY94" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" t="n">
-        <v>66544652</v>
-      </c>
-      <c r="B95" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E95" t="n">
-        <v>1312</v>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>Gammelgransskål</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>Pseudographis pinicola</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
-      <c r="P95" t="inlineStr">
-        <is>
-          <t>Djupfors V, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q95" t="n">
-        <v>561132.2069487682</v>
-      </c>
-      <c r="R95" t="n">
-        <v>7308696.41208922</v>
-      </c>
-      <c r="S95" t="n">
-        <v>50</v>
-      </c>
-      <c r="T95" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U95" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="V95" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W95" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="Y95" t="inlineStr">
-        <is>
-          <t>2014-09-05</t>
-        </is>
-      </c>
-      <c r="Z95" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA95" t="inlineStr">
-        <is>
-          <t>2014-09-05</t>
-        </is>
-      </c>
-      <c r="AB95" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD95" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE95" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG95" t="b">
-        <v>0</v>
-      </c>
-      <c r="AR95" t="inlineStr">
-        <is>
-          <t>25374</t>
-        </is>
-      </c>
-      <c r="AT95" t="inlineStr"/>
-      <c r="AW95" t="inlineStr">
-        <is>
-          <t>Malin Sahlin</t>
-        </is>
-      </c>
-      <c r="AX95" t="inlineStr">
-        <is>
-          <t>Via Malin Sahlin</t>
-        </is>
-      </c>
-      <c r="AY95" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 8219-2025 artfynd.xlsx
+++ b/artfynd/A 8219-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY84"/>
+  <dimension ref="A1:AZ84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126355489</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125605476</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126355483</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1075,6 +1095,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126355571</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126356440</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1279,6 +1309,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126356501</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1381,6 +1416,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126356436</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1487,6 +1527,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126355857</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1589,6 +1634,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126356490</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1691,6 +1741,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126356815</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1793,6 +1848,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126357095</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1895,6 +1955,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126355561</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1996,6 +2061,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127275517</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2098,6 +2168,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126356649</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2195,6 +2270,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127274996</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2292,6 +2372,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127274895</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2394,6 +2479,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126356631</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2500,6 +2590,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126357389</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2602,6 +2697,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126359227</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2708,6 +2808,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126358063</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2814,6 +2919,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126358035</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2920,6 +3030,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126357490</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3026,6 +3141,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126357916</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3128,6 +3248,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66544349</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3234,6 +3359,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126357718</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3336,6 +3466,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126359216</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3442,6 +3577,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126358040</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3548,6 +3688,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126357748</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3650,6 +3795,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126358410</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3756,6 +3906,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126358290</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3858,6 +4013,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126357428</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3964,6 +4124,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126358030</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4066,6 +4231,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126358404</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4173,6 +4343,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126357434</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4275,6 +4450,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66544351</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4381,6 +4561,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126360392</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4483,6 +4668,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66544348</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4589,6 +4779,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126360330</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4695,6 +4890,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126360636</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4797,6 +4997,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66544343</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4899,6 +5104,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66544345</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5001,6 +5211,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66544347</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5103,6 +5318,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66544350</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5209,6 +5429,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126360324</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5315,6 +5540,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126360389</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5417,6 +5647,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66544344</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5519,6 +5754,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66544353</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5621,6 +5861,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66544346</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5723,6 +5968,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66544342</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5825,6 +6075,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126361127</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5927,6 +6182,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66544648</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6033,6 +6293,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66544623</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6135,6 +6400,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66544638</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6237,6 +6507,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66544645</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6339,6 +6614,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66544651</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6441,6 +6721,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66544633</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6543,6 +6828,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66544628</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6645,6 +6935,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66544630</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6747,6 +7042,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66544627</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6849,6 +7149,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66544640</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6951,6 +7256,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66544646</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7053,6 +7363,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66544629</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7155,6 +7470,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126361165</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7257,6 +7577,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66544641</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7359,6 +7684,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66544619</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7461,6 +7791,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66544632</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7563,6 +7898,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66544636</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7665,6 +8005,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66544644</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7767,6 +8112,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66544649</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7869,6 +8219,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126361121</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7971,6 +8326,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66544634</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8073,6 +8433,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66544341</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8179,6 +8544,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66544622</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8285,6 +8655,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66544626</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8391,6 +8766,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66544631</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8497,6 +8877,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66544635</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8603,6 +8988,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66544639</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8709,6 +9099,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66544643</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8815,6 +9210,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66544647</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8917,6 +9317,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66544621</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9019,6 +9424,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66544625</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9121,6 +9531,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66544653</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9223,8 +9638,98 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66544652</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>